--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="110">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -3,8 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9197F33A-2120-4999-A6C4-B2F6282B7B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -19,375 +25,392 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr/>
-  <fileRecoveryPr autoRecover="0" crashSave="0" dataExtractLoad="0" repairLoad="0"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr autoRecover="0"/>
   <extLst>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="110">
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10;20;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseMonster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="114">
+  <si>
+    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>Slime</t>
+  </si>
+  <si>
+    <t>icon_id</t>
+  </si>
+  <si>
+    <t>메인 기차</t>
+  </si>
+  <si>
+    <t>레이저 포탑</t>
+  </si>
+  <si>
+    <t>저격 포탑</t>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>충격 포탑</t>
+  </si>
+  <si>
+    <t>체력 증가</t>
+  </si>
+  <si>
+    <t>공격력 증가</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>전기 포탑</t>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>포격 포탑</t>
+  </si>
+  <si>
+    <t>upgrade_value</t>
+  </si>
+  <si>
+    <t>monster_name</t>
+  </si>
+  <si>
+    <t>drop_exp_max</t>
+  </si>
+  <si>
+    <t>제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t>attack_range</t>
+  </si>
+  <si>
+    <t>drop_money_min</t>
+  </si>
+  <si>
+    <t>stage_end_time</t>
+  </si>
+  <si>
+    <t>drop_exp_min</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>upgrade_name</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>target_train_id</t>
+  </si>
+  <si>
+    <t>attack_count</t>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t>attack_delay</t>
+  </si>
+  <si>
+    <t>attack_damage</t>
+  </si>
+  <si>
+    <t>train_data_id</t>
+  </si>
+  <si>
+    <t>LaserProjectile</t>
+  </si>
+  <si>
+    <t>drop_money_max</t>
+  </si>
+  <si>
+    <t>FireTurretTrain</t>
+  </si>
+  <si>
+    <t>target_count</t>
+  </si>
+  <si>
+    <t>ExplosionProjectile</t>
+  </si>
+  <si>
+    <t>MissileTurretTrain</t>
+  </si>
+  <si>
+    <t>weighted_upgrades</t>
+  </si>
+  <si>
+    <t>CannonTurretTrain</t>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
+  </si>
+  <si>
+    <t>ElectrickProjectile</t>
+  </si>
+  <si>
+    <t>CannonProjectile</t>
+  </si>
+  <si>
+    <t>SniperTurretTrain</t>
+  </si>
+  <si>
+    <t>LaserTurretTrain</t>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t>SniperProjectile</t>
+  </si>
+  <si>
+    <t>max_upgrade_count</t>
+  </si>
+  <si>
+    <t>ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t>ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t>ColdAirProjectile</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>획득하는 골드 증가</t>
+  </si>
+  <si>
+    <t>10;20;30</t>
+  </si>
+  <si>
+    <t>공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t>prefab_id</t>
+  </si>
+  <si>
+    <t>train_name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>공격 딜레이 감소</t>
+  </si>
+  <si>
+    <t>move_speed</t>
+  </si>
+  <si>
+    <t>획득하는 경험치 증가</t>
+  </si>
+  <si>
+    <t>BaseMonster</t>
+  </si>
+  <si>
+    <t>MainTrain</t>
+  </si>
+  <si>
+    <t>need_money</t>
+  </si>
+  <si>
+    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t>projectile_prefab_id</t>
+  </si>
+  <si>
+    <t>stage_inspection_time</t>
+  </si>
+  <si>
+    <t>레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t>ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>FireEffectProjectile</t>
+  </si>
+  <si>
+    <t>upgrade_type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
+    <t>NonTrainUpgrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">TrainUpgrade</t>
+    <t>TrainUpgrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">stat_type</t>
+    <t>stat_type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">MaxHp</t>
+    <t>MaxHp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">AttackDamage</t>
+    <t>AttackDamage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">AttackInterval</t>
+    <t>AttackInterval</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+    <t>공격력 {0} 증가 범위 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+    <t>공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
+    <t>공격력 {0} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+    <t>공격력 {0} 증가 공격 범위 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
+    <t>기관총 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
+    <t>화염 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
+    <t>미사일 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
+    <t>레이저 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
+    <t>전기 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
+    <t>포격 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
+    <t>저격 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
+    <t>냉기 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
+    <t>폭발 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리트 기관총 포탑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관총 포탑에 강화 버전이다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalTurretTrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EliteNormalTurretTrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalProjectile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tier</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -416,12 +439,110 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="8"/>
+      </left>
+      <right style="medium">
+        <color theme="8"/>
+      </right>
+      <top style="medium">
+        <color theme="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="8"/>
+      </left>
+      <right style="medium">
+        <color theme="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top style="medium">
+        <color theme="7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="7"/>
+      </left>
+      <right style="medium">
+        <color theme="7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -430,7 +551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -440,21 +561,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}"/>
   </tableStyles>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -751,10 +905,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" style="1" customWidth="1"/>
@@ -768,15 +922,15 @@
     <col min="13" max="13" width="11.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -785,7 +939,7 @@
         <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>37</v>
@@ -806,10 +960,10 @@
         <v>27</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
@@ -826,42 +980,42 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L2" s="1">
         <v>1.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="1" customWidth="1"/>
@@ -869,15 +1023,15 @@
     <col min="9" max="9" width="19.78515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -898,15 +1052,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -915,15 +1069,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
@@ -932,15 +1086,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -949,15 +1103,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -967,15 +1121,15 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -984,15 +1138,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1003,16 +1157,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="1" customWidth="1"/>
@@ -1024,37 +1178,37 @@
     <col min="10" max="10" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>110001</v>
       </c>
@@ -1062,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1074,18 +1228,18 @@
         <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>110002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>0</v>
@@ -1100,13 +1254,13 @@
         <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>110003</v>
       </c>
@@ -1114,7 +1268,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1126,18 +1280,18 @@
         <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>110004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1152,15 +1306,15 @@
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>110005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1175,36 +1329,36 @@
         <v>10</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="1" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -1213,13 +1367,13 @@
         <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>20001</v>
       </c>
@@ -1236,21 +1390,21 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="1" customWidth="1"/>
@@ -1262,15 +1416,15 @@
     <col min="13" max="13" width="15.640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -1279,7 +1433,7 @@
         <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -1297,18 +1451,18 @@
         <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A2" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8">
         <v>40001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1317,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1335,8 +1489,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9">
         <v>40002</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1352,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1367,41 +1521,50 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>60</v>
-      </c>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" style="1" customWidth="1"/>
     <col min="4" max="5" width="15.640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.92578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="1" customWidth="1"/>
     <col min="7" max="10" width="15.640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="20.92578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.640625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="19.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -1410,7 +1573,7 @@
         <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -1431,11 +1594,11 @@
         <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A2" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
         <v>30001</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1450,8 +1613,8 @@
       <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>52</v>
+      <c r="F2" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1468,19 +1631,19 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A3" s="1">
+      <c r="M2" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="4">
         <v>30002</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
@@ -1507,18 +1670,18 @@
         <v>0</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A4" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4">
         <v>30003</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
@@ -1548,15 +1711,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A5" s="1">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4">
         <v>30004</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
@@ -1565,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H5" s="1">
         <v>15</v>
@@ -1586,15 +1749,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A6" s="1">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4">
         <v>30005</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -1603,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1624,8 +1787,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A7" s="1">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4">
         <v>30006</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1659,18 +1822,18 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A8" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4">
         <v>30007</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -1679,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
@@ -1697,43 +1860,117 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>56</v>
-      </c>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="4"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5">
+        <v>31001</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="1">
+        <v>150</v>
+      </c>
+      <c r="E12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="1">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="6"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="6"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6"/>
+    </row>
+    <row r="21" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>50001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1">
         <v>180</v>
@@ -1741,16 +1978,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="1" customWidth="1"/>
@@ -1760,9 +1997,9 @@
     <col min="7" max="7" width="13.92578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>39</v>
@@ -1770,9 +2007,12 @@
       <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A2" s="1">
+      <c r="D1" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8">
         <v>60001</v>
       </c>
       <c r="B2" s="1">
@@ -1781,9 +2021,12 @@
       <c r="C2" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A3" s="1">
+      <c r="D2" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9">
         <v>60002</v>
       </c>
       <c r="B3" s="1">
@@ -1792,9 +2035,12 @@
       <c r="C3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A4" s="1">
+      <c r="D3" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9">
         <v>60003</v>
       </c>
       <c r="B4" s="1">
@@ -1803,9 +2049,12 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A5" s="1">
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9">
         <v>60004</v>
       </c>
       <c r="B5" s="1">
@@ -1814,9 +2063,12 @@
       <c r="C5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A6" s="1">
+      <c r="D5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9">
         <v>60005</v>
       </c>
       <c r="B6" s="1">
@@ -1825,9 +2077,12 @@
       <c r="C6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A7" s="1">
+      <c r="D6" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9">
         <v>60006</v>
       </c>
       <c r="B7" s="1">
@@ -1836,9 +2091,12 @@
       <c r="C7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A8" s="1">
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9">
         <v>60007</v>
       </c>
       <c r="B8" s="1">
@@ -1847,9 +2105,12 @@
       <c r="C8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A9" s="1">
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9">
         <v>60008</v>
       </c>
       <c r="B9" s="1">
@@ -1858,9 +2119,12 @@
       <c r="C9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A10" s="1">
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="9">
         <v>60009</v>
       </c>
       <c r="B10" s="1">
@@ -1869,29 +2133,80 @@
       <c r="C10" s="1">
         <v>0</v>
       </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="9"/>
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="9"/>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="9"/>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="9"/>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="9"/>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="10"/>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>61001</v>
+      </c>
+      <c r="B17" s="1">
+        <v>31001</v>
+      </c>
+      <c r="D17" s="13">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.78515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>34</v>
@@ -1906,8 +2221,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A2" s="1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8">
         <v>70001</v>
       </c>
       <c r="B2" s="1">
@@ -1923,8 +2238,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="9">
         <v>70002</v>
       </c>
       <c r="B3" s="1">
@@ -1940,8 +2255,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A4" s="1">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9">
         <v>70003</v>
       </c>
       <c r="B4" s="1">
@@ -1957,8 +2272,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A5" s="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9">
         <v>70004</v>
       </c>
       <c r="B5" s="1">
@@ -1974,8 +2289,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A6" s="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9">
         <v>70005</v>
       </c>
       <c r="B6" s="1">
@@ -1991,8 +2306,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A7" s="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9">
         <v>70006</v>
       </c>
       <c r="B7" s="1">
@@ -2008,8 +2323,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A8" s="1">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9">
         <v>70007</v>
       </c>
       <c r="B8" s="1">
@@ -2025,8 +2340,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A9" s="1">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9">
         <v>70008</v>
       </c>
       <c r="B9" s="1">
@@ -2042,8 +2357,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A10" s="1">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="9">
         <v>70009</v>
       </c>
       <c r="B10" s="1">
@@ -2059,32 +2374,65 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="9"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="10"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="11"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="11"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="11"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="11"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="11"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -2093,23 +2441,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="1" customWidth="1"/>
@@ -2121,15 +2469,15 @@
     <col min="9" max="9" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -2150,15 +2498,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1">
         <v>5</v>
@@ -2167,15 +2515,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G3" s="1">
         <v>10</v>
@@ -2184,15 +2532,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="1">
         <v>25</v>
@@ -2201,57 +2549,57 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G7" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G8" s="1">
         <v>15</v>
@@ -2260,15 +2608,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="1">
         <v>20</v>
@@ -2277,15 +2625,15 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G10" s="1">
         <v>40</v>
@@ -2294,57 +2642,57 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A11" s="0">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
         <v>90004</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G11" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G12" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G13" s="1">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A14" s="0">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
         <v>90005</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
@@ -2353,15 +2701,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
         <v>5</v>
@@ -2370,15 +2718,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16" s="1">
         <v>7</v>
@@ -2387,15 +2735,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A17" s="0">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
         <v>90006</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -2404,15 +2752,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
@@ -2421,15 +2769,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
         <v>90006</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -2438,43 +2786,43 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2">
         <v>90007</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2">
         <v>90007</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G21" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2">
         <v>90007</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G22" s="1">
         <v>350</v>
@@ -2482,7 +2830,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9197F33A-2120-4999-A6C4-B2F6282B7B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5265ACE-9AB0-4FC6-8D8A-346611638EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5265ACE-9AB0-4FC6-8D8A-346611638EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -25,392 +19,397 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr autoRecover="0"/>
+  <calcPr/>
+  <fileRecoveryPr autoRecover="0" crashSave="0" dataExtractLoad="0" repairLoad="0"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="114">
-  <si>
-    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>Slime</t>
-  </si>
-  <si>
-    <t>icon_id</t>
-  </si>
-  <si>
-    <t>메인 기차</t>
-  </si>
-  <si>
-    <t>레이저 포탑</t>
-  </si>
-  <si>
-    <t>저격 포탑</t>
-  </si>
-  <si>
-    <t>화염 포탑</t>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>충격 포탑</t>
-  </si>
-  <si>
-    <t>체력 증가</t>
-  </si>
-  <si>
-    <t>공격력 증가</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>전기 포탑</t>
-  </si>
-  <si>
-    <t>미사일 포탑</t>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>포격 포탑</t>
-  </si>
-  <si>
-    <t>upgrade_value</t>
-  </si>
-  <si>
-    <t>monster_name</t>
-  </si>
-  <si>
-    <t>drop_exp_max</t>
-  </si>
-  <si>
-    <t>제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t>attack_range</t>
-  </si>
-  <si>
-    <t>drop_money_min</t>
-  </si>
-  <si>
-    <t>stage_end_time</t>
-  </si>
-  <si>
-    <t>drop_exp_min</t>
-  </si>
-  <si>
-    <t>is_main_train</t>
-  </si>
-  <si>
-    <t>upgrade_name</t>
-  </si>
-  <si>
-    <t>attack_interval</t>
-  </si>
-  <si>
-    <t>target_train_id</t>
-  </si>
-  <si>
-    <t>attack_count</t>
-  </si>
-  <si>
-    <t>기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t>attack_delay</t>
-  </si>
-  <si>
-    <t>attack_damage</t>
-  </si>
-  <si>
-    <t>train_data_id</t>
-  </si>
-  <si>
-    <t>LaserProjectile</t>
-  </si>
-  <si>
-    <t>drop_money_max</t>
-  </si>
-  <si>
-    <t>FireTurretTrain</t>
-  </si>
-  <si>
-    <t>target_count</t>
-  </si>
-  <si>
-    <t>ExplosionProjectile</t>
-  </si>
-  <si>
-    <t>MissileTurretTrain</t>
-  </si>
-  <si>
-    <t>weighted_upgrades</t>
-  </si>
-  <si>
-    <t>CannonTurretTrain</t>
-  </si>
-  <si>
-    <t>MissileProjectile</t>
-  </si>
-  <si>
-    <t>ElectrickProjectile</t>
-  </si>
-  <si>
-    <t>CannonProjectile</t>
-  </si>
-  <si>
-    <t>SniperTurretTrain</t>
-  </si>
-  <si>
-    <t>LaserTurretTrain</t>
-  </si>
-  <si>
-    <t>화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t>SniperProjectile</t>
-  </si>
-  <si>
-    <t>max_upgrade_count</t>
-  </si>
-  <si>
-    <t>ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t>ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t>ColdAirProjectile</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>획득하는 골드 증가</t>
-  </si>
-  <si>
-    <t>10;20;30</t>
-  </si>
-  <si>
-    <t>공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t>prefab_id</t>
-  </si>
-  <si>
-    <t>train_name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>공격 딜레이 감소</t>
-  </si>
-  <si>
-    <t>move_speed</t>
-  </si>
-  <si>
-    <t>획득하는 경험치 증가</t>
-  </si>
-  <si>
-    <t>BaseMonster</t>
-  </si>
-  <si>
-    <t>MainTrain</t>
-  </si>
-  <si>
-    <t>need_money</t>
-  </si>
-  <si>
-    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t>projectile_prefab_id</t>
-  </si>
-  <si>
-    <t>stage_inspection_time</t>
-  </si>
-  <si>
-    <t>레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t>ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t>FireEffectProjectile</t>
-  </si>
-  <si>
-    <t>upgrade_type</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="115">
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10;20;30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseMonster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NonTrainUpgrade</t>
+    <t xml:space="preserve">NonTrainUpgrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TrainUpgrade</t>
+    <t xml:space="preserve">TrainUpgrade</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>stat_type</t>
+    <t xml:space="preserve">stat_type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MaxHp</t>
+    <t xml:space="preserve">MaxHp</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AttackDamage</t>
+    <t xml:space="preserve">AttackDamage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AttackInterval</t>
+    <t xml:space="preserve">AttackInterval</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} 증가 범위 {1} 증가</t>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} 증가</t>
+    <t xml:space="preserve">공격력 {0} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} 증가 공격 범위 {1} 증가</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>기관총 포탑 강화</t>
+    <t xml:space="preserve">기관총 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>화염 포탑 강화</t>
+    <t xml:space="preserve">화염 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미사일 포탑 강화</t>
+    <t xml:space="preserve">미사일 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>레이저 포탑 강화</t>
+    <t xml:space="preserve">레이저 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>전기 포탑 강화</t>
+    <t xml:space="preserve">전기 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>포격 포탑 강화</t>
+    <t xml:space="preserve">포격 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>저격 포탑 강화</t>
+    <t xml:space="preserve">저격 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>냉기 포탑 강화</t>
+    <t xml:space="preserve">냉기 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>폭발 포탑 강화</t>
+    <t xml:space="preserve">폭발 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>엘리트 기관총 포탑</t>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>기관총 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NormalTurretTrain</t>
+    <t xml:space="preserve">NormalTurretTrain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>EliteNormalTurretTrain</t>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>NormalProjectile</t>
+    <t xml:space="preserve">NormalProjectile</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>tier</t>
+    <t xml:space="preserve">tier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -600,15 +599,15 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -905,10 +904,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" style="1" customWidth="1"/>
@@ -922,7 +921,7 @@
     <col min="13" max="13" width="11.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -963,7 +962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
@@ -1006,16 +1005,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="1" customWidth="1"/>
@@ -1023,7 +1022,7 @@
     <col min="9" max="9" width="19.78515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1052,7 +1051,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -1069,7 +1068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
@@ -1086,7 +1085,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
@@ -1103,7 +1102,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
@@ -1121,7 +1120,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
@@ -1138,7 +1137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
@@ -1157,16 +1156,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="1" customWidth="1"/>
@@ -1178,7 +1177,7 @@
     <col min="10" max="10" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1208,7 +1207,7 @@
       </c>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>110001</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>110002</v>
       </c>
@@ -1260,7 +1259,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>110003</v>
       </c>
@@ -1286,7 +1285,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>110004</v>
       </c>
@@ -1309,7 +1308,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>110005</v>
       </c>
@@ -1334,23 +1333,23 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="1" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1373,7 +1372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>20001</v>
       </c>
@@ -1395,16 +1394,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="1" customWidth="1"/>
@@ -1454,7 +1453,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>40001</v>
       </c>
@@ -1489,7 +1488,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A3" s="9">
         <v>40002</v>
       </c>
@@ -1524,10 +1523,10 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A4" s="9"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A5" s="9"/>
     </row>
     <row r="6" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.6">
@@ -1535,16 +1534,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="1" customWidth="1"/>
@@ -1597,7 +1596,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="3">
         <v>30001</v>
       </c>
@@ -1635,7 +1634,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A3" s="4">
         <v>30002</v>
       </c>
@@ -1673,7 +1672,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A4" s="4">
         <v>30003</v>
       </c>
@@ -1711,7 +1710,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A5" s="4">
         <v>30004</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A6" s="4">
         <v>30005</v>
       </c>
@@ -1787,7 +1786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A7" s="4">
         <v>30006</v>
       </c>
@@ -1825,7 +1824,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A8" s="4">
         <v>30007</v>
       </c>
@@ -1863,16 +1862,16 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A12" s="5">
         <v>31001</v>
       </c>
@@ -1910,28 +1909,28 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A13" s="6"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A16" s="6"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="6"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="6"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="6"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="6"/>
     </row>
     <row r="21" spans="1:1" ht="18" thickBot="1" x14ac:dyDescent="0.6">
@@ -1939,22 +1938,22 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -1965,7 +1964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>50001</v>
       </c>
@@ -1978,16 +1977,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="1" customWidth="1"/>
@@ -1997,7 +1996,7 @@
     <col min="7" max="7" width="13.92578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -2010,8 +2009,11 @@
       <c r="D1" s="12" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E1" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>60001</v>
       </c>
@@ -2025,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="9">
         <v>60002</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="9">
         <v>60003</v>
       </c>
@@ -2053,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="9">
         <v>60004</v>
       </c>
@@ -2067,7 +2069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="9">
         <v>60005</v>
       </c>
@@ -2081,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="9">
         <v>60006</v>
       </c>
@@ -2095,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="9">
         <v>60007</v>
       </c>
@@ -2109,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="9">
         <v>60008</v>
       </c>
@@ -2123,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="9">
         <v>60009</v>
       </c>
@@ -2137,44 +2139,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="9"/>
       <c r="D11" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="9"/>
       <c r="D12" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="9"/>
       <c r="D13" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="9"/>
       <c r="D14" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="9"/>
       <c r="D15" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16" s="10"/>
       <c r="D16" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A17" s="0">
         <v>61001</v>
       </c>
       <c r="B17" s="1">
@@ -2183,19 +2185,22 @@
       <c r="D17" s="13">
         <v>1</v>
       </c>
+      <c r="E17" s="13">
+        <v>30001</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="1" customWidth="1"/>
@@ -2221,7 +2226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>70001</v>
       </c>
@@ -2238,7 +2243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="9">
         <v>70002</v>
       </c>
@@ -2255,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="9">
         <v>70003</v>
       </c>
@@ -2272,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="9">
         <v>70004</v>
       </c>
@@ -2289,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="9">
         <v>70005</v>
       </c>
@@ -2306,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="9">
         <v>70006</v>
       </c>
@@ -2323,7 +2328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="9">
         <v>70007</v>
       </c>
@@ -2340,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="9">
         <v>70008</v>
       </c>
@@ -2357,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="9">
         <v>70009</v>
       </c>
@@ -2374,57 +2379,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="9"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="9"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="9"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="9"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="9"/>
     </row>
     <row r="16" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="11"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="11"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="11"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="11"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A21" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -2441,23 +2446,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="1" customWidth="1"/>
@@ -2469,7 +2474,7 @@
     <col min="9" max="9" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -2498,7 +2503,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
@@ -2515,7 +2520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
@@ -2532,7 +2537,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
@@ -2549,7 +2554,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
@@ -2563,7 +2568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
@@ -2577,7 +2582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
@@ -2591,7 +2596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
@@ -2608,7 +2613,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
@@ -2625,7 +2630,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
@@ -2642,8 +2647,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A11" s="0">
         <v>90004</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -2656,7 +2661,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
@@ -2670,7 +2675,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
@@ -2684,8 +2689,8 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A14" s="0">
         <v>90005</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2701,7 +2706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
@@ -2718,7 +2723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
@@ -2735,8 +2740,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A17" s="0">
         <v>90006</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -2752,7 +2757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
@@ -2769,7 +2774,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A19" s="2">
         <v>90006</v>
       </c>
@@ -2786,7 +2791,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A20" s="2">
         <v>90007</v>
       </c>
@@ -2800,7 +2805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A21" s="2">
         <v>90007</v>
       </c>
@@ -2814,7 +2819,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A22" s="2">
         <v>90007</v>
       </c>
@@ -2830,7 +2835,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69986110925674405" right="0.69986110925674405" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -2021,7 +2021,7 @@
         <v>30001</v>
       </c>
       <c r="C2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" s="13">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -24,83 +24,170 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="116">
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10;20;30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
   <si>
     <t xml:space="preserve">20</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
   </si>
   <si>
     <t xml:space="preserve">포격 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
     <t xml:space="preserve">미사일 포탑</t>
   </si>
   <si>
@@ -113,58 +200,43 @@
     <t xml:space="preserve">충격 포탑</t>
   </si>
   <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
     <t xml:space="preserve">레이저 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">체력 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">damage</t>
   </si>
   <si>
-    <t xml:space="preserve">화염 포탑</t>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
   </si>
   <si>
     <t xml:space="preserve">Gnoll</t>
   </si>
   <si>
-    <t xml:space="preserve">max_hp</t>
+    <t xml:space="preserve">Thief</t>
   </si>
   <si>
     <t xml:space="preserve">놀이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
     <t xml:space="preserve">해골 병사다.</t>
   </si>
   <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
   </si>
   <si>
     <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
@@ -173,189 +245,117 @@
     <t xml:space="preserve">target_train_id</t>
   </si>
   <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
+    <t xml:space="preserve">TrainUpgrade</t>
   </si>
   <si>
     <t xml:space="preserve">drop_exp_max</t>
   </si>
   <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10;20;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">stage_inspection_time</t>
   </si>
   <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteNormalTurretTrain</t>
   </si>
   <si>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
   </si>
 </sst>
 </file>
@@ -976,43 +976,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1020,10 +1020,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3">
         <v>10</v>
@@ -1035,25 +1035,25 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L2" s="3">
         <v>1.5</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1061,10 +1061,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1">
         <v>30</v>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1102,10 +1102,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1135,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1158,31 +1158,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1190,10 +1190,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1224,10 +1224,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1241,10 +1241,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1259,10 +1259,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1298,9 +1298,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.5859375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.92578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="15.140625" style="3" customWidth="1"/>
@@ -1312,31 +1312,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="J1" s="4"/>
     </row>
@@ -1345,10 +1345,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1360,10 +1360,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1371,10 +1371,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
         <v>200</v>
@@ -1386,10 +1386,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1397,10 +1397,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1412,10 +1412,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1423,10 +1423,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3">
         <v>300</v>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1446,10 +1446,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
         <v>500</v>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1483,25 +1483,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1509,10 +1509,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1548,40 +1548,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1589,10 +1589,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1624,10 +1624,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1687,43 +1687,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="18">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1731,10 +1731,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1769,10 +1769,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1807,10 +1807,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D4" s="3">
         <v>100</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1845,7 +1845,7 @@
         <v>30004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>111</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1883,10 +1883,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D6" s="3">
         <v>100</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1921,10 +1921,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3">
         <v>100</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1959,10 +1959,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3">
         <v>100</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2006,10 +2006,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3">
         <v>150</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2084,13 +2084,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2098,7 +2098,7 @@
         <v>50001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3">
         <v>180</v>
@@ -2126,19 +2126,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -2338,19 +2338,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2557,19 +2557,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2601,31 +2601,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2633,10 +2633,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G2" s="3">
         <v>5</v>
@@ -2650,10 +2650,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2667,10 +2667,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G4" s="3">
         <v>25</v>
@@ -2684,10 +2684,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2698,10 +2698,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -2712,10 +2712,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -2726,10 +2726,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -2743,10 +2743,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
@@ -2760,10 +2760,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3">
         <v>40</v>
@@ -2777,10 +2777,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G11" s="3">
         <v>50</v>
@@ -2791,10 +2791,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3">
         <v>150</v>
@@ -2805,10 +2805,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G13" s="3">
         <v>250</v>
@@ -2819,10 +2819,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G14" s="3">
         <v>3</v>
@@ -2836,10 +2836,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" s="3">
         <v>5</v>
@@ -2853,10 +2853,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G16" s="3">
         <v>7</v>
@@ -2870,7 +2870,7 @@
         <v>90006</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>112</v>
@@ -2887,7 +2887,7 @@
         <v>90006</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>112</v>
@@ -2904,7 +2904,7 @@
         <v>90006</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>112</v>
@@ -2921,10 +2921,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G20" s="3">
         <v>50</v>
@@ -2935,10 +2935,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3">
         <v>150</v>
@@ -2949,10 +2949,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2" activeTab="10"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -24,42 +24,294 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="116">
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
   </si>
   <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">전기 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
+    <t xml:space="preserve">공격력 {0} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">10;20;30</t>
@@ -68,310 +320,58 @@
     <t xml:space="preserve">need_money</t>
   </si>
   <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
   </si>
 </sst>
 </file>
@@ -976,43 +976,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1020,10 +1020,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D2" s="3">
         <v>10</v>
@@ -1035,25 +1035,25 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1061,10 +1061,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1">
         <v>30</v>
@@ -1091,10 +1091,10 @@
         <v>70</v>
       </c>
       <c r="L3" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1102,10 +1102,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1135,7 +1135,7 @@
         <v>7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1158,31 +1158,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1190,10 +1190,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1224,10 +1224,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1241,10 +1241,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1259,10 +1259,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1312,31 +1312,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="J1" s="4"/>
     </row>
@@ -1345,7 +1345,7 @@
         <v>110001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>101</v>
@@ -1360,10 +1360,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1371,10 +1371,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3">
         <v>200</v>
@@ -1386,10 +1386,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1397,10 +1397,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1412,10 +1412,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1423,10 +1423,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>300</v>
@@ -1438,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1446,10 +1446,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3">
         <v>500</v>
@@ -1461,7 +1461,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1483,25 +1483,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1509,10 +1509,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1548,40 +1548,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="18">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1589,10 +1589,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1624,10 +1624,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1673,7 +1673,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="3" customWidth="1"/>
@@ -1685,56 +1685,56 @@
     <col min="12" max="13" width="19.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.75">
       <c r="A2" s="5">
         <v>30001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1769,10 +1769,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1807,10 +1807,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D4" s="3">
         <v>100</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1845,10 +1845,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D5" s="3">
         <v>100</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1883,10 +1883,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D6" s="3">
         <v>100</v>
@@ -1895,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1921,10 +1921,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3">
         <v>100</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1959,10 +1959,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" s="3">
         <v>100</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -1998,18 +1998,18 @@
     <row r="10" spans="1:1">
       <c r="A10" s="6"/>
     </row>
-    <row r="11" spans="1:1" ht="18">
+    <row r="11" spans="1:1">
       <c r="A11" s="6"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="16.75">
       <c r="A12" s="7">
         <v>31001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3">
         <v>150</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H12" s="3">
         <v>5</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2063,7 +2063,7 @@
     <row r="20" spans="1:1">
       <c r="A20" s="8"/>
     </row>
-    <row r="21" spans="1:1" ht="18">
+    <row r="21" spans="1:1" ht="16.75">
       <c r="A21" s="9"/>
     </row>
   </sheetData>
@@ -2084,13 +2084,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2098,7 +2098,7 @@
         <v>50001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3">
         <v>180</v>
@@ -2126,19 +2126,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -2338,19 +2338,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2557,19 +2557,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2601,31 +2601,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2633,10 +2633,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G2" s="3">
         <v>5</v>
@@ -2650,10 +2650,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2667,10 +2667,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G4" s="3">
         <v>25</v>
@@ -2684,10 +2684,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2698,10 +2698,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -2712,10 +2712,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -2726,10 +2726,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -2743,10 +2743,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
@@ -2760,10 +2760,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3">
         <v>40</v>
@@ -2777,10 +2777,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3">
         <v>50</v>
@@ -2791,10 +2791,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3">
         <v>150</v>
@@ -2805,10 +2805,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G13" s="3">
         <v>250</v>
@@ -2819,10 +2819,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G14" s="3">
         <v>3</v>
@@ -2836,10 +2836,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G15" s="3">
         <v>5</v>
@@ -2853,10 +2853,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3">
         <v>7</v>
@@ -2870,10 +2870,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -2887,10 +2887,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2904,10 +2904,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -2921,10 +2921,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G20" s="3">
         <v>50</v>
@@ -2935,10 +2935,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G21" s="3">
         <v>150</v>
@@ -2949,10 +2949,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="G22" s="3">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2"/>
+    <workbookView windowWidth="13965" windowHeight="11670" tabRatio="839" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -19,359 +19,355 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="115">
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">MissileTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
   </si>
   <si>
     <t xml:space="preserve">냉기 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10;20;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
   </si>
   <si>
     <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
   </si>
 </sst>
 </file>
@@ -379,7 +375,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -410,6 +406,11 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -420,7 +421,7 @@
     </fill>
   </fills>
   <borders count="9">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -433,8 +434,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -447,8 +451,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -461,8 +468,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -475,8 +485,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -489,8 +502,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -503,8 +519,11 @@
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -517,8 +536,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -531,8 +553,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -545,10 +570,55 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -603,18 +673,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -639,28 +700,188 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
+      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
+      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -709,7 +930,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="20"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -761,7 +982,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="20"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -976,43 +1197,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1020,10 +1241,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3">
         <v>10</v>
@@ -1035,25 +1256,25 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
+      </c>
+      <c r="I2" s="3">
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
+      </c>
+      <c r="K2" s="3">
+        <v>10</v>
       </c>
       <c r="L2" s="3">
         <v>2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1061,13 +1282,13 @@
         <v>10002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1">
         <v>5</v>
@@ -1079,22 +1300,22 @@
         <v>0.5</v>
       </c>
       <c r="H3" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I3" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K3" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L3" s="3">
         <v>1.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1102,10 +1323,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1120,22 +1341,22 @@
         <v>3</v>
       </c>
       <c r="H4" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I4" s="3">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="J4" s="3">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="L4" s="3">
         <v>7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1158,31 +1379,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1190,10 +1411,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -1207,10 +1428,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1224,10 +1445,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1241,10 +1462,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1259,10 +1480,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1276,10 +1497,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1312,28 +1533,28 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>87</v>
@@ -1345,10 +1566,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1360,10 +1581,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1371,10 +1592,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3">
         <v>200</v>
@@ -1386,10 +1607,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1397,10 +1618,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1412,10 +1633,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1423,10 +1644,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3">
         <v>300</v>
@@ -1438,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1446,10 +1667,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3">
         <v>500</v>
@@ -1461,7 +1682,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1483,25 +1704,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1509,10 +1730,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1521,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1755,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="3" customWidth="1"/>
@@ -1546,53 +1767,53 @@
     <col min="13" max="13" width="15.640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.75">
       <c r="A2" s="10">
         <v>40001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1601,22 +1822,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
       </c>
       <c r="I2" s="3">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
       <c r="K2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1624,10 +1845,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1636,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1648,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1660,7 +1881,7 @@
     <row r="5" spans="1:1">
       <c r="A5" s="11"/>
     </row>
-    <row r="6" spans="1:1" ht="18">
+    <row r="6" spans="1:1" ht="16.75">
       <c r="A6" s="12"/>
     </row>
   </sheetData>
@@ -1687,43 +1908,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -1731,10 +1952,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1743,25 +1964,25 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
       </c>
       <c r="I2" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
       <c r="K2" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1769,10 +1990,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1781,13 +2002,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3">
         <v>1</v>
@@ -1799,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1807,10 +2028,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" s="3">
         <v>100</v>
@@ -1819,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
       </c>
       <c r="I4" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J4" s="3">
         <v>1</v>
@@ -1837,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1845,10 +2066,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D5" s="3">
         <v>100</v>
@@ -1857,25 +2078,25 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
       </c>
       <c r="I5" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J5" s="3">
         <v>1</v>
       </c>
       <c r="K5" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1883,10 +2104,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D6" s="3">
         <v>100</v>
@@ -1895,25 +2116,25 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
       </c>
       <c r="I6" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3">
         <v>5</v>
       </c>
       <c r="K6" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3">
         <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1921,10 +2142,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D7" s="3">
         <v>100</v>
@@ -1933,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
         <v>10</v>
@@ -1945,13 +2166,13 @@
         <v>1</v>
       </c>
       <c r="K7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1959,10 +2180,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3">
         <v>100</v>
@@ -1971,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
@@ -1983,13 +2204,13 @@
         <v>1</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2006,10 +2227,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3">
         <v>150</v>
@@ -2018,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H12" s="3">
         <v>5</v>
@@ -2036,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2076,7 +2297,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
@@ -2084,13 +2305,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2098,7 +2319,7 @@
         <v>50001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <v>180</v>
@@ -2126,19 +2347,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -2338,19 +2559,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2557,19 +2778,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2601,31 +2822,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2633,10 +2854,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" s="3">
         <v>5</v>
@@ -2650,10 +2871,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2667,10 +2888,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G4" s="3">
         <v>25</v>
@@ -2684,10 +2905,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2698,10 +2919,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -2712,10 +2933,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -2726,10 +2947,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -2743,10 +2964,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
@@ -2760,10 +2981,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3">
         <v>40</v>
@@ -2777,10 +2998,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3">
         <v>50</v>
@@ -2791,10 +3012,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3">
         <v>150</v>
@@ -2805,10 +3026,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3">
         <v>250</v>
@@ -2819,10 +3040,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3">
         <v>3</v>
@@ -2836,10 +3057,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3">
         <v>5</v>
@@ -2853,10 +3074,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3">
         <v>7</v>
@@ -2870,10 +3091,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -2887,10 +3108,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -2904,10 +3125,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -2921,10 +3142,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G20" s="3">
         <v>50</v>
@@ -2935,10 +3156,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G21" s="3">
         <v>150</v>
@@ -2949,10 +3170,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G22" s="3">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="13965" windowHeight="11670" tabRatio="839" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -19,34 +19,296 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="119">
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
   <si>
     <t xml:space="preserve">180;</t>
   </si>
   <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0;0;0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">max_upgrade_count</t>
   </si>
   <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
+    <t xml:space="preserve">MissileTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">CannonProjectile</t>
@@ -58,316 +320,67 @@
     <t xml:space="preserve">weighted_upgrades</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">MissileProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">stage_inspection_time</t>
   </si>
   <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteNormalTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -375,7 +388,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -406,11 +419,6 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -421,7 +429,7 @@
     </fill>
   </fills>
   <borders count="9">
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left>
         <color indexed="64"/>
       </left>
@@ -434,11 +442,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -451,11 +456,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -468,11 +470,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -485,11 +484,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -502,11 +498,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -519,11 +512,8 @@
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -536,11 +526,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -553,11 +540,8 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -570,55 +554,10 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -673,9 +612,18 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="4">
+    <dxf/>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -700,188 +648,28 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
-      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <tableStyleElement type="wholeTable" size="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1197,43 +985,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1241,10 +1029,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3">
         <v>10</v>
@@ -1256,16 +1044,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3">
         <v>10</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K2" s="3">
         <v>10</v>
@@ -1274,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1282,10 +1070,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D3" s="1">
         <v>50</v>
@@ -1315,7 +1103,7 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1323,10 +1111,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1356,7 +1144,7 @@
         <v>7</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1379,31 +1167,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1411,10 +1199,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F2" s="3">
         <v>1</v>
@@ -1428,10 +1216,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
@@ -1445,10 +1233,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1462,10 +1250,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1480,10 +1268,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1497,10 +1285,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1533,31 +1321,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="J1" s="4"/>
     </row>
@@ -1566,10 +1354,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1581,10 +1369,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1592,10 +1380,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
         <v>200</v>
@@ -1607,10 +1395,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1618,10 +1406,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1633,10 +1421,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1644,10 +1432,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D5" s="3">
         <v>300</v>
@@ -1659,7 +1447,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1667,10 +1455,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D6" s="3">
         <v>500</v>
@@ -1682,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1704,25 +1492,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1730,10 +1518,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1742,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1769,40 +1557,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -1810,10 +1598,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1822,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1837,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1845,10 +1633,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -1857,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -1872,7 +1660,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1908,43 +1696,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -1952,10 +1740,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
@@ -1964,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
@@ -1982,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1990,10 +1778,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3">
         <v>100</v>
@@ -2002,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
@@ -2020,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2028,10 +1816,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" s="3">
         <v>100</v>
@@ -2040,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
@@ -2058,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2066,10 +1854,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3">
         <v>100</v>
@@ -2078,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -2096,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2104,10 +1892,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D6" s="3">
         <v>100</v>
@@ -2116,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3">
         <v>10</v>
@@ -2134,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2142,10 +1930,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3">
         <v>100</v>
@@ -2154,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3">
         <v>10</v>
@@ -2172,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2180,10 +1968,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D8" s="3">
         <v>100</v>
@@ -2192,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3">
         <v>10</v>
@@ -2210,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2227,10 +2015,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3">
         <v>150</v>
@@ -2239,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H12" s="3">
         <v>5</v>
@@ -2257,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2296,33 +2084,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.3359375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3">
         <v>50001</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3">
         <v>180</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2347,19 +2149,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -2559,19 +2361,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2778,19 +2580,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2822,31 +2624,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2854,10 +2656,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G2" s="3">
         <v>5</v>
@@ -2871,10 +2673,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3">
         <v>10</v>
@@ -2888,10 +2690,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G4" s="3">
         <v>25</v>
@@ -2905,10 +2707,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G5" s="3">
         <v>2</v>
@@ -2919,10 +2721,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G6" s="3">
         <v>5</v>
@@ -2933,10 +2735,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -2947,10 +2749,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G8" s="3">
         <v>15</v>
@@ -2964,10 +2766,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G9" s="3">
         <v>20</v>
@@ -2981,10 +2783,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G10" s="3">
         <v>40</v>
@@ -2998,10 +2800,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G11" s="3">
         <v>50</v>
@@ -3012,10 +2814,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3">
         <v>150</v>
@@ -3026,10 +2828,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3">
         <v>250</v>
@@ -3040,10 +2842,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G14" s="3">
         <v>3</v>
@@ -3057,10 +2859,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G15" s="3">
         <v>5</v>
@@ -3074,10 +2876,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3">
         <v>7</v>
@@ -3091,10 +2893,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -3108,10 +2910,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
@@ -3125,10 +2927,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
@@ -3142,10 +2944,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G20" s="3">
         <v>50</v>
@@ -3156,10 +2958,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G21" s="3">
         <v>150</v>
@@ -3170,10 +2972,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G22" s="3">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2"/>
+    <workbookView windowWidth="13965" windowHeight="11670" tabRatio="839" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -19,77 +19,232 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="120">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
   <si>
     <t xml:space="preserve">Melee</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_type</t>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7;1;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
   </si>
   <si>
     <t xml:space="preserve">SniperProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">replace_train_id</t>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">CannonProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">SniperTurretTrain</t>
@@ -98,22 +253,76 @@
     <t xml:space="preserve">max_upgrade_count</t>
   </si>
   <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
   </si>
   <si>
     <t xml:space="preserve">train_data_id</t>
@@ -122,274 +331,58 @@
     <t xml:space="preserve">upgrade_type</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
     <t xml:space="preserve">drop_money_max</t>
   </si>
   <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_money_min</t>
   </si>
   <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
+    <t xml:space="preserve">attack_damage</t>
   </si>
   <si>
     <t xml:space="preserve">NonTrainUpgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
     <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0;0;0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
     <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
   </si>
 </sst>
 </file>
@@ -397,7 +390,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -428,6 +421,11 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -438,7 +436,7 @@
     </fill>
   </fills>
   <borders count="9">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -451,8 +449,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -465,8 +466,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -479,8 +483,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -493,8 +500,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -507,8 +517,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -521,8 +534,11 @@
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -535,8 +551,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -549,8 +568,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -563,10 +585,55 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -624,65 +691,87 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
       <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
         <bottom style="thin">
-          <color rgb="FF6182D6"/>
+          <color rgb="FF8FABDB"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
-    </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
-    </tableStyle>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0"/>
   </tableStyles>
 </styleSheet>
 </file>
@@ -997,46 +1086,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1044,43 +1133,43 @@
         <v>10001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="E2" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
+      <c r="G2" s="4">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <v>100</v>
       </c>
       <c r="I2" s="4">
-        <v>10</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="J2" s="4">
+        <v>40</v>
       </c>
       <c r="K2" s="4">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="L2" s="4">
         <v>2</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1088,43 +1177,43 @@
         <v>10002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="4">
         <v>5</v>
       </c>
-      <c r="F3" s="4">
-        <v>8</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.5</v>
-      </c>
       <c r="H3" s="4">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I3" s="4">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="J3" s="4">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="K3" s="4">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="L3" s="4">
         <v>1.5</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1132,43 +1221,43 @@
         <v>10003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="4">
         <v>3</v>
       </c>
       <c r="H4" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I4" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J4" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K4" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1270,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="4" customWidth="1"/>
@@ -1191,31 +1280,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1223,10 +1312,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4">
         <v>1</v>
@@ -1240,10 +1329,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
@@ -1257,10 +1346,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -1274,10 +1363,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -1292,10 +1381,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1309,10 +1398,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -1345,31 +1434,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="J1" s="5"/>
     </row>
@@ -1378,10 +1467,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D2" s="4">
         <v>100</v>
@@ -1393,10 +1482,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1404,10 +1493,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4">
         <v>200</v>
@@ -1419,10 +1508,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1430,7 +1519,7 @@
         <v>110003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>117</v>
@@ -1445,10 +1534,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1456,10 +1545,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4">
         <v>300</v>
@@ -1471,7 +1560,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1479,10 +1568,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D6" s="4">
         <v>500</v>
@@ -1494,7 +1583,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1516,25 +1605,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1542,10 +1631,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="D2" s="4">
         <v>100</v>
@@ -1554,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1581,40 +1670,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -1622,7 +1711,7 @@
         <v>40001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>114</v>
@@ -1634,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="H2" s="4">
         <v>5</v>
@@ -1649,7 +1738,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1657,10 +1746,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D3" s="4">
         <v>100</v>
@@ -1669,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="H3" s="4">
         <v>5</v>
@@ -1684,7 +1773,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -1720,43 +1809,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -1764,10 +1853,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="D2" s="4">
         <v>100</v>
@@ -1776,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="H2" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" s="4">
         <v>10</v>
@@ -1794,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1802,10 +1891,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4">
         <v>100</v>
@@ -1814,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="H3" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" s="4">
         <v>3</v>
@@ -1832,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1840,10 +1929,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" s="4">
         <v>100</v>
@@ -1852,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="H4" s="4">
         <v>10</v>
@@ -1870,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1878,10 +1967,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4">
         <v>100</v>
@@ -1890,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4">
         <v>15</v>
@@ -1902,13 +1991,13 @@
         <v>1</v>
       </c>
       <c r="K5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4">
         <v>0</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1916,10 +2005,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4">
         <v>100</v>
@@ -1928,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="H6" s="4">
         <v>10</v>
@@ -1946,7 +2035,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1954,10 +2043,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D7" s="4">
         <v>100</v>
@@ -1966,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H7" s="4">
         <v>10</v>
@@ -1984,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1992,10 +2081,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" s="4">
         <v>100</v>
@@ -2004,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="H8" s="4">
         <v>10</v>
@@ -2022,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2039,10 +2128,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="D12" s="4">
         <v>150</v>
@@ -2051,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="H12" s="4">
         <v>5</v>
@@ -2069,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2119,19 +2208,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2139,16 +2228,16 @@
         <v>50001</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4">
         <v>180</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2173,19 +2262,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -2385,19 +2474,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2596,7 +2685,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="4" customWidth="1"/>
@@ -2604,19 +2693,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2648,31 +2737,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2680,10 +2769,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G2" s="4">
         <v>5</v>
@@ -2697,10 +2786,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4">
         <v>10</v>
@@ -2714,10 +2803,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G4" s="4">
         <v>25</v>
@@ -2731,10 +2820,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
@@ -2745,10 +2834,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G6" s="4">
         <v>5</v>
@@ -2759,10 +2848,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G7" s="4">
         <v>10</v>
@@ -2773,10 +2862,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G8" s="4">
         <v>15</v>
@@ -2790,10 +2879,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G9" s="4">
         <v>20</v>
@@ -2807,10 +2896,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G10" s="4">
         <v>40</v>
@@ -2824,10 +2913,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G11" s="4">
         <v>50</v>
@@ -2838,10 +2927,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G12" s="4">
         <v>150</v>
@@ -2852,10 +2941,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G13" s="4">
         <v>250</v>
@@ -2866,10 +2955,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" s="4">
         <v>3</v>
@@ -2883,10 +2972,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -2900,10 +2989,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="4">
         <v>7</v>
@@ -2917,10 +3006,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="F17" s="4">
         <v>1</v>
@@ -2934,10 +3023,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
@@ -2951,10 +3040,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="F19" s="4">
         <v>1</v>
@@ -2968,10 +3057,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G20" s="4">
         <v>50</v>
@@ -2982,10 +3071,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G21" s="4">
         <v>150</v>
@@ -2996,10 +3085,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G22" s="4">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
-    <sheet name="Train_Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Range_Train_Data" sheetId="3" r:id="rId6"/>
-    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId7"/>
-    <sheet name="Stage_Data" sheetId="5" r:id="rId8"/>
-    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId9"/>
-    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId10"/>
-    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId11"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId12"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
-    <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Range_Train_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage_Data" sheetId="5" r:id="rId5"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
+  <calcPr/>
+  <extLst>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="149">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -49,9 +55,6 @@
     <t xml:space="preserve">10</t>
   </si>
   <si>
-    <t xml:space="preserve">1;</t>
-  </si>
-  <si>
     <t xml:space="preserve">뱀이다</t>
   </si>
   <si>
@@ -142,9 +145,6 @@
     <t xml:space="preserve">Shark</t>
   </si>
   <si>
-    <t xml:space="preserve">10016;</t>
-  </si>
-  <si>
     <t xml:space="preserve">난쟁이다</t>
   </si>
   <si>
@@ -470,6 +470,14 @@
   </si>
   <si>
     <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -477,7 +485,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -487,31 +495,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -523,22 +514,12 @@
     </fill>
   </fills>
   <borders count="9">
-    <border diagonalUp="1" diagonalDown="1">
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -550,12 +531,8 @@
       <top style="medium">
         <color rgb="FF5B9BD5"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -564,15 +541,9 @@
       <right style="medium">
         <color rgb="FF5B9BD5"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -584,12 +555,8 @@
       <top style="medium">
         <color rgb="FFFFC000"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -598,15 +565,9 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -615,15 +576,11 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -635,12 +592,8 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -649,15 +602,9 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -666,65 +613,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -779,19 +680,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -800,88 +696,21 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
-      <tableStyleElement type="totalRow" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="1">
+      <tableStyleElement type="headerRow"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -928,7 +757,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="20"/>
+        <a:latin typeface="Calibri Light" panose="20000000000000000000"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -980,7 +809,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="20"/>
+        <a:latin typeface="Calibri" panose="20000000000000000000"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1170,6 +999,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1177,7 +1008,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="5" customWidth="1"/>
@@ -1191,62 +1022,62 @@
     <col min="11" max="11" width="15.92578125" style="5" customWidth="1"/>
     <col min="12" max="12" width="11.78515625" style="5" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="13.37890625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>10001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" s="5">
         <v>10</v>
@@ -1276,21 +1107,21 @@
         <v>2</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A3" s="3">
         <v>10002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3">
         <v>35</v>
@@ -1320,21 +1151,21 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A4" s="3">
         <v>10003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1364,21 +1195,21 @@
         <v>6</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A5" s="3">
         <v>10004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3">
         <v>60</v>
@@ -1408,21 +1239,21 @@
         <v>2</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A6" s="3">
         <v>10005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3">
         <v>40</v>
@@ -1452,21 +1283,21 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A7" s="5">
         <v>10006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3">
         <v>200</v>
@@ -1496,21 +1327,21 @@
         <v>2</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A8" s="3">
         <v>10007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3">
         <v>40</v>
@@ -1540,18 +1371,18 @@
         <v>3</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A9" s="3">
         <v>10008</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>4</v>
@@ -1563,7 +1394,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="5">
-        <v>6.4000000000000004</v>
+        <v>6.4</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
@@ -1584,21 +1415,21 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A10" s="3">
         <v>10009</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D10" s="3">
         <v>100</v>
@@ -1607,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="5">
-        <v>4.2999999999999998</v>
+        <v>4.3</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
@@ -1628,18 +1459,18 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A11" s="3">
         <v>10010</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>5</v>
@@ -1672,21 +1503,21 @@
         <v>2</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A12" s="5">
         <v>10011</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
         <v>30</v>
@@ -1716,21 +1547,21 @@
         <v>2</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A13" s="3">
         <v>10012</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3">
         <v>100</v>
@@ -1760,21 +1591,21 @@
         <v>3</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A14" s="3">
         <v>10013</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3">
         <v>250</v>
@@ -1804,21 +1635,21 @@
         <v>2</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A15" s="3">
         <v>10014</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="3">
         <v>60</v>
@@ -1848,21 +1679,21 @@
         <v>2</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A16" s="3">
         <v>10015</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D16" s="3">
         <v>60</v>
@@ -1892,21 +1723,21 @@
         <v>5</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A17" s="5">
         <v>10016</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D17" s="3">
         <v>300</v>
@@ -1936,13 +1767,14 @@
         <v>2</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1952,7 +1784,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="5" customWidth="1"/>
@@ -1960,44 +1792,44 @@
     <col min="9" max="9" width="19.78515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>100001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -2006,15 +1838,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="5">
         <v>100001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -2023,15 +1855,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="5">
         <v>100001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -2040,15 +1872,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="5">
         <v>100002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -2058,15 +1890,15 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="5">
         <v>100002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -2075,15 +1907,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="5">
         <v>100002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -2093,6 +1925,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2102,9 +1935,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
-    <col min="2" max="2" width="27.5859375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="5" customWidth="1"/>
     <col min="4" max="4" width="12.92578125" style="5" customWidth="1"/>
     <col min="5" max="5" width="15.140625" style="5" customWidth="1"/>
@@ -2114,45 +1947,45 @@
     <col min="10" max="10" width="12.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>110001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2164,18 +1997,18 @@
         <v>100</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="5">
         <v>110002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>0</v>
@@ -2184,27 +2017,27 @@
         <v>200</v>
       </c>
       <c r="E3" s="5">
-        <v>-0.10000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" s="5">
         <v>100</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="5">
         <v>110003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -2216,21 +2049,21 @@
         <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="5">
         <v>110004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <v>300</v>
@@ -2242,18 +2075,18 @@
         <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="5">
         <v>110005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5">
         <v>500</v>
@@ -2265,10 +2098,11 @@
         <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2278,45 +2112,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="5" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>20001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2325,10 +2159,11 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2338,7 +2173,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="5" customWidth="1"/>
@@ -2350,53 +2185,53 @@
     <col min="13" max="13" width="15.640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16.75">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="12">
         <v>40001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2405,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="5">
         <v>5</v>
@@ -2420,15 +2255,15 @@
         <v>4</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A3" s="13">
         <v>40002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>1</v>
@@ -2440,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="5">
         <v>5</v>
@@ -2452,22 +2287,23 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A4" s="13"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A5" s="13"/>
     </row>
-    <row r="6" spans="1:1" ht="16.75">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A6" s="14"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2477,7 +2313,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="5" customWidth="1"/>
@@ -2489,56 +2325,56 @@
     <col min="12" max="13" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="M1" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16.75">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>30001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2547,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="5">
         <v>5</v>
@@ -2565,18 +2401,18 @@
         <v>0</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A3" s="8">
         <v>30002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -2585,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H3" s="5">
         <v>5</v>
@@ -2597,24 +2433,24 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A4" s="8">
         <v>30003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" s="5">
         <v>100</v>
@@ -2623,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="5">
         <v>10</v>
@@ -2641,18 +2477,18 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A5" s="8">
         <v>30004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D5" s="5">
         <v>100</v>
@@ -2661,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="5">
         <v>15</v>
@@ -2679,18 +2515,18 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A6" s="8">
         <v>30005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D6" s="5">
         <v>100</v>
@@ -2699,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H6" s="5">
         <v>10</v>
@@ -2717,15 +2553,15 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A7" s="8">
         <v>30006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>2</v>
@@ -2737,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5">
         <v>10</v>
@@ -2755,18 +2591,18 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A8" s="8">
         <v>30007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
@@ -2775,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="5">
         <v>10</v>
@@ -2793,27 +2629,27 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A9" s="8"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A10" s="8"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A11" s="8"/>
     </row>
-    <row r="12" spans="1:13" ht="16.75">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A12" s="9">
         <v>31001</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="5">
         <v>150</v>
@@ -2822,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H12" s="5">
         <v>5</v>
@@ -2834,43 +2670,44 @@
         <v>2</v>
       </c>
       <c r="K12" s="5">
-        <v>0.29999999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="L12" s="5">
         <v>0</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A13" s="10"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A14" s="10"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A15" s="10"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="10"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="10"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="10"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="10"/>
     </row>
-    <row r="21" spans="1:1" ht="16.75">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A21" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2880,58 +2717,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
-    <col min="4" max="4" width="23.91796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6171875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.92578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.92578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>50001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" s="5">
         <v>180</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>8</v>
+      <c r="D2" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2939,7 +2777,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="5" customWidth="1"/>
@@ -2949,24 +2787,24 @@
     <col min="7" max="7" width="13.92578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.75">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="12">
         <v>60001</v>
       </c>
@@ -2980,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="13">
         <v>60002</v>
       </c>
@@ -2994,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="13">
         <v>60003</v>
       </c>
@@ -3008,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="13">
         <v>60004</v>
       </c>
@@ -3022,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="13">
         <v>60005</v>
       </c>
@@ -3036,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="13">
         <v>60006</v>
       </c>
@@ -3050,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="13">
         <v>60007</v>
       </c>
@@ -3064,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="13">
         <v>60008</v>
       </c>
@@ -3078,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="13">
         <v>60009</v>
       </c>
@@ -3092,43 +2930,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="13"/>
       <c r="D11" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="13"/>
       <c r="D12" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="13"/>
       <c r="D13" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="13"/>
       <c r="D14" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="13"/>
       <c r="D15" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="14"/>
       <c r="D16" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A17" s="4">
         <v>61001</v>
       </c>
@@ -3143,6 +2981,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3152,7 +2991,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="5" customWidth="1"/>
@@ -3161,24 +3000,24 @@
     <col min="5" max="5" width="13.78515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="12">
         <v>70001</v>
       </c>
@@ -3195,7 +3034,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="13">
         <v>70002</v>
       </c>
@@ -3212,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="13">
         <v>70003</v>
       </c>
@@ -3229,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="13">
         <v>70004</v>
       </c>
@@ -3246,7 +3085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="13">
         <v>70005</v>
       </c>
@@ -3263,7 +3102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="13">
         <v>70006</v>
       </c>
@@ -3280,7 +3119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="13">
         <v>70007</v>
       </c>
@@ -3297,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="13">
         <v>70008</v>
       </c>
@@ -3314,7 +3153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="13">
         <v>70009</v>
       </c>
@@ -3331,40 +3170,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="13"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="13"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="13"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="13"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="13"/>
     </row>
-    <row r="16" spans="1:1" ht="18">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="15"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="15"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="15"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="15"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A21" s="15"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -3374,35 +3214,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="5" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3412,7 +3253,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="5" customWidth="1"/>
@@ -3424,44 +3265,44 @@
     <col min="9" max="9" width="16" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="5">
         <v>90001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G2" s="5">
         <v>5</v>
@@ -3470,15 +3311,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="5">
         <v>90001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -3487,15 +3328,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="5">
         <v>90001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G4" s="5">
         <v>25</v>
@@ -3504,150 +3345,150 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="5">
         <v>90002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="5">
         <v>90002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="5">
         <v>90002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G7" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A8" s="5">
         <v>90003</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G8" s="5">
         <v>15</v>
       </c>
       <c r="I8" s="5">
-        <v>0.14999999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A9" s="5">
         <v>90003</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G9" s="5">
         <v>20</v>
       </c>
       <c r="I9" s="5">
-        <v>0.14999999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A10" s="5">
         <v>90003</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G10" s="5">
         <v>40</v>
       </c>
       <c r="I10" s="5">
-        <v>0.20000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A11" s="4">
         <v>90004</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G11" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A12" s="5">
         <v>90004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G12" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A13" s="5">
         <v>90004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G13" s="5">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A14" s="4">
         <v>90005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G14" s="5">
         <v>3</v>
@@ -3656,15 +3497,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A15" s="5">
         <v>90005</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G15" s="5">
         <v>5</v>
@@ -3673,15 +3514,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A16" s="5">
         <v>90005</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G16" s="5">
         <v>7</v>
@@ -3690,15 +3531,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A17" s="4">
         <v>90006</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -3707,15 +3548,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A18" s="5">
         <v>90006</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -3724,15 +3565,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A19" s="6">
         <v>90006</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F19" s="5">
         <v>1</v>
@@ -3741,49 +3582,50 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A20" s="6">
         <v>90007</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G20" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A21" s="6">
         <v>90007</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G21" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A22" s="6">
         <v>90007</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G22" s="5">
         <v>350</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,35 +1,278 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="4"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Range_Train_Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId4"/>
-    <sheet name="Stage_Data" sheetId="5" r:id="rId5"/>
-    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
-    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
-    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
-    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId5"/>
+    <sheet name="Range_Train_Data" sheetId="3" r:id="rId6"/>
+    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId7"/>
+    <sheet name="Stage_Data" sheetId="5" r:id="rId8"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId9"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId10"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId11"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId12"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="149">
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -40,444 +283,193 @@
     <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
+    <t xml:space="preserve">Shark</t>
   </si>
   <si>
     <t xml:space="preserve">미노타우로스다</t>
   </si>
   <si>
-    <t xml:space="preserve">Shark</t>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">난쟁이다</t>
   </si>
   <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
     <t xml:space="preserve">화염 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">냉기 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
   </si>
   <si>
     <t xml:space="preserve">Spider</t>
   </si>
   <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
   </si>
   <si>
     <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">spawn_monsters_level</t>
   </si>
   <si>
-    <t xml:space="preserve">stage_inspection_time</t>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
   </si>
   <si>
     <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -485,7 +477,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -495,14 +487,31 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -514,12 +523,22 @@
     </fill>
   </fills>
   <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border diagonalUp="1" diagonalDown="1">
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -531,8 +550,12 @@
       <top style="medium">
         <color rgb="FF5B9BD5"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -541,9 +564,15 @@
       <right style="medium">
         <color rgb="FF5B9BD5"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -555,8 +584,12 @@
       <top style="medium">
         <color rgb="FFFFC000"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -565,9 +598,15 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -576,11 +615,15 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top/>
+      <top>
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
-      <diagonal/>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -592,8 +635,12 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -602,9 +649,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -613,15 +666,61 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top>
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -680,14 +779,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -696,21 +795,77 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="1">
-      <tableStyleElement type="headerRow"/>
-    </tableStyle>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1"/>
   </tableStyles>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -757,7 +912,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="20000000000000000000"/>
+        <a:latin typeface="Calibri Light" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -809,7 +964,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="20000000000000000000"/>
+        <a:latin typeface="Calibri" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -999,8 +1154,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1008,7 +1161,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="5" customWidth="1"/>
@@ -1025,59 +1178,59 @@
     <col min="14" max="14" width="13.35546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:14">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="5">
         <v>10001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="D2" s="5">
         <v>10</v>
@@ -1089,16 +1242,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I2" s="5">
         <v>10</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K2" s="5">
         <v>10</v>
@@ -1107,21 +1260,21 @@
         <v>2</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>10002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D3" s="3">
         <v>35</v>
@@ -1151,21 +1304,21 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>10003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1195,21 +1348,21 @@
         <v>6</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>10004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D5" s="3">
         <v>60</v>
@@ -1239,21 +1392,21 @@
         <v>2</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>10005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="D6" s="3">
         <v>40</v>
@@ -1283,21 +1436,21 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="5">
         <v>10006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="D7" s="3">
         <v>200</v>
@@ -1327,21 +1480,21 @@
         <v>2</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>10007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
         <v>40</v>
@@ -1371,21 +1524,21 @@
         <v>3</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>10008</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
         <v>70</v>
@@ -1394,7 +1547,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="5">
-        <v>6.4</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
@@ -1415,21 +1568,21 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>10009</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="D10" s="3">
         <v>100</v>
@@ -1438,7 +1591,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="5">
-        <v>4.3</v>
+        <v>4.2999999999999998</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
@@ -1459,21 +1612,21 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>10010</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>150</v>
@@ -1503,21 +1656,21 @@
         <v>2</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5">
         <v>10011</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3">
         <v>30</v>
@@ -1547,21 +1700,21 @@
         <v>2</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>10012</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3">
         <v>100</v>
@@ -1591,21 +1744,21 @@
         <v>3</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>10013</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3">
         <v>250</v>
@@ -1635,21 +1788,21 @@
         <v>2</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>10014</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3">
         <v>60</v>
@@ -1679,21 +1832,21 @@
         <v>2</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>10015</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>60</v>
@@ -1723,21 +1876,21 @@
         <v>5</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.55">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="5">
         <v>10016</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D17" s="3">
         <v>300</v>
@@ -1767,14 +1920,13 @@
         <v>2</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1784,7 +1936,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="5" customWidth="1"/>
@@ -1792,44 +1944,44 @@
     <col min="9" max="9" width="19.78515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>100001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -1838,15 +1990,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>100001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -1855,15 +2007,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>100001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -1872,15 +2024,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9">
       <c r="A5" s="5">
         <v>100002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -1890,15 +2042,15 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>100002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -1907,15 +2059,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>100002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -1925,7 +2077,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -1935,7 +2086,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="5" customWidth="1"/>
@@ -1947,45 +2098,45 @@
     <col min="10" max="10" width="12.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9">
       <c r="A2" s="5">
         <v>110001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -1997,47 +2148,47 @@
         <v>100</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="5">
         <v>110002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D3" s="5">
         <v>200</v>
       </c>
       <c r="E3" s="5">
-        <v>-0.1</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="F3" s="5">
         <v>100</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="5">
         <v>110003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -2049,21 +2200,21 @@
         <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="5">
         <v>110004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="D5" s="5">
         <v>300</v>
@@ -2075,10 +2226,10 @@
         <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="5">
         <v>110005</v>
       </c>
@@ -2086,7 +2237,7 @@
         <v>144</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="D6" s="5">
         <v>500</v>
@@ -2098,11 +2249,10 @@
         <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2112,45 +2262,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="5" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="5">
         <v>20001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2159,11 +2309,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2173,7 +2322,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="5" customWidth="1"/>
@@ -2185,53 +2334,53 @@
     <col min="13" max="13" width="15.640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.75">
       <c r="A2" s="12">
         <v>40001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2240,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="H2" s="5">
         <v>5</v>
@@ -2255,18 +2404,18 @@
         <v>4</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="13">
         <v>40002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -2275,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="H3" s="5">
         <v>5</v>
@@ -2287,23 +2436,22 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="13"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:1">
       <c r="A5" s="13"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:1" ht="16.75">
       <c r="A6" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2313,7 +2461,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="5" customWidth="1"/>
@@ -2325,56 +2473,56 @@
     <col min="12" max="13" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.75">
       <c r="A2" s="7">
         <v>30001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2383,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="H2" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I2" s="5">
         <v>10</v>
@@ -2401,18 +2549,18 @@
         <v>0</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="8">
         <v>30002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -2421,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
@@ -2433,24 +2581,24 @@
         <v>1</v>
       </c>
       <c r="K3" s="5">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="5">
         <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="8">
         <v>30003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D4" s="5">
         <v>100</v>
@@ -2459,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="H4" s="5">
         <v>10</v>
@@ -2477,18 +2625,18 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="8">
         <v>30004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D5" s="5">
         <v>100</v>
@@ -2497,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H5" s="5">
         <v>15</v>
@@ -2515,18 +2663,18 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="8">
         <v>30005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" s="5">
         <v>100</v>
@@ -2535,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H6" s="5">
         <v>10</v>
@@ -2553,18 +2701,18 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="8">
         <v>30006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="D7" s="5">
         <v>100</v>
@@ -2573,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5">
         <v>10</v>
@@ -2591,18 +2739,18 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="8">
         <v>30007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
@@ -2611,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H8" s="5">
         <v>10</v>
@@ -2629,27 +2777,27 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="8"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:1">
       <c r="A10" s="8"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:1">
       <c r="A11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:13" ht="16.75">
       <c r="A12" s="9">
         <v>31001</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D12" s="5">
         <v>150</v>
@@ -2658,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H12" s="5">
         <v>5</v>
@@ -2670,44 +2818,43 @@
         <v>2</v>
       </c>
       <c r="K12" s="5">
-        <v>0.3</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="L12" s="5">
         <v>0</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" s="10"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:1">
       <c r="A14" s="10"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:1">
       <c r="A15" s="10"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:1">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:1">
       <c r="A17" s="10"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:1">
       <c r="A18" s="10"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:1">
       <c r="A19" s="10"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:1">
       <c r="A20" s="10"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:1" ht="16.75">
       <c r="A21" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2717,7 +2864,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
@@ -2726,50 +2873,49 @@
     <col min="6" max="6" width="19.640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="5">
         <v>50001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C2" s="5">
         <v>180</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -2777,7 +2923,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="12" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="5" customWidth="1"/>
@@ -2787,24 +2933,24 @@
     <col min="7" max="7" width="13.92578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="12">
         <v>60001</v>
       </c>
@@ -2818,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:4">
       <c r="A3" s="13">
         <v>60002</v>
       </c>
@@ -2832,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:4">
       <c r="A4" s="13">
         <v>60003</v>
       </c>
@@ -2846,7 +2992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:4">
       <c r="A5" s="13">
         <v>60004</v>
       </c>
@@ -2860,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:4">
       <c r="A6" s="13">
         <v>60005</v>
       </c>
@@ -2874,7 +3020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:4">
       <c r="A7" s="13">
         <v>60006</v>
       </c>
@@ -2888,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:4">
       <c r="A8" s="13">
         <v>60007</v>
       </c>
@@ -2902,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:4">
       <c r="A9" s="13">
         <v>60008</v>
       </c>
@@ -2916,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:4">
       <c r="A10" s="13">
         <v>60009</v>
       </c>
@@ -2930,43 +3076,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:4">
       <c r="A11" s="13"/>
       <c r="D11" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:4">
       <c r="A12" s="13"/>
       <c r="D12" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:4">
       <c r="A13" s="13"/>
       <c r="D13" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:4">
       <c r="A14" s="13"/>
       <c r="D14" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:4">
       <c r="A15" s="13"/>
       <c r="D15" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:4">
       <c r="A16" s="14"/>
       <c r="D16" s="17">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:5">
       <c r="A17" s="4">
         <v>61001</v>
       </c>
@@ -2981,7 +3127,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2991,7 +3136,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="5" customWidth="1"/>
@@ -3000,24 +3145,24 @@
     <col min="5" max="5" width="13.78515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="12">
         <v>70001</v>
       </c>
@@ -3034,7 +3179,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:5">
       <c r="A3" s="13">
         <v>70002</v>
       </c>
@@ -3051,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:5">
       <c r="A4" s="13">
         <v>70003</v>
       </c>
@@ -3068,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:5">
       <c r="A5" s="13">
         <v>70004</v>
       </c>
@@ -3085,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:5">
       <c r="A6" s="13">
         <v>70005</v>
       </c>
@@ -3102,7 +3247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:5">
       <c r="A7" s="13">
         <v>70006</v>
       </c>
@@ -3119,7 +3264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:5">
       <c r="A8" s="13">
         <v>70007</v>
       </c>
@@ -3136,7 +3281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:5">
       <c r="A9" s="13">
         <v>70008</v>
       </c>
@@ -3153,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:5">
       <c r="A10" s="13">
         <v>70009</v>
       </c>
@@ -3170,41 +3315,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:1">
       <c r="A11" s="13"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:1">
       <c r="A12" s="13"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:1">
       <c r="A13" s="13"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:1">
       <c r="A14" s="13"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:1">
       <c r="A15" s="13"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:1">
       <c r="A16" s="14"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:1">
       <c r="A17" s="15"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:1">
       <c r="A18" s="15"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:1">
       <c r="A19" s="15"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:1">
       <c r="A20" s="15"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:1">
       <c r="A21" s="15"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -3214,36 +3358,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="5" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="5">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3253,7 +3396,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="5" customWidth="1"/>
@@ -3265,44 +3408,44 @@
     <col min="9" max="9" width="16" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="5">
         <v>90001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G2" s="5">
         <v>5</v>
@@ -3311,15 +3454,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9">
       <c r="A3" s="5">
         <v>90001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -3328,15 +3471,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9">
       <c r="A4" s="5">
         <v>90001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G4" s="5">
         <v>25</v>
@@ -3345,150 +3488,150 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>90002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>90002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>90002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G7" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:9">
       <c r="A8" s="5">
         <v>90003</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G8" s="5">
         <v>15</v>
       </c>
       <c r="I8" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.14999999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="5">
         <v>90003</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G9" s="5">
         <v>20</v>
       </c>
       <c r="I9" s="5">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.14999999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="5">
         <v>90003</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G10" s="5">
         <v>40</v>
       </c>
       <c r="I10" s="5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.20000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="4">
         <v>90004</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G11" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>90004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G12" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>90004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G13" s="5">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:8">
       <c r="A14" s="4">
         <v>90005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G14" s="5">
         <v>3</v>
@@ -3497,15 +3640,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:8">
       <c r="A15" s="5">
         <v>90005</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G15" s="5">
         <v>5</v>
@@ -3514,15 +3657,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:8">
       <c r="A16" s="5">
         <v>90005</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G16" s="5">
         <v>7</v>
@@ -3531,15 +3674,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:7">
       <c r="A17" s="4">
         <v>90006</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -3548,15 +3691,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>90006</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -3565,15 +3708,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>90006</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F19" s="5">
         <v>1</v>
@@ -3582,50 +3725,49 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>90007</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G20" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>90007</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G21" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>90007</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="G22" s="5">
         <v>350</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="3"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -23,27 +23,231 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="152">
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
   <si>
     <t xml:space="preserve">need_money</t>
   </si>
   <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">Minotaur</t>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">GoblinSpear</t>
@@ -52,424 +256,229 @@
     <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">move_speed</t>
   </si>
   <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
     <t xml:space="preserve">폭발 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
+    <t xml:space="preserve">Hammershark</t>
   </si>
   <si>
     <t xml:space="preserve">attack_type</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
   </si>
 </sst>
 </file>
@@ -1180,46 +1189,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="H1" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1227,10 +1236,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D2" s="5">
         <v>10</v>
@@ -1242,16 +1251,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" s="5">
         <v>10</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K2" s="5">
         <v>10</v>
@@ -1260,10 +1269,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1271,10 +1280,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D3" s="3">
         <v>35</v>
@@ -1304,10 +1313,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1315,10 +1324,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="D4" s="3">
         <v>50</v>
@@ -1348,10 +1357,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1359,10 +1368,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D5" s="3">
         <v>60</v>
@@ -1392,10 +1401,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1403,10 +1412,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D6" s="3">
         <v>40</v>
@@ -1436,10 +1445,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1447,10 +1456,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D7" s="3">
         <v>200</v>
@@ -1480,10 +1489,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1491,10 +1500,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3">
         <v>40</v>
@@ -1524,10 +1533,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1535,10 +1544,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3">
         <v>70</v>
@@ -1568,10 +1577,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1579,10 +1588,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3">
         <v>100</v>
@@ -1612,10 +1621,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1623,10 +1632,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D11" s="3">
         <v>150</v>
@@ -1656,10 +1665,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1667,10 +1676,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3">
         <v>30</v>
@@ -1700,10 +1709,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1711,10 +1720,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3">
         <v>100</v>
@@ -1744,10 +1753,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1755,10 +1764,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3">
         <v>250</v>
@@ -1788,10 +1797,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1799,10 +1808,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3">
         <v>60</v>
@@ -1832,10 +1841,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1843,10 +1852,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3">
         <v>60</v>
@@ -1876,10 +1885,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1887,10 +1896,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="D17" s="3">
         <v>300</v>
@@ -1920,10 +1929,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="N17" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1946,31 +1955,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1978,10 +1987,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
@@ -1995,10 +2004,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -2012,10 +2021,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F4" s="5">
         <v>1</v>
@@ -2029,10 +2038,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F5" s="5">
         <v>1</v>
@@ -2047,10 +2056,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
@@ -2064,10 +2073,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="F7" s="5">
         <v>1</v>
@@ -2100,31 +2109,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="J1" s="6"/>
     </row>
@@ -2133,10 +2142,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2148,10 +2157,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2159,10 +2168,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D3" s="5">
         <v>200</v>
@@ -2174,10 +2183,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2185,10 +2194,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -2200,10 +2209,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2211,10 +2220,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D5" s="5">
         <v>300</v>
@@ -2226,7 +2235,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2234,10 +2243,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5">
         <v>500</v>
@@ -2249,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2271,25 +2280,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2297,10 +2306,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2309,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2336,40 +2345,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -2377,10 +2386,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2389,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H2" s="5">
         <v>5</v>
@@ -2404,7 +2413,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2412,10 +2421,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -2424,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="H3" s="5">
         <v>5</v>
@@ -2439,7 +2448,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2475,43 +2484,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2519,10 +2528,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5">
         <v>100</v>
@@ -2531,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H2" s="5">
         <v>10</v>
@@ -2549,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2560,7 +2569,7 @@
         <v>105</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D3" s="5">
         <v>100</v>
@@ -2569,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H3" s="5">
         <v>10</v>
@@ -2587,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2595,10 +2604,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="D4" s="5">
         <v>100</v>
@@ -2607,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="H4" s="5">
         <v>10</v>
@@ -2625,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2633,10 +2642,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5">
         <v>100</v>
@@ -2645,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="H5" s="5">
         <v>15</v>
@@ -2663,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2671,10 +2680,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D6" s="5">
         <v>100</v>
@@ -2683,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H6" s="5">
         <v>10</v>
@@ -2701,7 +2710,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2709,10 +2718,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D7" s="5">
         <v>100</v>
@@ -2721,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5">
         <v>10</v>
@@ -2739,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2747,10 +2756,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
@@ -2759,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="H8" s="5">
         <v>10</v>
@@ -2777,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2794,10 +2803,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5">
         <v>150</v>
@@ -2806,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H12" s="5">
         <v>5</v>
@@ -2824,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -2863,9 +2872,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="5" customWidth="1"/>
     <col min="4" max="4" width="23.92578125" style="2" bestFit="1" customWidth="1"/>
@@ -2875,22 +2885,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2898,19 +2908,59 @@
         <v>50001</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C2" s="5">
         <v>180</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>126</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="0">
+        <v>50002</v>
+      </c>
+      <c r="B3" s="5">
+        <v>180</v>
+      </c>
+      <c r="C3" s="5">
+        <v>180</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="0">
+        <v>50003</v>
+      </c>
+      <c r="B4" s="5">
+        <v>180</v>
+      </c>
+      <c r="C4" s="5">
+        <v>180</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2935,19 +2985,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="C1" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3147,19 +3197,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3366,19 +3416,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3410,31 +3460,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="I1" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3442,10 +3492,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G2" s="5">
         <v>5</v>
@@ -3459,10 +3509,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -3476,10 +3526,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G4" s="5">
         <v>25</v>
@@ -3493,10 +3543,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G5" s="5">
         <v>2</v>
@@ -3507,10 +3557,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G6" s="5">
         <v>5</v>
@@ -3521,10 +3571,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G7" s="5">
         <v>10</v>
@@ -3535,10 +3585,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G8" s="5">
         <v>15</v>
@@ -3552,10 +3602,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G9" s="5">
         <v>20</v>
@@ -3569,10 +3619,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G10" s="5">
         <v>40</v>
@@ -3586,10 +3636,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G11" s="5">
         <v>50</v>
@@ -3600,10 +3650,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G12" s="5">
         <v>150</v>
@@ -3614,10 +3664,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G13" s="5">
         <v>250</v>
@@ -3628,10 +3678,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G14" s="5">
         <v>3</v>
@@ -3645,10 +3695,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G15" s="5">
         <v>5</v>
@@ -3662,10 +3712,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G16" s="5">
         <v>7</v>
@@ -3679,10 +3729,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -3696,10 +3746,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
@@ -3713,10 +3763,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F19" s="5">
         <v>1</v>
@@ -3733,7 +3783,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G20" s="5">
         <v>50</v>
@@ -3747,7 +3797,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G21" s="5">
         <v>150</v>
@@ -3761,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="G22" s="5">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\RedEyes\TrainDefense\Assets\02_Resources\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
     <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="2"/>
   </x:bookViews>
@@ -31,521 +26,521 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="170">
   <x:si>
+    <x:t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weighted_upgrades</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염으로 지속적인 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10001;10002;10003;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExplosionProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CannonTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectrickProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CannonProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0} 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hammershark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 기관총 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stat_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Turtle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해골 병사다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dwarf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;1;1;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거북이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">상어다 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Panda</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난쟁이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spider</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Snake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>놀이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀상어다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skull</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인 기차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도마뱀이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 거인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>180;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gnoll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>icon_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoblinSorcerer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target_count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>upgrade_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NonTrainUpgrade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>monster_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stage_end_time</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>is_main_train</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_monsters</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainUpgrade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉기 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_interval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총으로 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FireTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_exp_max</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_money_min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_exp_min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_money_max</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LaserProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_data_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>upgrade_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target_train_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제일 기본이 되는 기차이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_range</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_delay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>upgrade_value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>획득하는 골드 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>획득하는 경험치 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FireEffectProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0} 증가 공격 범위 {1} 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stage_inspection_time</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0} 증가 범위 {1} 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteNormalTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectrickTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>projectile_prefab_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저로 강하게 지속적인 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0} 증가 공격딜레이 {1} 감소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_monsters_level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뱀이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거미다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판다다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lizard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ranged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해골 왕이당.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thief</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미노타우로스다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>max_hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkullKing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoblinSpear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prefab_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 폭발 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 화염 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 레이저 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 미사일 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 포격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 전기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 저격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 냉기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 주술사다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;1;1;1;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GiantGoblin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 창병이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Minotaur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉기 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>need_money</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MainTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>move_speed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10004;10005;10006;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SniperTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExplosionRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ColdAirProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SniperProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MissileTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>max_upgrade_count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MissileProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LaserTurretTrain</x:t>
+  </x:si>
+  <x:si>
     <x:t>미사일 포탑에 강화 버전이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>ColdAirRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>replace_train_id</x:t>
+  </x:si>
+  <x:si>
     <x:t>레이저 포탑에 강화 버전이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>엘리트 폭발 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 화염 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 미사일 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 레이저 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 전기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 포격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 저격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거미다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판다다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뱀이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>upgrade_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NonTrainUpgrade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>target_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GoblinSorcerer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_money_max</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_exp_min</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LaserProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_delay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>is_main_train</x:t>
-  </x:si>
-  <x:si>
-    <x:t>spawn_monsters</x:t>
-  </x:si>
-  <x:si>
-    <x:t>monster_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainUpgrade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FireTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_exp_max</x:t>
-  </x:si>
-  <x:si>
-    <x:t>upgrade_value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_data_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총으로 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>upgrade_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stage_end_time</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_interval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>target_train_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제일 기본이 되는 기차이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_money_min</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_range</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>난쟁이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Panda</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1;1;1;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Spider</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dwarf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">상어다 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거북이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Turtle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Snake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해골 병사다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀상어다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메인 기차</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도마뱀이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 거인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gnoll</x:t>
-  </x:si>
-  <x:si>
-    <x:t>180;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>icon_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skull</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lizard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ranged</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thief</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해골 왕이당.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미노타우로스다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>max_hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shark</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Melee</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭발 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 냉기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GiantGoblin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 창병이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Minotaur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 주술사다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>need_money</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1;1;1;1;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MainTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>move_speed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GoblinSpear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkullKing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>prefab_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포격 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 기관총 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stat_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0} 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hammershark</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭발 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭발 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ColdAirRangeTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LaserTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>replace_train_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExplosionRangeTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ColdAirProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SniperProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MissileTurretTrain</x:t>
-  </x:si>
-  <x:si>
     <x:t>공격 딜레이 {0}/{1} % 감소</x:t>
   </x:si>
   <x:si>
-    <x:t>max_upgrade_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MissileProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10004;10005;10006;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SniperTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CannonProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염으로 지속적인 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10001;10002;10003;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CannonTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectrickProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weighted_upgrades</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExplosionProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포격 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>spawn_monsters_probability</x:t>
   </x:si>
   <x:si>
     <x:t>10007;10008;10009;10010;</x:t>
   </x:si>
   <x:si>
+    <x:t>미사일로 강한 피해를 준다. 공격속도는 느리다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0} 증가 공격하는 적 수 {1} 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면에 있는 다수의 적들을 전기로 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범위 내에 있는 적들을 밀치고 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격을 발사해 몇 초 후 강한 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>포탑들의 체력이 {0}({1})만큼 증가합니다.</x:t>
   </x:si>
   <x:si>
     <x:t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격을 발사해 몇 초 후 강한 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범위 내에 있는 적들을 밀치고 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0} 증가 공격하는 적 수 {1} 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면에 있는 다수의 적들을 전기로 공격한다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일로 강한 피해를 준다. 공격속도는 느리다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>projectile_prefab_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저로 강하게 지속적인 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stage_inspection_time</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0} 증가 범위 {1} 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>획득하는 골드 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EliteNormalTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0} 증가 공격 범위 {1} 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FireEffectProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0} 증가 공격딜레이 {1} 감소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>spawn_monsters_level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>획득하는 경험치 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectrickTurretTrain</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="11"/>
@@ -576,6 +571,11 @@
       <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
+    <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -586,7 +586,7 @@
     </x:fill>
   </x:fills>
   <x:borders count="12">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color indexed="64"/>
       </x:left>
@@ -599,8 +599,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ff5b9bd5"/>
       </x:left>
@@ -613,8 +616,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ff5b9bd5"/>
       </x:left>
@@ -627,8 +633,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffc000"/>
       </x:left>
@@ -641,8 +650,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffc000"/>
       </x:left>
@@ -655,8 +667,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffc000"/>
       </x:left>
@@ -669,8 +684,11 @@
       <x:bottom style="medium">
         <x:color rgb="ffffc000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color indexed="64"/>
       </x:left>
@@ -683,8 +701,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color indexed="64"/>
       </x:left>
@@ -697,8 +718,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color indexed="64"/>
       </x:left>
@@ -711,8 +735,11 @@
       <x:bottom style="medium">
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffd700"/>
       </x:left>
@@ -725,8 +752,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffd700"/>
       </x:left>
@@ -739,8 +769,11 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="medium">
         <x:color rgb="ffffd700"/>
       </x:left>
@@ -753,10 +786,55 @@
       <x:bottom style="medium">
         <x:color rgb="ffffd700"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -832,14 +910,15 @@
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -922,6 +1001,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -956,6 +1036,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1000,6 +1081,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1043,6 +1125,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1127,6 +1210,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1147,6 +1231,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1177,6 +1262,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1202,6 +1288,457 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffdae3f3"/>
+              <x:bgColor rgb="ffdae3f3"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffdae3f3"/>
+              <x:bgColor rgb="ffdae3f3"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffdae3f3"/>
+              <x:bgColor rgb="ffdae3f3"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffdae3f3"/>
+              <x:bgColor rgb="ffdae3f3"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4472c4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4472c4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4472c4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4472c4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffdae3f3"/>
+          <x:bgColor rgb="ffdae3f3"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8fabdb"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffdae3f3"/>
+          <x:bgColor rgb="ffdae3f3"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8fabdb"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8fabdb"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4472c4"/>
+              <x:bgColor rgb="ff4472c4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4472c4"/>
+              <x:bgColor rgb="ff4472c4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4472c4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4472c4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffdae3f3"/>
+          <x:bgColor rgb="ffdae3f3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffdae3f3"/>
+          <x:bgColor rgb="ffdae3f3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -1230,7 +1767,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office 테마">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1540,46 +2077,46 @@
   <x:sheetData>
     <x:row r="1" spans="1:14">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I1" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J1" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K1" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="M1" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N1" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14">
@@ -1587,10 +2124,10 @@
         <x:v>10001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D2" s="6">
         <x:v>10</x:v>
@@ -1602,16 +2139,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H2" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I2" s="6">
         <x:v>10</x:v>
       </x:c>
       <x:c r="J2" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K2" s="6">
         <x:v>10</x:v>
@@ -1620,10 +2157,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M2" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N2" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:14">
@@ -1631,10 +2168,10 @@
         <x:v>10002</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>80</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="4">
         <x:v>35</x:v>
@@ -1664,10 +2201,10 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="M3" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N3" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:14">
@@ -1675,10 +2212,10 @@
         <x:v>10003</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>50</x:v>
@@ -1708,10 +2245,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="M4" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="N4" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:14">
@@ -1719,10 +2256,10 @@
         <x:v>10004</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="4">
         <x:v>60</x:v>
@@ -1752,10 +2289,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M5" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N5" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:14">
@@ -1763,10 +2300,10 @@
         <x:v>10005</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="4">
         <x:v>40</x:v>
@@ -1796,10 +2333,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M6" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="N6" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:14">
@@ -1807,10 +2344,10 @@
         <x:v>10006</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>200</x:v>
@@ -1840,10 +2377,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M7" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:14">
@@ -1851,10 +2388,10 @@
         <x:v>10007</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D8" s="4">
         <x:v>40</x:v>
@@ -1884,10 +2421,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M8" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N8" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:14">
@@ -1895,10 +2432,10 @@
         <x:v>10008</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D9" s="4">
         <x:v>70</x:v>
@@ -1928,10 +2465,10 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="M9" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:14">
@@ -1939,10 +2476,10 @@
         <x:v>10009</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D10" s="4">
         <x:v>100</x:v>
@@ -1972,10 +2509,10 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="M10" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N10" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:14">
@@ -1983,10 +2520,10 @@
         <x:v>10010</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D11" s="4">
         <x:v>150</x:v>
@@ -2016,10 +2553,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M11" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N11" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:14">
@@ -2027,10 +2564,10 @@
         <x:v>10011</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="4">
         <x:v>30</x:v>
@@ -2060,10 +2597,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M12" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:14">
@@ -2071,10 +2608,10 @@
         <x:v>10012</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D13" s="4">
         <x:v>100</x:v>
@@ -2104,10 +2641,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M13" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:14">
@@ -2115,10 +2652,10 @@
         <x:v>10013</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>97</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D14" s="4">
         <x:v>250</x:v>
@@ -2148,10 +2685,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M14" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N14" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:14">
@@ -2159,10 +2696,10 @@
         <x:v>10014</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D15" s="4">
         <x:v>60</x:v>
@@ -2192,10 +2729,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M15" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N15" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:14">
@@ -2203,10 +2740,10 @@
         <x:v>10015</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D16" s="4">
         <x:v>60</x:v>
@@ -2236,10 +2773,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M16" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="N16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:14">
@@ -2247,10 +2784,10 @@
         <x:v>10016</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D17" s="4">
         <x:v>300</x:v>
@@ -2280,10 +2817,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M17" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:15">
@@ -2291,10 +2828,10 @@
         <x:v>10100</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D22" s="4">
         <x:v>500</x:v>
@@ -2324,13 +2861,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M22" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="N22" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="O22" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2343,7 +2880,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet10"/>
   <x:dimension ref="A1:I7"/>
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="2" max="2" width="15.640625" style="6" customWidth="1"/>
     <x:col min="3" max="3" width="27.5" style="6" customWidth="1"/>
@@ -2353,31 +2890,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:9">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G1" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I1" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
@@ -2385,10 +2922,10 @@
         <x:v>100001</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F2" s="6">
         <x:v>1</x:v>
@@ -2402,10 +2939,10 @@
         <x:v>100001</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F3" s="6">
         <x:v>1</x:v>
@@ -2419,10 +2956,10 @@
         <x:v>100001</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>119</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F4" s="6">
         <x:v>1</x:v>
@@ -2436,16 +2973,16 @@
         <x:v>100002</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F5" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="6">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I5" s="7"/>
     </x:row>
@@ -2454,16 +2991,16 @@
         <x:v>100002</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F6" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="6">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -2471,16 +3008,16 @@
         <x:v>100002</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>99</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>161</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F7" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="6">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2507,31 +3044,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H1" s="7" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I1" s="7" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H1" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="I1" s="7" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="J1" s="7"/>
     </x:row>
@@ -2540,10 +3077,10 @@
         <x:v>110001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>141</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D2" s="6">
         <x:v>100</x:v>
@@ -2555,10 +3092,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H2" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I2" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -2566,10 +3103,10 @@
         <x:v>110002</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>131</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D3" s="6">
         <x:v>200</x:v>
@@ -2581,10 +3118,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -2592,10 +3129,10 @@
         <x:v>110003</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D4" s="6">
         <x:v>50</x:v>
@@ -2607,10 +3144,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H4" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I4" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:8">
@@ -2618,10 +3155,10 @@
         <x:v>110004</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="6">
         <x:v>300</x:v>
@@ -2633,7 +3170,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H5" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
@@ -2641,10 +3178,10 @@
         <x:v>110005</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>168</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="6">
         <x:v>500</x:v>
@@ -2656,7 +3193,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H6" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2678,25 +3215,25 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F1" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -2704,10 +3241,10 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D2" s="6">
         <x:v>100</x:v>
@@ -2716,7 +3253,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2743,40 +3280,40 @@
   <x:sheetData>
     <x:row r="1" spans="1:12">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F1" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I1" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J1" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K1" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L1" s="6" t="s">
-        <x:v>158</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="16.75">
@@ -2784,10 +3321,10 @@
         <x:v>40001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>154</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D2" s="6">
         <x:v>100</x:v>
@@ -2796,7 +3333,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H2" s="6">
         <x:v>5</x:v>
@@ -2811,7 +3348,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L2" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12">
@@ -2819,10 +3356,10 @@
         <x:v>40002</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D3" s="6">
         <x:v>100</x:v>
@@ -2831,7 +3368,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H3" s="6">
         <x:v>5</x:v>
@@ -2846,7 +3383,7 @@
         <x:v>0.10000000000000001</x:v>
       </x:c>
       <x:c r="L3" s="6" t="s">
-        <x:v>127</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
@@ -2855,19 +3392,19 @@
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="14"/>
     </x:row>
-    <x:row r="6" spans="1:2" ht="16.75">
+    <x:row r="6" spans="1:2">
       <x:c r="A6" s="14"/>
       <x:c r="B6"/>
     </x:row>
-    <x:row r="7" spans="1:5" ht="16.75">
+    <x:row r="7" spans="1:11" ht="16.75">
       <x:c r="A7" s="20">
         <x:v>41001</x:v>
       </x:c>
       <x:c r="B7" t="s">
-        <x:v>2</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D7" s="6">
         <x:v>150</x:v>
@@ -2875,22 +3412,46 @@
       <x:c r="E7" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
+      <x:c r="H7" s="6">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="6">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J7" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K7" s="6">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:11">
       <x:c r="A8" s="21">
         <x:v>41002</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>92</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D8" s="6">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E8" s="6" t="b">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="6">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I8" s="6">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J8" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K8" s="6">
+        <x:v>0.10000000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
@@ -2901,7 +3462,7 @@
       <x:c r="A10" s="21"/>
       <x:c r="B10"/>
     </x:row>
-    <x:row r="11" spans="1:2">
+    <x:row r="11" spans="1:2" ht="16.75">
       <x:c r="A11" s="22"/>
       <x:c r="B11"/>
     </x:row>
@@ -2933,43 +3494,43 @@
   <x:sheetData>
     <x:row r="1" spans="1:13">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F1" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I1" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J1" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K1" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L1" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M1" s="6" t="s">
-        <x:v>158</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13" ht="16.75">
@@ -2977,10 +3538,10 @@
         <x:v>30001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D2" s="6">
         <x:v>100</x:v>
@@ -2989,7 +3550,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" s="7" t="s">
-        <x:v>123</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H2" s="6">
         <x:v>10</x:v>
@@ -3007,7 +3568,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="7" t="s">
-        <x:v>138</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:13">
@@ -3015,10 +3576,10 @@
         <x:v>30002</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D3" s="6">
         <x:v>100</x:v>
@@ -3027,7 +3588,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H3" s="6">
         <x:v>10</x:v>
@@ -3045,7 +3606,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="6" t="s">
-        <x:v>165</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13">
@@ -3053,10 +3614,10 @@
         <x:v>30003</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D4" s="6">
         <x:v>100</x:v>
@@ -3065,7 +3626,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H4" s="6">
         <x:v>10</x:v>
@@ -3083,7 +3644,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M4" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:13">
@@ -3091,10 +3652,10 @@
         <x:v>30004</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>159</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="6">
         <x:v>100</x:v>
@@ -3103,7 +3664,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H5" s="6">
         <x:v>15</x:v>
@@ -3121,7 +3682,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:13">
@@ -3129,10 +3690,10 @@
         <x:v>30005</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D6" s="6">
         <x:v>100</x:v>
@@ -3141,7 +3702,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>169</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H6" s="6">
         <x:v>10</x:v>
@@ -3159,7 +3720,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M6" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:13">
@@ -3167,10 +3728,10 @@
         <x:v>30006</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>81</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D7" s="6">
         <x:v>100</x:v>
@@ -3179,7 +3740,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="6" t="s">
-        <x:v>140</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H7" s="6">
         <x:v>10</x:v>
@@ -3197,7 +3758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="6" t="s">
-        <x:v>136</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:13">
@@ -3205,10 +3766,10 @@
         <x:v>30007</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>153</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D8" s="6">
         <x:v>100</x:v>
@@ -3217,7 +3778,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H8" s="6">
         <x:v>10</x:v>
@@ -3235,7 +3796,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
@@ -3252,10 +3813,10 @@
         <x:v>31001</x:v>
       </x:c>
       <x:c r="B12" s="7" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D12" s="6">
         <x:v>150</x:v>
@@ -3264,36 +3825,36 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F12" s="7" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H12" s="6">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I12" s="6">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J12" s="6">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H12">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I12">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J12">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12">
+        <x:v>0.10000000000000001</x:v>
+      </x:c>
+      <x:c r="L12">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="7" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" s="6">
-        <x:v>0.29999999999999999</x:v>
-      </x:c>
-      <x:c r="L12" s="6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="7" t="s">
-        <x:v>138</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5">
+    </x:row>
+    <x:row r="13" spans="1:12">
       <x:c r="A13" s="11">
         <x:v>31002</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" s="6">
         <x:v>150</x:v>
@@ -3301,16 +3862,31 @@
       <x:c r="E13" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5" ht="16.75">
+      <x:c r="H13" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I13" s="6">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="J13" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="6">
+        <x:v>0.10000000000000001</x:v>
+      </x:c>
+      <x:c r="L13" s="6">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:12" ht="16.75">
       <x:c r="A14" s="10">
         <x:v>31003</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D14" s="6">
         <x:v>150</x:v>
@@ -3318,16 +3894,31 @@
       <x:c r="E14" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" spans="1:5">
+      <x:c r="H14" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I14" s="6">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J14" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="6">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L14" s="6">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:12">
       <x:c r="A15" s="11">
         <x:v>31004</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D15" s="6">
         <x:v>150</x:v>
@@ -3335,16 +3926,31 @@
       <x:c r="E15" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:5" ht="16.75">
+      <x:c r="H15" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I15" s="6">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="J15" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L15" s="6">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:12" ht="16.75">
       <x:c r="A16" s="10">
         <x:v>31005</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D16" s="6">
         <x:v>150</x:v>
@@ -3352,16 +3958,31 @@
       <x:c r="E16" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5">
+      <x:c r="H16" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I16" s="6">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="J16" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K16" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L16" s="6">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:12">
       <x:c r="A17" s="11">
         <x:v>31006</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C17" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D17" s="6">
         <x:v>150</x:v>
@@ -3369,21 +3990,51 @@
       <x:c r="E17" s="6" t="b">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5" ht="16.75">
+      <x:c r="H17" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I17" s="6">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="J17" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L17" s="6">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:12" ht="16.75">
       <x:c r="A18" s="10">
         <x:v>31007</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C18" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="6">
         <x:v>150</x:v>
       </x:c>
       <x:c r="E18" s="6" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I18" s="6">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="J18" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="6">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="L18" s="6">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -3418,22 +4069,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>160</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>149</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -3441,19 +4092,19 @@
         <x:v>50001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="6">
         <x:v>180</x:v>
       </x:c>
       <x:c r="D2" s="19" t="s">
-        <x:v>139</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="19" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="19" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -3467,13 +4118,13 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -3487,13 +4138,13 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>101</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3506,7 +4157,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet6"/>
   <x:dimension ref="A1:E17"/>
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="2" max="2" width="12" style="6" customWidth="1"/>
     <x:col min="3" max="3" width="12.640625" style="6" customWidth="1"/>
@@ -3518,22 +4169,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D1" s="17" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E1" s="17" t="s">
-        <x:v>125</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4" ht="16.75">
       <x:c r="A2" s="13">
         <x:v>60001</x:v>
       </x:c>
@@ -3689,7 +4340,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:4">
+    <x:row r="16" spans="1:4" ht="16.75">
       <x:c r="A16" s="15"/>
       <x:c r="D16" s="18">
         <x:v>0</x:v>
@@ -3719,7 +4370,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet7"/>
   <x:dimension ref="A1:E21"/>
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="10" style="5" customWidth="1"/>
     <x:col min="2" max="2" width="13.92578125" style="6" customWidth="1"/>
@@ -3730,22 +4381,22 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>143</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5" ht="16.75">
       <x:c r="A2" s="13">
         <x:v>70001</x:v>
       </x:c>
@@ -3913,7 +4564,7 @@
     <x:row r="15" spans="1:1">
       <x:c r="A15" s="14"/>
     </x:row>
-    <x:row r="16" spans="1:1">
+    <x:row r="16" spans="1:1" ht="16.75">
       <x:c r="A16" s="15"/>
     </x:row>
     <x:row r="17" spans="1:1">
@@ -3941,7 +4592,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet8"/>
   <x:dimension ref="A1:E2"/>
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="15.78515625" style="6" customWidth="1"/>
     <x:col min="2" max="2" width="13.5" style="6" customWidth="1"/>
@@ -3949,19 +4600,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
@@ -3979,7 +4630,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet9"/>
   <x:dimension ref="A1:I22"/>
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001"/>
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="2" max="2" width="17.28515625" style="6" customWidth="1"/>
     <x:col min="3" max="3" width="35.0703125" style="6" customWidth="1"/>
@@ -3993,31 +4644,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:9">
       <x:c r="A1" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B1" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D1" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F1" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G1" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I1" s="7" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9">
@@ -4025,10 +4676,10 @@
         <x:v>90001</x:v>
       </x:c>
       <x:c r="B2" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G2" s="6">
         <x:v>5</x:v>
@@ -4042,10 +4693,10 @@
         <x:v>90001</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G3" s="6">
         <x:v>10</x:v>
@@ -4059,10 +4710,10 @@
         <x:v>90001</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G4" s="6">
         <x:v>25</x:v>
@@ -4076,10 +4727,10 @@
         <x:v>90002</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G5" s="6">
         <x:v>2</x:v>
@@ -4090,10 +4741,10 @@
         <x:v>90002</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C6" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G6" s="6">
         <x:v>5</x:v>
@@ -4104,10 +4755,10 @@
         <x:v>90002</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
-        <x:v>95</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G7" s="6">
         <x:v>10</x:v>
@@ -4118,10 +4769,10 @@
         <x:v>90003</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G8" s="6">
         <x:v>15</x:v>
@@ -4135,10 +4786,10 @@
         <x:v>90003</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G9" s="6">
         <x:v>20</x:v>
@@ -4152,10 +4803,10 @@
         <x:v>90003</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>166</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G10" s="6">
         <x:v>40</x:v>
@@ -4169,10 +4820,10 @@
         <x:v>90004</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G11" s="6">
         <x:v>50</x:v>
@@ -4183,10 +4834,10 @@
         <x:v>90004</x:v>
       </x:c>
       <x:c r="B12" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G12" s="6">
         <x:v>150</x:v>
@@ -4197,10 +4848,10 @@
         <x:v>90004</x:v>
       </x:c>
       <x:c r="B13" s="7" t="s">
-        <x:v>108</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G13" s="6">
         <x:v>250</x:v>
@@ -4211,10 +4862,10 @@
         <x:v>90005</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>155</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G14" s="6">
         <x:v>3</x:v>
@@ -4228,10 +4879,10 @@
         <x:v>90005</x:v>
       </x:c>
       <x:c r="B15" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>155</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G15" s="6">
         <x:v>5</x:v>
@@ -4245,10 +4896,10 @@
         <x:v>90005</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>117</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>155</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G16" s="6">
         <x:v>7</x:v>
@@ -4262,10 +4913,10 @@
         <x:v>90006</x:v>
       </x:c>
       <x:c r="B17" s="7" t="s">
-        <x:v>109</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C17" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F17" s="6">
         <x:v>1</x:v>
@@ -4279,10 +4930,10 @@
         <x:v>90006</x:v>
       </x:c>
       <x:c r="B18" s="7" t="s">
-        <x:v>109</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F18" s="6">
         <x:v>1</x:v>
@@ -4296,10 +4947,10 @@
         <x:v>90006</x:v>
       </x:c>
       <x:c r="B19" s="7" t="s">
-        <x:v>109</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C19" s="7" t="s">
-        <x:v>164</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F19" s="6">
         <x:v>1</x:v>
@@ -4313,10 +4964,10 @@
         <x:v>90007</x:v>
       </x:c>
       <x:c r="B20" s="7" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C20" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G20" s="6">
         <x:v>50</x:v>
@@ -4327,10 +4978,10 @@
         <x:v>90007</x:v>
       </x:c>
       <x:c r="B21" s="7" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G21" s="6">
         <x:v>150</x:v>
@@ -4341,10 +4992,10 @@
         <x:v>90007</x:v>
       </x:c>
       <x:c r="B22" s="7" t="s">
-        <x:v>94</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C22" s="7" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G22" s="6">
         <x:v>350</x:v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
@@ -235,310 +235,345 @@
     <t xml:space="preserve">체력 {0}/{1} % 증가</t>
   </si>
   <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -546,7 +581,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -555,6 +590,13 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -716,7 +758,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -786,19 +828,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -969,23 +1006,22 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="9">
-      <tableStyleElement type="wholeTable" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="totalRow" dxfId="11"/>
-      <tableStyleElement type="firstColumn" dxfId="10"/>
-      <tableStyleElement type="lastColumn" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="12"/>
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="totalRow" dxfId="10"/>
+      <tableStyleElement type="firstColumn" dxfId="9"/>
+      <tableStyleElement type="lastColumn" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="8">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="6">
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="totalRow" dxfId="3"/>
+      <tableStyleElement type="firstColumn" dxfId="2"/>
+      <tableStyleElement type="lastColumn" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1312,46 +1348,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>56</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>36</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="L1" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.55">
@@ -1374,16 +1410,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I2" s="6">
         <v>10</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K2" s="6">
         <v>10</v>
@@ -1392,7 +1428,7 @@
         <v>2</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>43</v>
@@ -1403,7 +1439,7 @@
         <v>10002</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>47</v>
@@ -1436,10 +1472,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.55">
@@ -1480,7 +1516,7 @@
         <v>6</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>49</v>
@@ -1524,7 +1560,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>14</v>
@@ -1535,7 +1571,7 @@
         <v>10005</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>29</v>
@@ -1568,10 +1604,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.55">
@@ -1612,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -1626,7 +1662,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D8" s="4">
         <v>40</v>
@@ -1656,7 +1692,7 @@
         <v>3</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>39</v>
@@ -1670,7 +1706,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="4">
         <v>70</v>
@@ -1700,7 +1736,7 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>31</v>
@@ -1711,7 +1747,7 @@
         <v>10009</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>45</v>
@@ -1744,10 +1780,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.55">
@@ -1755,10 +1791,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D11" s="4">
         <v>150</v>
@@ -1788,10 +1824,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.55">
@@ -1832,7 +1868,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>25</v>
@@ -1846,7 +1882,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" s="4">
         <v>100</v>
@@ -1876,7 +1912,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>34</v>
@@ -1887,10 +1923,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D14" s="4">
         <v>250</v>
@@ -1920,10 +1956,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.55">
@@ -1931,10 +1967,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D15" s="4">
         <v>60</v>
@@ -1964,10 +2000,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.55">
@@ -1978,7 +2014,7 @@
         <v>51</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D16" s="4">
         <v>60</v>
@@ -2008,7 +2044,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>51</v>
@@ -2019,7 +2055,7 @@
         <v>10016</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>46</v>
@@ -2052,10 +2088,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.55">
@@ -2063,10 +2099,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D22" s="4">
         <v>500</v>
@@ -2096,10 +2132,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O22" s="1"/>
     </row>
@@ -2124,25 +2160,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>58</v>
@@ -2159,7 +2195,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
@@ -2176,7 +2212,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F3" s="6">
         <v>1</v>
@@ -2193,7 +2229,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
@@ -2207,10 +2243,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F5" s="6">
         <v>1</v>
@@ -2225,10 +2261,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F6" s="6">
         <v>1</v>
@@ -2242,10 +2278,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
@@ -2279,28 +2315,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>50</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>18</v>
@@ -2315,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D2" s="6">
         <v>100</v>
@@ -2330,7 +2366,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55">
@@ -2338,10 +2374,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" s="6">
         <v>200</v>
@@ -2356,7 +2392,7 @@
         <v>62</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55">
@@ -2367,7 +2403,7 @@
         <v>67</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D4" s="6">
         <v>50</v>
@@ -2382,7 +2418,7 @@
         <v>62</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55">
@@ -2390,7 +2426,7 @@
         <v>110004</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>0</v>
@@ -2413,7 +2449,7 @@
         <v>110005</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1</v>
@@ -2451,22 +2487,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>50</v>
@@ -2480,7 +2516,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" s="6">
         <v>100</v>
@@ -2489,7 +2525,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2517,31 +2553,31 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>50</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>58</v>
@@ -2550,7 +2586,7 @@
         <v>64</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -2558,10 +2594,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D2" s="6">
         <v>100</v>
@@ -2570,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H2" s="6">
         <v>5</v>
@@ -2596,7 +2632,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D3" s="6">
         <v>100</v>
@@ -2605,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H3" s="6">
         <v>5</v>
@@ -2620,7 +2656,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55">
@@ -2638,16 +2674,19 @@
         <v>41001</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="6">
         <v>150</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>176</v>
       </c>
       <c r="H7" s="6">
         <v>8</v>
@@ -2670,7 +2709,7 @@
         <v>41002</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>63</v>
@@ -2681,6 +2720,9 @@
       <c r="E8" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="F8" s="23" t="s">
+        <v>177</v>
+      </c>
       <c r="H8" s="6">
         <v>13</v>
       </c>
@@ -2694,7 +2736,7 @@
         <v>0.1</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55">
@@ -2738,31 +2780,31 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>50</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>58</v>
@@ -2774,7 +2816,7 @@
         <v>52</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -2794,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H2" s="6">
         <v>10</v>
@@ -2831,8 +2873,8 @@
       <c r="E3" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>68</v>
+      <c r="F3" s="23" t="s">
+        <v>168</v>
       </c>
       <c r="H3" s="6">
         <v>10</v>
@@ -2850,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55">
@@ -2858,10 +2900,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D4" s="6">
         <v>100</v>
@@ -2869,8 +2911,8 @@
       <c r="E4" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>152</v>
+      <c r="F4" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="H4" s="6">
         <v>10</v>
@@ -2888,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55">
@@ -2899,7 +2941,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D5" s="6">
         <v>100</v>
@@ -2908,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H5" s="6">
         <v>15</v>
@@ -2926,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55">
@@ -2934,10 +2976,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D6" s="6">
         <v>100</v>
@@ -2946,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H6" s="6">
         <v>10</v>
@@ -2972,10 +3014,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D7" s="6">
         <v>100</v>
@@ -3013,7 +3055,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D8" s="6">
         <v>100</v>
@@ -3022,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H8" s="6">
         <v>10</v>
@@ -3040,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55">
@@ -3060,7 +3102,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D12" s="6">
         <v>150</v>
@@ -3068,8 +3110,8 @@
       <c r="E12" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>92</v>
+      <c r="F12" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="H12" s="0">
         <v>10</v>
@@ -3095,7 +3137,7 @@
         <v>31002</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>60</v>
@@ -3106,6 +3148,9 @@
       <c r="E13" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="F13" s="23" t="s">
+        <v>170</v>
+      </c>
       <c r="H13" s="6">
         <v>10</v>
       </c>
@@ -3122,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55">
@@ -3130,10 +3175,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D14" s="6">
         <v>150</v>
@@ -3141,6 +3186,9 @@
       <c r="E14" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="F14" s="23" t="s">
+        <v>171</v>
+      </c>
       <c r="H14" s="6">
         <v>10</v>
       </c>
@@ -3157,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55">
@@ -3165,10 +3213,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D15" s="6">
         <v>150</v>
@@ -3176,6 +3224,9 @@
       <c r="E15" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="F15" s="23" t="s">
+        <v>172</v>
+      </c>
       <c r="H15" s="6">
         <v>10</v>
       </c>
@@ -3192,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55">
@@ -3200,7 +3251,7 @@
         <v>31005</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>66</v>
@@ -3210,6 +3261,9 @@
       </c>
       <c r="E16" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="H16" s="6">
         <v>10</v>
@@ -3235,16 +3289,19 @@
         <v>31006</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" s="6">
         <v>150</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>0</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="H17" s="6">
         <v>10</v>
@@ -3270,7 +3327,7 @@
         <v>31007</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>55</v>
@@ -3281,6 +3338,9 @@
       <c r="E18" s="6" t="b">
         <v>0</v>
       </c>
+      <c r="F18" s="23" t="s">
+        <v>175</v>
+      </c>
       <c r="H18" s="6">
         <v>10</v>
       </c>
@@ -3297,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55">
@@ -3312,7 +3372,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3332,10 +3392,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>57</v>
@@ -3344,10 +3404,10 @@
         <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55">
@@ -3381,7 +3441,7 @@
         <v>180</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>27</v>
@@ -3401,13 +3461,13 @@
         <v>180</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3433,10 +3493,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>33</v>
@@ -3445,7 +3505,7 @@
         <v>41</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -3646,10 +3706,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>3</v>
@@ -3866,16 +3926,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>50</v>
@@ -3911,25 +3971,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>50</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>58</v>
@@ -3946,7 +4006,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G2" s="6">
         <v>5</v>
@@ -3963,7 +4023,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="6">
         <v>10</v>
@@ -3980,7 +4040,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G4" s="6">
         <v>25</v>
@@ -3994,7 +4054,7 @@
         <v>90002</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
@@ -4008,7 +4068,7 @@
         <v>90002</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>13</v>
@@ -4022,7 +4082,7 @@
         <v>90002</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
@@ -4039,7 +4099,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G8" s="6">
         <v>15</v>
@@ -4056,7 +4116,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G9" s="6">
         <v>20</v>
@@ -4073,7 +4133,7 @@
         <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G10" s="6">
         <v>40</v>
@@ -4132,7 +4192,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G14" s="6">
         <v>3</v>
@@ -4149,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G15" s="6">
         <v>5</v>
@@ -4166,7 +4226,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G16" s="6">
         <v>7</v>
@@ -4183,7 +4243,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
@@ -4200,7 +4260,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" s="6">
         <v>1</v>
@@ -4217,7 +4277,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F19" s="6">
         <v>1</v>
@@ -4231,7 +4291,7 @@
         <v>90007</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>13</v>
@@ -4245,7 +4305,7 @@
         <v>90007</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>13</v>
@@ -4259,7 +4319,7 @@
         <v>90007</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>13</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -19,545 +19,544 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
   </si>
 </sst>
 </file>
@@ -565,7 +564,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -596,6 +595,11 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -606,7 +610,7 @@
     </fill>
   </fills>
   <borders count="12">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -619,8 +623,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -633,8 +640,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -647,8 +657,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -661,8 +674,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -675,8 +691,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -689,8 +708,11 @@
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -703,8 +725,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -717,8 +742,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -731,8 +759,11 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -745,8 +776,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -759,8 +793,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -773,10 +810,55 @@
       <bottom style="medium">
         <color rgb="FFFFD700"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -858,10 +940,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -894,28 +975,101 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondColumnStripe" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -964,7 +1118,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri Light" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1016,7 +1170,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1213,7 +1367,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="7" customWidth="1"/>
@@ -1232,46 +1386,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1279,10 +1433,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1294,16 +1448,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1312,10 +1466,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1323,10 +1477,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1356,10 +1510,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1367,10 +1521,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1400,10 +1554,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1411,10 +1565,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1444,10 +1598,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1455,10 +1609,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1488,10 +1642,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1499,10 +1653,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1532,10 +1686,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1543,10 +1697,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1576,10 +1730,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1587,10 +1741,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1620,10 +1774,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1631,10 +1785,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1664,10 +1818,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1675,10 +1829,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1708,10 +1862,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1719,10 +1873,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1752,10 +1906,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1763,10 +1917,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1796,10 +1950,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1807,10 +1961,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -1840,10 +1994,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1851,10 +2005,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -1884,10 +2038,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1895,10 +2049,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -1928,10 +2082,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1939,10 +2093,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -1972,10 +2126,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1983,10 +2137,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2016,10 +2170,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2033,7 +2187,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="7" customWidth="1"/>
@@ -2043,31 +2197,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2075,10 +2229,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2092,10 +2246,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2109,10 +2263,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2126,10 +2280,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2144,10 +2298,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2161,10 +2315,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2183,7 +2337,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="7" customWidth="1"/>
@@ -2197,31 +2351,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>37</v>
+        <v>110</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2230,10 +2384,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2245,10 +2399,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2256,10 +2410,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2271,10 +2425,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2282,10 +2436,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2297,10 +2451,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2308,10 +2462,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2323,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2331,10 +2485,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2346,7 +2500,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2513,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="7" customWidth="1"/>
@@ -2368,25 +2522,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2394,10 +2548,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2406,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2433,40 +2587,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -2474,10 +2628,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2486,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2501,7 +2655,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2509,10 +2663,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2521,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2536,7 +2690,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2554,10 +2708,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2566,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2581,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2589,10 +2743,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2601,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2616,7 +2770,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2659,43 +2813,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2703,10 +2857,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2715,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2733,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2741,10 +2895,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2753,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2771,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>171</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2779,10 +2933,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2791,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2809,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2817,10 +2971,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2829,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -2847,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2855,10 +3009,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -2867,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -2885,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2893,10 +3047,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -2905,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -2923,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2931,10 +3085,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -2943,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -2961,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -2978,10 +3132,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -2990,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3008,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3016,10 +3170,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3028,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3046,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>171</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3054,10 +3208,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3066,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3084,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3092,10 +3246,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3104,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3122,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3130,10 +3284,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3142,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3160,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3168,10 +3322,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3180,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3198,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3206,10 +3360,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3218,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3236,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3270,22 +3424,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>166</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3293,19 +3447,19 @@
         <v>50001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C2" s="7">
         <v>180</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3319,13 +3473,13 @@
         <v>180</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3339,13 +3493,13 @@
         <v>180</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3358,7 +3512,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="12" style="7" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="7" customWidth="1"/>
@@ -3370,22 +3524,22 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.75">
       <c r="A2" s="14">
         <v>60001</v>
       </c>
@@ -3477,7 +3631,7 @@
         <v>30007</v>
       </c>
       <c r="C8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="19">
         <v>0</v>
@@ -3541,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="16.75">
       <c r="A16" s="16"/>
       <c r="D16" s="19">
         <v>0</v>
@@ -3571,7 +3725,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="7" customWidth="1"/>
@@ -3582,22 +3736,22 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.75">
       <c r="A2" s="14">
         <v>70001</v>
       </c>
@@ -3765,7 +3919,7 @@
     <row r="15" spans="1:1">
       <c r="A15" s="15"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" ht="16.75">
       <c r="A16" s="16"/>
     </row>
     <row r="17" spans="1:1">
@@ -3793,7 +3947,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="7" customWidth="1"/>
@@ -3801,19 +3955,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3831,7 +3985,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="7" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="7" customWidth="1"/>
@@ -3845,31 +3999,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3877,10 +4031,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -3894,10 +4048,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -3911,10 +4065,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -3928,10 +4082,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -3942,10 +4096,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -3956,10 +4110,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -3970,10 +4124,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -3987,10 +4141,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4004,10 +4158,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4021,10 +4175,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4035,10 +4189,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4049,10 +4203,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4063,10 +4217,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4080,10 +4234,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4097,10 +4251,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4114,10 +4268,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4131,10 +4285,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4148,10 +4302,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4165,10 +4319,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4179,10 +4333,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4193,10 +4347,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -25,535 +25,535 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
     <t xml:space="preserve">뱀이다</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
   </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
     <t xml:space="preserve">거미다</t>
   </si>
   <si>
     <t xml:space="preserve">곰이다</t>
   </si>
   <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">10007;10008;10009;10010;</t>
@@ -942,15 +942,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1049,27 +1041,98 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
+      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
+      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1386,46 +1449,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1433,10 +1496,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1448,16 +1511,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1466,10 +1529,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1477,10 +1540,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1510,10 +1573,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1521,10 +1584,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1554,10 +1617,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1565,10 +1628,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1598,10 +1661,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1609,10 +1672,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1642,10 +1705,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1653,10 +1716,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1686,10 +1749,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1697,10 +1760,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1730,10 +1793,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1741,10 +1804,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1774,10 +1837,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1785,10 +1848,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1818,10 +1881,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1829,10 +1892,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1862,10 +1925,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1873,10 +1936,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1906,10 +1969,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1917,10 +1980,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1950,10 +2013,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>161</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1961,10 +2024,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -1994,10 +2057,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2005,10 +2068,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2038,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2049,10 +2112,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2082,10 +2145,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2093,10 +2156,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2126,10 +2189,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2140,7 +2203,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2170,7 +2233,7 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>17</v>
@@ -2197,31 +2260,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2229,10 +2292,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2246,10 +2309,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2263,10 +2326,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2280,10 +2343,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2298,10 +2361,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2315,10 +2378,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2351,31 +2414,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2384,10 +2447,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2399,10 +2462,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>109</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2410,10 +2473,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2425,10 +2488,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2436,7 +2499,7 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>171</v>
@@ -2451,10 +2514,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2462,10 +2525,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>57</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2477,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2485,10 +2548,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>165</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2500,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2522,25 +2585,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2548,10 +2611,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2560,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2587,40 +2650,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -2628,10 +2691,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2640,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2655,7 +2718,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2663,10 +2726,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2675,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2690,7 +2753,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2708,10 +2771,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2720,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2735,7 +2798,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2743,10 +2806,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2755,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2770,7 +2833,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2813,43 +2876,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2857,10 +2920,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2869,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2887,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2895,10 +2958,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2907,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2925,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2933,10 +2996,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2945,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2963,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2971,10 +3034,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2983,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -3001,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3009,10 +3072,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3021,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3039,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3047,10 +3110,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3059,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3077,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3085,10 +3148,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3097,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3115,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3132,10 +3195,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3144,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3162,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3170,10 +3233,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3182,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3200,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3211,7 +3274,7 @@
         <v>33</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3220,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3238,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3246,10 +3309,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3258,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3276,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3284,10 +3347,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3296,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3314,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3322,10 +3385,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3334,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3352,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3360,10 +3423,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3372,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3390,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3424,22 +3487,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3447,19 +3510,19 @@
         <v>50001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="C2" s="7">
         <v>180</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3473,13 +3536,13 @@
         <v>180</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3496,10 +3559,10 @@
         <v>177</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3524,19 +3587,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3631,7 +3694,7 @@
         <v>30007</v>
       </c>
       <c r="C8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="19">
         <v>0</v>
@@ -3736,19 +3799,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -3955,19 +4018,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3999,31 +4062,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4031,10 +4094,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4048,10 +4111,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4065,10 +4128,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4082,10 +4145,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4096,10 +4159,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4110,10 +4173,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4127,7 +4190,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4144,7 +4207,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4161,7 +4224,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4178,7 +4241,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4192,7 +4255,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4206,7 +4269,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4217,10 +4280,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4234,10 +4297,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4251,10 +4314,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4268,10 +4331,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4285,10 +4348,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4302,10 +4365,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4319,10 +4382,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4333,10 +4396,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4347,10 +4410,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -25,172 +25,394 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 {0} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
     <t xml:space="preserve">stat_type</t>
   </si>
   <si>
     <t xml:space="preserve">attack_type</t>
   </si>
   <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">미사일 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">폭발 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
     <t xml:space="preserve">엘리트 냉기 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">기관총 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">GoblinSpear</t>
   </si>
   <si>
     <t xml:space="preserve">need_money</t>
   </si>
   <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">Minotaur</t>
   </si>
   <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
     <t xml:space="preserve">냉기 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">projectile_prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
   </si>
   <si>
     <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">stage_inspection_time</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
   </si>
   <si>
     <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
@@ -199,285 +421,90 @@
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
   </si>
   <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
     <t xml:space="preserve">기관총으로 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
   </si>
   <si>
     <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_exp_max</t>
   </si>
   <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
     <t xml:space="preserve">upgrade_value</t>
   </si>
   <si>
@@ -487,73 +514,46 @@
     <t xml:space="preserve">drop_exp_min</t>
   </si>
   <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">AttackInterval</t>
   </si>
   <si>
     <t xml:space="preserve">AttackDamage</t>
   </si>
   <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
     <t xml:space="preserve">attack_damage</t>
   </si>
   <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">10007;10008;10009;10010;</t>
@@ -946,22 +946,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FF6182D6"/>
           <bgColor rgb="FF6182D6"/>
         </patternFill>
@@ -1056,6 +1040,14 @@
           <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
       <border>
         <left style="thin">
           <color rgb="FFBFBFBF"/>
@@ -1117,22 +1109,20 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
-      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
+      <tableStyleElement type="lastColumn" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1449,43 +1439,43 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>26</v>
@@ -1496,10 +1486,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1511,16 +1501,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1529,10 +1519,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1540,10 +1530,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1573,10 +1563,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1584,10 +1574,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1617,10 +1607,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1631,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1661,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>1</v>
@@ -1672,10 +1662,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1705,10 +1695,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1716,10 +1706,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1749,10 +1739,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1760,10 +1750,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1793,10 +1783,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1804,10 +1794,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1837,10 +1827,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1848,10 +1838,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1881,10 +1871,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1892,10 +1882,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1925,10 +1915,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1936,10 +1926,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1969,10 +1959,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1980,10 +1970,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -2013,10 +2003,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -2024,10 +2014,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -2057,10 +2047,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2068,10 +2058,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2101,10 +2091,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2112,10 +2102,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2145,10 +2135,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2156,10 +2146,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2189,10 +2179,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2200,10 +2190,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2233,10 +2223,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2260,31 +2250,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2295,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2312,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2329,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2343,10 +2333,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2361,10 +2351,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2378,10 +2368,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2414,31 +2404,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2447,10 +2437,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2462,10 +2452,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2473,10 +2463,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>55</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2488,10 +2478,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2499,10 +2489,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2514,10 +2504,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2525,10 +2515,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2540,7 +2530,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2548,10 +2538,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2563,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2585,25 +2575,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2611,10 +2601,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2623,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2650,40 +2640,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -2691,10 +2681,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2703,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2718,7 +2708,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2726,10 +2716,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2738,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2753,7 +2743,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2771,10 +2761,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2783,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2798,7 +2788,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2806,10 +2796,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2818,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2833,7 +2823,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2876,43 +2866,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2920,10 +2910,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2932,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2950,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2958,10 +2948,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2970,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2988,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2996,10 +2986,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -3008,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -3026,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3034,10 +3024,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -3046,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -3064,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3072,10 +3062,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3084,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3102,7 +3092,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3110,10 +3100,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3122,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3140,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3148,10 +3138,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3160,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3178,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3195,10 +3185,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3225,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3233,10 +3223,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3245,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3263,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3271,10 +3261,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3283,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3301,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3309,10 +3299,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3321,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3339,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3347,10 +3337,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3359,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3377,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3385,10 +3375,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3397,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3415,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3423,10 +3413,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3435,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3453,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3487,22 +3477,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3510,19 +3500,19 @@
         <v>50001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C2" s="7">
         <v>180</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3536,13 +3526,13 @@
         <v>180</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3559,10 +3549,10 @@
         <v>177</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3587,19 +3577,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3652,7 +3642,7 @@
         <v>30004</v>
       </c>
       <c r="C5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="19">
         <v>0</v>
@@ -3799,19 +3789,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -4018,19 +4008,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4062,31 +4052,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4094,10 +4084,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4111,10 +4101,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4128,10 +4118,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4145,10 +4135,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4159,10 +4149,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4173,10 +4163,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4190,7 +4180,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4207,7 +4197,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4224,7 +4214,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4238,10 +4228,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4252,10 +4242,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4266,10 +4256,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4280,10 +4270,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4297,10 +4287,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4314,10 +4304,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4331,10 +4321,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4348,10 +4338,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4365,10 +4355,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4382,10 +4372,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4396,10 +4386,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4410,10 +4400,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -25,538 +25,538 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">포격 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">폭발 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">레이저 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">전기 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">SkullKing</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">EliteFireTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">EliteCannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
   </si>
 </sst>
 </file>
@@ -942,15 +942,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1109,20 +1101,18 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
-      <tableStyleElement type="lastColumn" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
+      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
+      <tableStyleElement type="totalRow" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1439,46 +1429,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1486,10 +1476,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1501,16 +1491,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1519,10 +1509,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1530,10 +1520,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1563,10 +1553,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1574,10 +1564,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1607,10 +1597,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1618,10 +1608,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1651,10 +1641,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>1</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1662,10 +1652,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1695,10 +1685,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1706,10 +1696,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1739,10 +1729,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1750,10 +1740,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1783,10 +1773,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1794,10 +1784,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1827,10 +1817,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1838,10 +1828,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1871,10 +1861,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1882,10 +1872,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1915,10 +1905,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1926,10 +1916,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1959,10 +1949,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1970,10 +1960,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -2003,10 +1993,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -2014,10 +2004,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -2047,10 +2037,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2058,10 +2048,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2091,10 +2081,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2102,10 +2092,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>10</v>
+        <v>142</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2135,10 +2125,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>133</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2146,10 +2136,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2179,10 +2169,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2190,10 +2180,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2223,10 +2213,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2250,31 +2240,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2282,10 +2272,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2299,10 +2289,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2316,10 +2306,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>6</v>
+        <v>141</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2333,10 +2323,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2351,10 +2341,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2368,10 +2358,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2404,31 +2394,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2437,10 +2427,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2452,10 +2442,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2463,10 +2453,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2478,10 +2468,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>163</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2489,10 +2479,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2504,10 +2494,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2515,10 +2505,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2530,7 +2520,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>135</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2538,10 +2528,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2553,7 +2543,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>135</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2575,25 +2565,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2601,10 +2591,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2613,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>28</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2640,40 +2630,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="I1" s="7" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="16.75">
@@ -2681,10 +2671,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2693,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2708,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2716,10 +2706,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2728,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2743,7 +2733,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2761,10 +2751,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2773,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2788,7 +2778,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2796,10 +2786,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2808,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2823,7 +2813,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2866,43 +2856,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="I1" s="7" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2910,10 +2900,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2922,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2940,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2948,10 +2938,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2960,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2978,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2986,10 +2976,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2998,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -3016,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3024,10 +3014,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -3036,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -3054,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3062,10 +3052,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3074,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3092,7 +3082,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3100,10 +3090,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3112,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3130,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3138,10 +3128,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3150,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3168,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3185,10 +3175,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3197,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3215,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3223,10 +3213,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3235,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3253,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3261,10 +3251,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3273,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3291,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3299,10 +3289,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3311,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3329,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3337,10 +3327,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3349,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3367,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3375,10 +3365,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3387,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3405,7 +3395,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3413,10 +3403,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3425,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3443,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3477,22 +3467,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>146</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3500,19 +3490,19 @@
         <v>50001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C2" s="7">
         <v>180</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3526,13 +3516,13 @@
         <v>180</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3546,13 +3536,13 @@
         <v>180</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3577,19 +3567,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3642,7 +3632,7 @@
         <v>30004</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="19">
         <v>0</v>
@@ -3656,7 +3646,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="19">
         <v>0</v>
@@ -3789,19 +3779,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>138</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -4008,19 +3998,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4052,31 +4042,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>166</v>
+        <v>12</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4084,10 +4074,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4101,10 +4091,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4118,10 +4108,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4135,10 +4125,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4149,10 +4139,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4163,10 +4153,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4177,10 +4167,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4194,10 +4184,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4211,10 +4201,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4228,10 +4218,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4242,10 +4232,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4256,10 +4246,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4270,10 +4260,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4287,10 +4277,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4304,10 +4294,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>11</v>
+        <v>146</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4321,10 +4311,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4338,10 +4328,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4355,10 +4345,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4372,10 +4362,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4386,10 +4376,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4400,10 +4390,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="5"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
-    <sheet name="Train_Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Range_Train_Data" sheetId="3" r:id="rId6"/>
-    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId7"/>
-    <sheet name="Stage_Data" sheetId="5" r:id="rId8"/>
-    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId9"/>
-    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId10"/>
-    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId11"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId12"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
-    <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Range_Train_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage_Data" sheetId="5" r:id="rId5"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
+  <calcPr/>
+  <extLst>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="178">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>
@@ -265,9 +271,6 @@
     <t xml:space="preserve">1;1;1;</t>
   </si>
   <si>
-    <t xml:space="preserve">180;</t>
-  </si>
-  <si>
     <t xml:space="preserve">포격 포탑</t>
   </si>
   <si>
@@ -557,6 +560,10 @@
   </si>
   <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -564,7 +571,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -574,31 +581,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -610,22 +600,12 @@
     </fill>
   </fills>
   <borders count="12">
-    <border diagonalUp="1" diagonalDown="1">
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -637,12 +617,8 @@
       <top style="medium">
         <color rgb="FF5B9BD5"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -651,15 +627,9 @@
       <right style="medium">
         <color rgb="FF5B9BD5"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -671,12 +641,8 @@
       <top style="medium">
         <color rgb="FFFFC000"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -685,15 +651,9 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -702,15 +662,11 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -722,12 +678,8 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -736,15 +688,9 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -753,15 +699,11 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -773,12 +715,8 @@
       <top style="medium">
         <color rgb="FFFFD700"/>
       </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -787,15 +725,9 @@
       <right style="medium">
         <color rgb="FFFFD700"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -804,65 +736,19 @@
       <right style="medium">
         <color rgb="FFFFD700"/>
       </right>
-      <top>
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFFFD700"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -938,43 +824,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1000,6 +857,14 @@
           <color rgb="FF8FABDB"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1049,72 +914,29 @@
         </right>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
-      <tableStyleElement type="totalRow" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="1">
+      <tableStyleElement type="headerRow" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1161,7 +983,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="2147483647"/>
+        <a:latin typeface="Calibri Light" panose="21474836470000000000"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1213,7 +1035,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="2147483647"/>
+        <a:latin typeface="Calibri" panose="21474836470000000000"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1403,6 +1225,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1410,7 +1234,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="7" customWidth="1"/>
@@ -1427,7 +1251,7 @@
     <col min="14" max="14" width="13.35546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -1435,16 +1259,16 @@
         <v>29</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>34</v>
@@ -1465,21 +1289,21 @@
         <v>26</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1512,10 +1336,10 @@
         <v>73</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A3" s="5">
         <v>10002</v>
       </c>
@@ -1523,7 +1347,7 @@
         <v>76</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1559,12 +1383,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A4" s="5">
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>70</v>
@@ -1600,18 +1424,18 @@
         <v>71</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A5" s="5">
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1644,18 +1468,18 @@
         <v>73</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A6" s="5">
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1688,18 +1512,18 @@
         <v>71</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A7" s="7">
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1732,15 +1556,15 @@
         <v>73</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A8" s="5">
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>41</v>
@@ -1776,15 +1600,15 @@
         <v>73</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A9" s="5">
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>40</v>
@@ -1796,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="7">
-        <v>6.4000000000000004</v>
+        <v>6.4</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -1820,18 +1644,18 @@
         <v>73</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A10" s="5">
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1840,7 +1664,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="7">
-        <v>4.2999999999999998</v>
+        <v>4.3</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -1864,15 +1688,15 @@
         <v>73</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A11" s="5">
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>35</v>
@@ -1908,18 +1732,18 @@
         <v>73</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A12" s="7">
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1952,10 +1776,10 @@
         <v>73</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A13" s="5">
         <v>10012</v>
       </c>
@@ -1999,12 +1823,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A14" s="5">
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>74</v>
@@ -2040,18 +1864,18 @@
         <v>73</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A15" s="5">
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2084,10 +1908,10 @@
         <v>73</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A16" s="5">
         <v>10015</v>
       </c>
@@ -2095,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2131,15 +1955,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A17" s="7">
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2172,18 +1996,18 @@
         <v>73</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A22" s="5">
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2195,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="7">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H22" s="7">
         <v>1000</v>
@@ -2216,11 +2040,12 @@
         <v>73</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O22" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2230,7 +2055,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="7" customWidth="1"/>
@@ -2238,7 +2063,7 @@
     <col min="9" max="9" width="19.78515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -2246,13 +2071,13 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>26</v>
@@ -2267,15 +2092,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2284,15 +2109,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="7">
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2301,15 +2126,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="7">
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2318,15 +2143,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="7">
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2336,15 +2161,15 @@
       </c>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="7">
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2353,15 +2178,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="7">
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2371,6 +2196,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2380,7 +2206,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="7" customWidth="1"/>
@@ -2392,7 +2218,7 @@
     <col min="10" max="10" width="12.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -2400,10 +2226,10 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>13</v>
@@ -2412,17 +2238,17 @@
         <v>59</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>24</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>110001</v>
       </c>
@@ -2430,7 +2256,7 @@
         <v>65</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2448,7 +2274,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="7">
         <v>110002</v>
       </c>
@@ -2462,7 +2288,7 @@
         <v>200</v>
       </c>
       <c r="E3" s="7">
-        <v>-0.10000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" s="7">
         <v>100</v>
@@ -2474,7 +2300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="7">
         <v>110003</v>
       </c>
@@ -2482,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2497,18 +2323,18 @@
         <v>3</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="7">
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2523,15 +2349,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="7">
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2547,6 +2373,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2556,42 +2383,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="7" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>33</v>
@@ -2603,10 +2430,11 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2616,39 +2444,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="7" customWidth="1"/>
     <col min="4" max="5" width="15.640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="22.65234375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.640625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="15.640625" style="7" customWidth="1"/>
     <col min="11" max="11" width="18.2109375" style="7" customWidth="1"/>
     <col min="12" max="12" width="21" style="7" customWidth="1"/>
     <col min="13" max="13" width="15.640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>26</v>
@@ -2663,10 +2491,10 @@
         <v>27</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="16.75">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="14">
         <v>40001</v>
       </c>
@@ -2674,7 +2502,7 @@
         <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2701,7 +2529,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A3" s="15">
         <v>40002</v>
       </c>
@@ -2730,28 +2558,28 @@
         <v>1</v>
       </c>
       <c r="K3" s="7">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A4" s="15"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A5" s="15"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A6" s="15"/>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="16.75">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A7" s="21">
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>18</v>
@@ -2763,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2781,12 +2609,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A8" s="22">
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>10</v>
@@ -2798,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2810,29 +2638,30 @@
         <v>1</v>
       </c>
       <c r="K8" s="7">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A9" s="22"/>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A10" s="22"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" ht="16.75">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A11" s="23"/>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2842,7 +2671,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="7" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="7" customWidth="1"/>
@@ -2854,27 +2683,27 @@
     <col min="12" max="13" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>26</v>
@@ -2892,15 +2721,15 @@
         <v>22</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="16.75">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="9">
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>28</v>
@@ -2933,12 +2762,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A3" s="10">
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>61</v>
@@ -2962,16 +2791,16 @@
         <v>1</v>
       </c>
       <c r="K3" s="7">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="7">
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A4" s="10">
         <v>30003</v>
       </c>
@@ -2979,7 +2808,7 @@
         <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -3009,15 +2838,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A5" s="10">
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -3047,15 +2876,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A6" s="10">
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3064,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3085,12 +2914,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A7" s="10">
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>68</v>
@@ -3123,15 +2952,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A8" s="10">
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3161,21 +2990,21 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A9" s="10"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A10" s="10"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A11" s="10"/>
     </row>
-    <row r="12" spans="1:13" ht="16.75">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A12" s="11">
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>49</v>
@@ -3187,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3199,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -3208,12 +3037,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A13" s="12">
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>5</v>
@@ -3225,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3237,21 +3066,21 @@
         <v>1</v>
       </c>
       <c r="K13" s="7">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L13" s="7">
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="16.75">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A14" s="11">
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>46</v>
@@ -3263,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3284,12 +3113,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A15" s="12">
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>52</v>
@@ -3301,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3322,12 +3151,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.75">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A16" s="11">
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>8</v>
@@ -3339,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3360,12 +3189,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A17" s="12">
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -3377,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3398,12 +3227,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16.75">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A18" s="11">
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>9</v>
@@ -3415,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3436,16 +3265,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A19" s="12"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A20" s="12"/>
     </row>
-    <row r="21" spans="1:1" ht="16.75">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A21" s="13"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3454,58 +3284,65 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="7" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="7" customWidth="1"/>
     <col min="4" max="4" width="23.92578125" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.92578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.2109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="F1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>50001</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>80</v>
+      <c r="B2" s="7">
+        <v>180</v>
       </c>
       <c r="C2" s="7">
         <v>180</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>57</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>79</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A3" s="2">
         <v>50002</v>
       </c>
@@ -3515,17 +3352,20 @@
       <c r="C3" s="7">
         <v>180</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A4" s="2">
         <v>50003</v>
       </c>
@@ -3535,19 +3375,23 @@
       <c r="C4" s="7">
         <v>180</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>159</v>
+      <c r="D4" s="7">
+        <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>124</v>
+        <v>158</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3555,7 +3399,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" style="7" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="7" customWidth="1"/>
@@ -3565,7 +3409,7 @@
     <col min="7" max="7" width="13.92578125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -3573,16 +3417,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.75">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="14">
         <v>60001</v>
       </c>
@@ -3596,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="15">
         <v>60002</v>
       </c>
@@ -3610,7 +3454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="15">
         <v>60003</v>
       </c>
@@ -3624,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="15">
         <v>60004</v>
       </c>
@@ -3638,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="15">
         <v>60005</v>
       </c>
@@ -3652,7 +3496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="15">
         <v>60006</v>
       </c>
@@ -3666,7 +3510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="15">
         <v>60007</v>
       </c>
@@ -3680,7 +3524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="15">
         <v>60008</v>
       </c>
@@ -3694,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="15">
         <v>60009</v>
       </c>
@@ -3708,43 +3552,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="15"/>
       <c r="D11" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="15"/>
       <c r="D12" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="15"/>
       <c r="D13" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="15"/>
       <c r="D14" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="15"/>
       <c r="D15" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="16.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="16"/>
       <c r="D16" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A17" s="6">
         <v>61001</v>
       </c>
@@ -3759,6 +3603,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3768,7 +3613,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="7" customWidth="1"/>
@@ -3777,7 +3622,7 @@
     <col min="5" max="5" width="13.78515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -3788,13 +3633,13 @@
         <v>62</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.75">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="14">
         <v>70001</v>
       </c>
@@ -3811,7 +3656,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="15">
         <v>70002</v>
       </c>
@@ -3828,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="15">
         <v>70003</v>
       </c>
@@ -3845,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="15">
         <v>70004</v>
       </c>
@@ -3862,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="15">
         <v>70005</v>
       </c>
@@ -3879,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="15">
         <v>70006</v>
       </c>
@@ -3896,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="15">
         <v>70007</v>
       </c>
@@ -3913,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="15">
         <v>70008</v>
       </c>
@@ -3930,7 +3775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="15">
         <v>70009</v>
       </c>
@@ -3947,40 +3792,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="15"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="15"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="15"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="15"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="15"/>
     </row>
-    <row r="16" spans="1:1" ht="16.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="17"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="17"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="17"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="17"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A21" s="17"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -3990,13 +3836,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -4004,21 +3850,22 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -4028,7 +3875,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="7" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="7" customWidth="1"/>
@@ -4040,7 +3887,7 @@
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="7" t="s">
         <v>36</v>
       </c>
@@ -4048,13 +3895,13 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>26</v>
@@ -4069,15 +3916,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="7">
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4086,15 +3933,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="7">
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4103,15 +3950,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="7">
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4120,150 +3967,150 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="7">
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="7">
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="7">
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A8" s="7">
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
       </c>
       <c r="I8" s="7">
-        <v>0.14999999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A9" s="7">
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
       </c>
       <c r="I9" s="7">
-        <v>0.14999999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A10" s="7">
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
       </c>
       <c r="I10" s="7">
-        <v>0.20000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A11" s="6">
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A12" s="7">
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A13" s="7">
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A14" s="6">
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4272,15 +4119,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A15" s="7">
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4289,15 +4136,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A16" s="7">
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4306,15 +4153,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A17" s="6">
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4323,15 +4170,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A18" s="7">
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4340,15 +4187,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A19" s="8">
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4357,49 +4204,50 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A20" s="8">
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A21" s="8">
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A22" s="8">
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,35 +1,458 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" activeTab="4"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Range_Train_Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId4"/>
-    <sheet name="Stage_Data" sheetId="5" r:id="rId5"/>
-    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
-    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
-    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
-    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId5"/>
+    <sheet name="Range_Train_Data" sheetId="3" r:id="rId6"/>
+    <sheet name="Turret_Train_Data" sheetId="4" r:id="rId7"/>
+    <sheet name="Stage_Data" sheetId="5" r:id="rId8"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId9"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId10"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId11"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId12"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>
@@ -37,533 +460,103 @@
     <t xml:space="preserve">체력 {0}/{1} % 증가</t>
   </si>
   <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">NonTrainUpgrade</t>
   </si>
   <si>
     <t xml:space="preserve">TrainUpgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">target_train_id</t>
   </si>
   <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
     <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
   </si>
   <si>
     <t xml:space="preserve">attack_delay</t>
   </si>
   <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">spawn_interval</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -571,7 +564,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -581,14 +574,31 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -600,12 +610,22 @@
     </fill>
   </fills>
   <borders count="12">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border diagonalUp="1" diagonalDown="1">
+      <left>
+        <color indexed="64"/>
+      </left>
+      <right>
+        <color indexed="64"/>
+      </right>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -617,8 +637,12 @@
       <top style="medium">
         <color rgb="FF5B9BD5"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -627,9 +651,15 @@
       <right style="medium">
         <color rgb="FF5B9BD5"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -641,8 +671,12 @@
       <top style="medium">
         <color rgb="FFFFC000"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -651,9 +685,15 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -662,11 +702,15 @@
       <right style="medium">
         <color rgb="FFFFC000"/>
       </right>
-      <top/>
+      <top>
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
-      <diagonal/>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -678,8 +722,12 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -688,9 +736,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -699,11 +753,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top>
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -715,8 +773,12 @@
       <top style="medium">
         <color rgb="FFFFD700"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -725,9 +787,15 @@
       <right style="medium">
         <color rgb="FFFFD700"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top>
+        <color indexed="64"/>
+      </top>
+      <bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
     <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
@@ -736,15 +804,61 @@
       <right style="medium">
         <color rgb="FFFFD700"/>
       </right>
-      <top/>
+      <top>
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFFFD700"/>
       </bottom>
-      <diagonal/>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -824,27 +938,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -914,29 +1015,94 @@
         </right>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="1">
-      <tableStyleElement type="headerRow" dxfId="7"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
+      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="6">
+      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -983,7 +1149,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri Light" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1035,7 +1201,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1225,8 +1391,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1234,7 +1398,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="7" customWidth="1"/>
@@ -1251,59 +1415,59 @@
     <col min="14" max="14" width="13.35546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>132</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="7">
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1315,16 +1479,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1333,21 +1497,21 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="5">
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1377,21 +1541,21 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="5">
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1421,21 +1585,21 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="5">
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1465,21 +1629,21 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="5">
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1509,21 +1673,21 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="7">
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1553,21 +1717,21 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="5">
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1597,21 +1761,21 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="5">
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1620,7 +1784,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="7">
-        <v>6.4</v>
+        <v>6.4000000000000004</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
@@ -1641,21 +1805,21 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="5">
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1664,7 +1828,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="7">
-        <v>4.3</v>
+        <v>4.2999999999999998</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -1685,21 +1849,21 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="5">
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1729,21 +1893,21 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="7">
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1773,21 +1937,21 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="5">
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1817,21 +1981,21 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="5">
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -1861,21 +2025,21 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="5">
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -1905,21 +2069,21 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="5">
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -1949,21 +2113,21 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="7">
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -1993,21 +2157,21 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="5">
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2019,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="G22" s="7">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="H22" s="7">
         <v>1000</v>
@@ -2037,15 +2201,14 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="O22" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2055,7 +2218,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="7" customWidth="1"/>
@@ -2063,44 +2226,44 @@
     <col min="9" max="9" width="19.78515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="7">
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2109,15 +2272,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:7">
       <c r="A3" s="7">
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2126,15 +2289,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:7">
       <c r="A4" s="7">
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2143,15 +2306,15 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9">
       <c r="A5" s="7">
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2161,15 +2324,15 @@
       </c>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:7">
       <c r="A6" s="7">
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2178,15 +2341,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2196,7 +2359,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2206,7 +2368,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="7" customWidth="1"/>
@@ -2218,45 +2380,45 @@
     <col min="10" max="10" width="12.140625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9">
       <c r="A2" s="7">
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2268,47 +2430,47 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="7">
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
       </c>
       <c r="E3" s="7">
-        <v>-0.1</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="F3" s="7">
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="7">
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2320,21 +2482,21 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="7">
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>167</v>
+        <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2346,18 +2508,18 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="7">
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>166</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2369,11 +2531,10 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>2</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2383,45 +2544,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="7" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="7">
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2430,11 +2591,10 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2444,7 +2604,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="7" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="7" customWidth="1"/>
@@ -2456,53 +2616,53 @@
     <col min="13" max="13" width="15.640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="14">
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2511,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2526,18 +2686,18 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="15">
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2546,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2558,31 +2718,31 @@
         <v>1</v>
       </c>
       <c r="K3" s="7">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="15"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:1">
       <c r="A5" s="15"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:2">
       <c r="A6" s="15"/>
       <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:12">
       <c r="A7" s="21">
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2591,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2606,18 +2766,18 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="22">
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2626,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2638,30 +2798,29 @@
         <v>1</v>
       </c>
       <c r="K8" s="7">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="22"/>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:2">
       <c r="A10" s="22"/>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:2">
       <c r="A11" s="23"/>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -2671,7 +2830,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="7" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="7" customWidth="1"/>
@@ -2683,56 +2842,56 @@
     <col min="12" max="13" width="19.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>27</v>
+        <v>161</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="9">
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2741,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2759,18 +2918,18 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="10">
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2779,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2791,24 +2950,24 @@
         <v>1</v>
       </c>
       <c r="K3" s="7">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7">
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="10">
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2817,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2835,18 +2994,18 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="10">
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2855,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -2873,18 +3032,18 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="10">
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -2893,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -2911,18 +3070,18 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="10">
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -2931,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -2949,18 +3108,18 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="10">
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -2969,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -2987,27 +3146,27 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="10"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:1">
       <c r="A10" s="10"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:1">
       <c r="A11" s="10"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:13">
       <c r="A12" s="11">
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3016,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3028,24 +3187,24 @@
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="12">
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3054,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3066,24 +3225,24 @@
         <v>1</v>
       </c>
       <c r="K13" s="7">
-        <v>0.1</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L13" s="7">
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="11">
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3092,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3110,18 +3269,18 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="12">
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3130,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>160</v>
+        <v>6</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3148,18 +3307,18 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="11">
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3168,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3186,18 +3345,18 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="12">
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3206,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3224,18 +3383,18 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="11">
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>9</v>
+        <v>174</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3244,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3262,20 +3421,19 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" s="12"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:1">
       <c r="A20" s="12"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:1">
       <c r="A21" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3285,7 +3443,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="7" customWidth="1"/>
@@ -3296,30 +3454,30 @@
     <col min="7" max="7" width="20.2109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D1" s="25" t="s">
         <v>177</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>15</v>
+        <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="7">
         <v>50001</v>
       </c>
@@ -3333,16 +3491,16 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>50002</v>
       </c>
@@ -3356,16 +3514,16 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>50003</v>
       </c>
@@ -3379,19 +3537,18 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -3399,7 +3556,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="12" style="7" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="7" customWidth="1"/>
@@ -3409,24 +3566,24 @@
     <col min="7" max="7" width="13.92578125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.75">
       <c r="A2" s="14">
         <v>60001</v>
       </c>
@@ -3440,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:4">
       <c r="A3" s="15">
         <v>60002</v>
       </c>
@@ -3454,7 +3611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:4">
       <c r="A4" s="15">
         <v>60003</v>
       </c>
@@ -3462,13 +3619,13 @@
         <v>30003</v>
       </c>
       <c r="C4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:4">
       <c r="A5" s="15">
         <v>60004</v>
       </c>
@@ -3482,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:4">
       <c r="A6" s="15">
         <v>60005</v>
       </c>
@@ -3490,13 +3647,13 @@
         <v>30005</v>
       </c>
       <c r="C6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:4">
       <c r="A7" s="15">
         <v>60006</v>
       </c>
@@ -3510,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:4">
       <c r="A8" s="15">
         <v>60007</v>
       </c>
@@ -3524,7 +3681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:4">
       <c r="A9" s="15">
         <v>60008</v>
       </c>
@@ -3538,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:4">
       <c r="A10" s="15">
         <v>60009</v>
       </c>
@@ -3552,43 +3709,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:4">
       <c r="A11" s="15"/>
       <c r="D11" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:4">
       <c r="A12" s="15"/>
       <c r="D12" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:4">
       <c r="A13" s="15"/>
       <c r="D13" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:4">
       <c r="A14" s="15"/>
       <c r="D14" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:4">
       <c r="A15" s="15"/>
       <c r="D15" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:4" ht="16.75">
       <c r="A16" s="16"/>
       <c r="D16" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:5">
       <c r="A17" s="6">
         <v>61001</v>
       </c>
@@ -3603,7 +3760,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3613,7 +3769,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="7" customWidth="1"/>
@@ -3622,24 +3778,24 @@
     <col min="5" max="5" width="13.78515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.75">
       <c r="A2" s="14">
         <v>70001</v>
       </c>
@@ -3656,7 +3812,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:5">
       <c r="A3" s="15">
         <v>70002</v>
       </c>
@@ -3673,7 +3829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:5">
       <c r="A4" s="15">
         <v>70003</v>
       </c>
@@ -3690,7 +3846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:5">
       <c r="A5" s="15">
         <v>70004</v>
       </c>
@@ -3707,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:5">
       <c r="A6" s="15">
         <v>70005</v>
       </c>
@@ -3724,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:5">
       <c r="A7" s="15">
         <v>70006</v>
       </c>
@@ -3741,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:5">
       <c r="A8" s="15">
         <v>70007</v>
       </c>
@@ -3758,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:5">
       <c r="A9" s="15">
         <v>70008</v>
       </c>
@@ -3775,7 +3931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:5">
       <c r="A10" s="15">
         <v>70009</v>
       </c>
@@ -3792,41 +3948,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:1">
       <c r="A11" s="15"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:1">
       <c r="A12" s="15"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:1">
       <c r="A13" s="15"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:1">
       <c r="A14" s="15"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:1">
       <c r="A15" s="15"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:1" ht="16.75">
       <c r="A16" s="16"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:1">
       <c r="A17" s="17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:1">
       <c r="A18" s="17"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:1">
       <c r="A19" s="17"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:1">
       <c r="A20" s="17"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:1">
       <c r="A21" s="17"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -3836,36 +3991,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="7">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -3875,7 +4029,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="7" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="7" customWidth="1"/>
@@ -3887,44 +4041,44 @@
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="7">
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -3933,15 +4087,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9">
       <c r="A3" s="7">
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -3950,15 +4104,15 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9">
       <c r="A4" s="7">
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -3967,150 +4121,150 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:7">
       <c r="A5" s="7">
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:7">
       <c r="A6" s="7">
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:9">
       <c r="A8" s="7">
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
       </c>
       <c r="I8" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.14999999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="7">
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
       </c>
       <c r="I9" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.14999999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="7">
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
       </c>
       <c r="I10" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
+        <v>0.20000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:7">
       <c r="A12" s="7">
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:7">
       <c r="A13" s="7">
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:8">
       <c r="A14" s="6">
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4119,15 +4273,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:8">
       <c r="A15" s="7">
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4136,15 +4290,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:8">
       <c r="A16" s="7">
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4153,15 +4307,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4170,15 +4324,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:7">
       <c r="A18" s="7">
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4187,15 +4341,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:7">
       <c r="A19" s="8">
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4204,50 +4358,49 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:7">
       <c r="A20" s="8">
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:7">
       <c r="A21" s="8">
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="22" spans="1:7">
       <c r="A22" s="8">
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -25,202 +25,382 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
   <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteMissileTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
   </si>
   <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">stage_inspection_time</t>
   </si>
   <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
@@ -238,325 +418,145 @@
     <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
     <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
   </si>
 </sst>
 </file>
@@ -945,28 +945,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF8FABDB"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1092,15 +1071,13 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="6">
-      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe" size="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="4">
+      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1417,46 +1394,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1464,10 +1441,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1479,16 +1456,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1497,10 +1474,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1508,10 +1485,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1541,10 +1518,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1552,10 +1529,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1588,7 +1565,7 @@
         <v>25</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1596,10 +1573,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1629,10 +1606,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1640,10 +1617,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1676,7 +1653,7 @@
         <v>25</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1684,10 +1661,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1717,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1728,10 +1705,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1761,10 +1738,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1772,10 +1749,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1805,10 +1782,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1816,10 +1793,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1849,10 +1826,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1860,10 +1837,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1893,10 +1870,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1904,10 +1881,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1937,10 +1914,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1951,7 +1928,7 @@
         <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1981,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>32</v>
@@ -1992,10 +1969,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -2025,10 +2002,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2036,10 +2013,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2069,10 +2046,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2083,7 +2060,7 @@
         <v>142</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2124,10 +2101,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2157,10 +2134,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2168,10 +2145,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2201,10 +2178,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2228,31 +2205,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>156</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2260,10 +2237,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2277,10 +2254,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2294,10 +2271,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2311,10 +2288,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2329,10 +2306,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2346,10 +2323,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2382,31 +2359,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2415,10 +2392,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2430,10 +2407,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2441,10 +2418,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2456,10 +2433,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2467,10 +2444,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2482,10 +2459,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2493,10 +2470,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2508,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2516,10 +2493,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2531,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2553,25 +2530,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2579,10 +2556,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2591,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2618,40 +2595,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>156</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2659,10 +2636,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2671,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2686,7 +2663,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2694,10 +2671,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2706,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2721,7 +2698,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2739,10 +2716,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2751,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2766,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2774,10 +2751,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2786,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2801,7 +2778,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2844,43 +2821,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>156</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2888,10 +2865,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2900,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2918,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2926,10 +2903,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2938,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2956,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2964,10 +2941,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2976,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2994,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -3002,10 +2979,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -3014,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -3032,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3040,10 +3017,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3052,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3070,7 +3047,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3078,10 +3055,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3090,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3108,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3116,10 +3093,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3128,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3146,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3163,10 +3140,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3175,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3193,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3201,10 +3178,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3213,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3231,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -3239,10 +3216,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3251,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3269,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3277,10 +3254,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3289,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3307,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3315,10 +3292,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3327,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3345,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3353,10 +3330,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3365,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3383,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3391,10 +3368,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3403,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3421,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3456,25 +3433,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3491,13 +3468,13 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3514,13 +3491,13 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3537,13 +3514,13 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3568,19 +3545,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3619,7 +3596,7 @@
         <v>30003</v>
       </c>
       <c r="C4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="19">
         <v>0</v>
@@ -3647,7 +3624,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="19">
         <v>0</v>
@@ -3780,19 +3757,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -3999,19 +3976,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4043,31 +4020,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>156</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4075,10 +4052,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4092,10 +4069,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4109,10 +4086,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4126,7 +4103,7 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>94</v>
@@ -4140,7 +4117,7 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>94</v>
@@ -4154,7 +4131,7 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>94</v>
@@ -4168,10 +4145,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4185,10 +4162,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4202,10 +4179,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4219,7 +4196,7 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>94</v>
@@ -4233,7 +4210,7 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>94</v>
@@ -4247,7 +4224,7 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>94</v>
@@ -4261,10 +4238,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4278,10 +4255,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4295,10 +4272,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4312,10 +4289,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4329,10 +4306,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4346,10 +4323,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4363,7 +4340,7 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>94</v>
@@ -4377,7 +4354,7 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>94</v>
@@ -4391,7 +4368,7 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>94</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="5"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -23,519 +23,531 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="179">
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
   <si>
     <t xml:space="preserve">weight</t>
   </si>
   <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
     <t xml:space="preserve">icon_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
+    <t xml:space="preserve">귀상어다.</t>
   </si>
   <si>
     <t xml:space="preserve">Spider</t>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
+    <t xml:space="preserve">냉기 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">Hammershark</t>
   </si>
   <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">1;5;5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">10007;10008;10009;10010;</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
@@ -544,19 +556,10 @@
     <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -945,31 +948,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDAE3F3"/>
-          <bgColor rgb="FFDAE3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1071,13 +1050,10 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="4">
-      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="1">
+      <tableStyleElement type="wholeTable" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1394,46 +1370,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1441,10 +1417,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1456,16 +1432,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1474,10 +1450,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1485,10 +1461,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1518,10 +1494,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1529,10 +1505,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1562,10 +1538,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1573,10 +1549,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1606,10 +1582,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1617,10 +1593,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1650,10 +1626,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1661,10 +1637,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1694,10 +1670,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1705,10 +1681,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1738,10 +1714,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1749,10 +1725,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1782,10 +1758,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1793,10 +1769,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1826,10 +1802,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1837,10 +1813,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1870,10 +1846,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1881,10 +1857,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1914,10 +1890,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1925,10 +1901,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1958,10 +1934,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1969,10 +1945,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -2002,10 +1978,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>107</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -2013,10 +1989,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2046,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2057,10 +2033,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2090,10 +2066,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2101,10 +2077,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2134,10 +2110,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2145,10 +2121,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2178,10 +2154,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2205,31 +2181,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2237,10 +2213,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2254,10 +2230,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2271,10 +2247,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2288,10 +2264,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2306,10 +2282,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2323,10 +2299,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2359,31 +2335,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2392,10 +2368,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2407,10 +2383,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2418,10 +2394,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2433,10 +2409,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2444,10 +2420,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2459,10 +2435,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2470,7 +2446,7 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>130</v>
@@ -2485,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2493,10 +2469,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2508,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2530,25 +2506,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2556,10 +2532,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2568,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2595,40 +2571,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2636,10 +2612,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2648,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2663,7 +2639,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2671,10 +2647,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2683,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2698,7 +2674,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2716,10 +2692,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2728,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2743,7 +2719,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2751,10 +2727,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2763,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2778,7 +2754,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2807,7 +2783,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="7" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="7" customWidth="1"/>
@@ -2821,54 +2797,54 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.75">
       <c r="A2" s="9">
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2877,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2895,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2903,10 +2879,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2915,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2933,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2941,10 +2917,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2953,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2971,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2979,10 +2955,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2991,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -3009,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3017,10 +2993,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -3029,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3047,7 +3023,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3055,10 +3031,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3067,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3085,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3093,10 +3069,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3105,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3123,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3135,15 +3111,15 @@
     <row r="11" spans="1:1">
       <c r="A11" s="10"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="16.75">
       <c r="A12" s="11">
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3152,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3170,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3178,10 +3154,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3190,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3208,18 +3184,18 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="16.75">
       <c r="A14" s="11">
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3228,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3246,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3254,10 +3230,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3266,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3284,18 +3260,18 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="16.75">
       <c r="A16" s="11">
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>166</v>
+        <v>60</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3322,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3330,10 +3306,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>111</v>
+        <v>160</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3342,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3360,18 +3336,18 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="16.75">
       <c r="A18" s="11">
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>164</v>
+        <v>71</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3380,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3398,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3407,7 +3383,7 @@
     <row r="20" spans="1:1">
       <c r="A20" s="12"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" ht="16.75">
       <c r="A21" s="13"/>
     </row>
   </sheetData>
@@ -3433,25 +3409,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3468,13 +3444,13 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3491,13 +3467,13 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3514,13 +3490,13 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3545,19 +3521,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3596,7 +3572,7 @@
         <v>30003</v>
       </c>
       <c r="C4" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="19">
         <v>0</v>
@@ -3624,7 +3600,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="19">
         <v>0</v>
@@ -3757,19 +3733,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -3968,7 +3944,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="7" customWidth="1"/>
@@ -3976,19 +3952,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4006,7 +3982,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="7" customWidth="1"/>
     <col min="3" max="3" width="35.0703125" style="7" customWidth="1"/>
@@ -4020,31 +3996,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4052,10 +4028,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4069,10 +4045,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4086,10 +4062,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4103,10 +4079,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4117,10 +4093,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4131,10 +4107,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4145,10 +4121,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4162,10 +4138,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4179,10 +4155,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4196,10 +4172,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4210,10 +4186,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4224,10 +4200,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4238,7 +4214,7 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>174</v>
@@ -4255,7 +4231,7 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>174</v>
@@ -4272,7 +4248,7 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>174</v>
@@ -4289,10 +4265,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4306,10 +4282,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4323,10 +4299,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4340,10 +4316,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4354,10 +4330,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4368,10 +4344,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="4"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -23,60 +23,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="179">
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
   <si>
     <t xml:space="preserve">spawn_monsters_level</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
+    <t xml:space="preserve">10</t>
   </si>
   <si>
     <t xml:space="preserve">곰이다</t>
@@ -85,346 +196,250 @@
     <t xml:space="preserve">거미다</t>
   </si>
   <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
     <t xml:space="preserve">뱀이다</t>
   </si>
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">10004;10005;10006;</t>
   </si>
   <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">ExplosionProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;5;5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
   </si>
   <si>
     <t xml:space="preserve">need_money</t>
   </si>
   <si>
-    <t xml:space="preserve">move_speed</t>
+    <t xml:space="preserve">전기 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">레이저 포탑 강화</t>
@@ -433,130 +448,115 @@
     <t xml:space="preserve">고블린 창병이다</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">엘리트 화염 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">화염 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 전기 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
     <t xml:space="preserve">stat_type</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_type</t>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 저격 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">기관총 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">GiantGoblin</t>
   </si>
   <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
   </si>
   <si>
     <t xml:space="preserve">폭발 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hammershark</t>
   </si>
   <si>
-    <t xml:space="preserve">1;5;5;</t>
-  </si>
-  <si>
     <t xml:space="preserve">spawn_monsters_probability</t>
   </si>
   <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
@@ -948,15 +948,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1050,11 +1042,9 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
+      <tableStyleElement type="headerRow" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="wholeTable" size="1"/>
-    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1"/>
   </tableStyles>
 </styleSheet>
 </file>
@@ -1370,46 +1360,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>133</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1417,7 +1407,7 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>93</v>
@@ -1432,16 +1422,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1450,10 +1440,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1461,10 +1451,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1494,10 +1484,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1505,10 +1495,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1538,10 +1528,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1549,10 +1539,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1582,10 +1572,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1593,10 +1583,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1626,10 +1616,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1637,7 +1627,7 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>107</v>
@@ -1670,10 +1660,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1681,10 +1671,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1714,10 +1704,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1725,10 +1715,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1758,10 +1748,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1769,10 +1759,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1802,10 +1792,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1813,10 +1803,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1846,10 +1836,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1857,10 +1847,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1890,10 +1880,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1901,10 +1891,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1934,10 +1924,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1945,10 +1935,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -1978,10 +1968,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1992,7 +1982,7 @@
         <v>143</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2022,7 +2012,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>143</v>
@@ -2033,10 +2023,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2066,10 +2056,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2077,10 +2067,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2110,10 +2100,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2121,10 +2111,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2154,10 +2144,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2181,31 +2171,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2213,10 +2203,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2230,10 +2220,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2247,10 +2237,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2264,10 +2254,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2282,10 +2272,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2299,10 +2289,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2335,31 +2325,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2368,10 +2358,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2383,10 +2373,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2394,10 +2384,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2409,10 +2399,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2420,10 +2410,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2435,10 +2425,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2446,10 +2436,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2461,7 +2451,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2469,10 +2459,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2484,7 +2474,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2506,25 +2496,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2532,10 +2522,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2544,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2571,40 +2561,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2612,10 +2602,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2624,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2639,7 +2629,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2647,10 +2637,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2659,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2674,7 +2664,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2692,10 +2682,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2704,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2719,7 +2709,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2727,10 +2717,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2739,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2754,7 +2744,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2797,43 +2787,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2841,10 +2831,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2853,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2871,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2879,10 +2869,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2891,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2909,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2917,10 +2907,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2929,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2947,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2958,7 +2948,7 @@
         <v>91</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2967,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -2985,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2993,7 +2983,7 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>178</v>
@@ -3005,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3023,7 +3013,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3031,10 +3021,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3043,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3061,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3069,10 +3059,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3081,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3099,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3116,10 +3106,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3128,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3146,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3154,10 +3144,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3166,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3184,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3195,7 +3185,7 @@
         <v>165</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3204,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3222,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3230,10 +3220,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3242,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3260,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3268,10 +3258,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3280,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3298,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3306,10 +3296,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7">
         <v>150</v>
@@ -3318,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3336,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3344,10 +3334,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3356,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3374,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3409,25 +3399,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>72</v>
-      </c>
       <c r="D1" s="25" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>168</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3444,13 +3434,13 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3467,13 +3457,13 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3490,13 +3480,13 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3521,19 +3511,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3572,7 +3562,7 @@
         <v>30003</v>
       </c>
       <c r="C4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="19">
         <v>0</v>
@@ -3614,7 +3604,7 @@
         <v>30006</v>
       </c>
       <c r="C7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="19">
         <v>0</v>
@@ -3733,19 +3723,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -3952,19 +3942,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3996,31 +3986,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4028,10 +4018,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4045,10 +4035,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4062,10 +4052,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4079,10 +4069,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4093,10 +4083,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4107,10 +4097,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4121,10 +4111,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4138,10 +4128,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4155,10 +4145,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4172,10 +4162,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4186,10 +4176,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4200,10 +4190,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4214,10 +4204,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4231,10 +4221,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4248,10 +4238,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4265,10 +4255,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4282,10 +4272,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4299,10 +4289,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4316,10 +4306,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4330,10 +4320,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4344,10 +4334,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -25,541 +25,541 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="179">
   <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
     <t xml:space="preserve">AttackInterval</t>
   </si>
   <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
   </si>
   <si>
     <t xml:space="preserve">drop_exp_min</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
   </si>
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>
   <si>
-    <t xml:space="preserve">target_train_id</t>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
     <t xml:space="preserve">drop_money_min</t>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;5;5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;5;5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
 </sst>
 </file>
@@ -948,23 +948,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1041,9 +1025,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="headerRow" size="1"/>
-    </tableStyle>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="1"/>
   </tableStyles>
 </styleSheet>
@@ -1360,46 +1342,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1407,10 +1389,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="D2" s="7">
         <v>10</v>
@@ -1422,16 +1404,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I2" s="7">
         <v>10</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -1440,10 +1422,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1451,10 +1433,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="D3" s="5">
         <v>35</v>
@@ -1484,10 +1466,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1495,10 +1477,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="D4" s="5">
         <v>50</v>
@@ -1528,10 +1510,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1539,10 +1521,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5">
         <v>60</v>
@@ -1572,10 +1554,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1583,10 +1565,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D6" s="5">
         <v>40</v>
@@ -1616,10 +1598,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1627,10 +1609,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D7" s="5">
         <v>200</v>
@@ -1660,10 +1642,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1671,10 +1653,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D8" s="5">
         <v>40</v>
@@ -1704,10 +1686,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1715,10 +1697,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D9" s="5">
         <v>70</v>
@@ -1748,10 +1730,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1759,10 +1741,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D10" s="5">
         <v>100</v>
@@ -1792,10 +1774,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1803,10 +1785,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D11" s="5">
         <v>150</v>
@@ -1836,10 +1818,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1847,10 +1829,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="D12" s="5">
         <v>30</v>
@@ -1880,10 +1862,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1891,10 +1873,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D13" s="5">
         <v>100</v>
@@ -1924,10 +1906,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1935,10 +1917,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>163</v>
+        <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5">
         <v>250</v>
@@ -1968,10 +1950,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>163</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1979,10 +1961,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D15" s="5">
         <v>60</v>
@@ -2012,10 +1994,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -2023,10 +2005,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D16" s="5">
         <v>60</v>
@@ -2056,10 +2038,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -2067,10 +2049,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="D17" s="5">
         <v>300</v>
@@ -2100,10 +2082,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2111,10 +2093,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D22" s="5">
         <v>500</v>
@@ -2144,10 +2126,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="O22" s="2"/>
     </row>
@@ -2171,31 +2153,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2203,10 +2185,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F2" s="7">
         <v>1</v>
@@ -2220,10 +2202,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2237,10 +2219,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2254,10 +2236,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2272,10 +2254,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F6" s="7">
         <v>1</v>
@@ -2289,10 +2271,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="F7" s="7">
         <v>1</v>
@@ -2325,31 +2307,31 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="J1" s="8"/>
     </row>
@@ -2358,10 +2340,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2373,10 +2355,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2384,10 +2366,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="D3" s="7">
         <v>200</v>
@@ -2399,10 +2381,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2410,10 +2392,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="D4" s="7">
         <v>50</v>
@@ -2425,10 +2407,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2436,10 +2418,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="D5" s="7">
         <v>300</v>
@@ -2451,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2459,10 +2441,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="D6" s="7">
         <v>500</v>
@@ -2474,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2496,25 +2478,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2522,10 +2504,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2534,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2561,40 +2543,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>51</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2602,10 +2584,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2614,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="H2" s="7">
         <v>5</v>
@@ -2629,7 +2611,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2637,10 +2619,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2649,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="H3" s="7">
         <v>5</v>
@@ -2664,7 +2646,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -2682,10 +2664,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="7">
         <v>150</v>
@@ -2694,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H7" s="7">
         <v>8</v>
@@ -2709,7 +2691,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2717,10 +2699,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7">
         <v>150</v>
@@ -2729,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="H8" s="7">
         <v>13</v>
@@ -2744,7 +2726,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2787,43 +2769,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>51</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16.75">
@@ -2831,10 +2813,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7">
         <v>100</v>
@@ -2843,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="H2" s="7">
         <v>10</v>
@@ -2861,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2869,10 +2851,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="D3" s="7">
         <v>100</v>
@@ -2881,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" s="7">
         <v>10</v>
@@ -2899,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2907,10 +2889,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="D4" s="7">
         <v>100</v>
@@ -2919,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="H4" s="7">
         <v>10</v>
@@ -2937,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2945,10 +2927,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="D5" s="7">
         <v>100</v>
@@ -2957,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="H5" s="7">
         <v>15</v>
@@ -2975,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2983,10 +2965,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="D6" s="7">
         <v>100</v>
@@ -2995,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
@@ -3013,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3021,10 +3003,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D7" s="7">
         <v>100</v>
@@ -3033,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="H7" s="7">
         <v>10</v>
@@ -3051,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -3059,10 +3041,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D8" s="7">
         <v>100</v>
@@ -3071,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="H8" s="7">
         <v>10</v>
@@ -3089,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3106,10 +3088,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="D12" s="7">
         <v>150</v>
@@ -3118,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -3136,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -3144,10 +3126,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D13" s="7">
         <v>150</v>
@@ -3156,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="H13" s="7">
         <v>10</v>
@@ -3174,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>48</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="16.75">
@@ -3182,10 +3164,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>165</v>
+        <v>7</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D14" s="7">
         <v>150</v>
@@ -3194,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="H14" s="7">
         <v>10</v>
@@ -3212,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -3220,10 +3202,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="D15" s="7">
         <v>150</v>
@@ -3232,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
@@ -3250,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.75">
@@ -3258,10 +3240,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7">
         <v>150</v>
@@ -3270,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="H16" s="7">
         <v>10</v>
@@ -3288,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3296,7 +3278,7 @@
         <v>31006</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>12</v>
@@ -3308,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="H17" s="7">
         <v>10</v>
@@ -3326,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.75">
@@ -3334,10 +3316,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D18" s="7">
         <v>150</v>
@@ -3346,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>39</v>
+        <v>176</v>
       </c>
       <c r="H18" s="7">
         <v>10</v>
@@ -3364,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3399,25 +3381,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3434,13 +3416,13 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3457,13 +3439,13 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3480,13 +3462,13 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3511,19 +3493,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.75">
@@ -3576,7 +3558,7 @@
         <v>30004</v>
       </c>
       <c r="C5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="19">
         <v>0</v>
@@ -3590,7 +3572,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="19">
         <v>0</v>
@@ -3604,7 +3586,7 @@
         <v>30006</v>
       </c>
       <c r="C7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="19">
         <v>0</v>
@@ -3723,19 +3705,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.75">
@@ -3942,19 +3924,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3986,31 +3968,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4018,10 +4000,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G2" s="7">
         <v>5</v>
@@ -4035,10 +4017,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -4052,10 +4034,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G4" s="7">
         <v>25</v>
@@ -4069,10 +4051,10 @@
         <v>90002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G5" s="7">
         <v>2</v>
@@ -4083,10 +4065,10 @@
         <v>90002</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G6" s="7">
         <v>5</v>
@@ -4097,10 +4079,10 @@
         <v>90002</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -4111,10 +4093,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G8" s="7">
         <v>15</v>
@@ -4128,10 +4110,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G9" s="7">
         <v>20</v>
@@ -4145,10 +4127,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G10" s="7">
         <v>40</v>
@@ -4162,10 +4144,10 @@
         <v>90004</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G11" s="7">
         <v>50</v>
@@ -4176,10 +4158,10 @@
         <v>90004</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G12" s="7">
         <v>150</v>
@@ -4190,10 +4172,10 @@
         <v>90004</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G13" s="7">
         <v>250</v>
@@ -4204,10 +4186,10 @@
         <v>90005</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="G14" s="7">
         <v>3</v>
@@ -4221,10 +4203,10 @@
         <v>90005</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="G15" s="7">
         <v>5</v>
@@ -4238,10 +4220,10 @@
         <v>90005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="G16" s="7">
         <v>7</v>
@@ -4255,10 +4237,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
@@ -4272,10 +4254,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
@@ -4289,10 +4271,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -4306,10 +4288,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4320,10 +4302,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G21" s="7">
         <v>150</v>
@@ -4334,10 +4316,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="G22" s="7">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" activeTab="2"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="198">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -238,9 +238,6 @@
     <t xml:space="preserve">고블린 주술사다</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">미사일 포탑 강화</t>
   </si>
   <si>
@@ -469,9 +466,6 @@
     <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">CannonProjectile</t>
   </si>
   <si>
@@ -493,9 +487,6 @@
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
   </si>
   <si>
@@ -523,9 +514,6 @@
     <t xml:space="preserve">EliteLaserTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-  </si>
-  <si>
     <t xml:space="preserve">spawn_monsters_level</t>
   </si>
   <si>
@@ -533,12 +521,6 @@
   </si>
   <si>
     <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
   </si>
   <si>
     <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
@@ -602,6 +584,60 @@
   <si>
     <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {2} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {3} 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5853&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;증가&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5853&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5854&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5855&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5856&gt;증가&lt;/color&gt;</t>
   </si>
 </sst>
 </file>
@@ -609,7 +645,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -618,6 +654,13 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -779,7 +822,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,35 +907,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b/>
@@ -1047,23 +1069,21 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="9">
-      <tableStyleElement type="wholeTable" dxfId="13"/>
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="totalRow" dxfId="11"/>
-      <tableStyleElement type="firstColumn" dxfId="10"/>
-      <tableStyleElement type="lastColumn" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" dxfId="8"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstColumn" dxfId="8"/>
+      <tableStyleElement type="lastColumn" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="8">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="5">
+      <tableStyleElement type="wholeTable" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="totalRow" dxfId="2"/>
+      <tableStyleElement type="firstColumn" dxfId="1"/>
+      <tableStyleElement type="lastColumn"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1390,13 +1410,13 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
@@ -1408,28 +1428,28 @@
         <v>50</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.55">
@@ -1452,16 +1472,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I2" s="8">
         <v>10</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K2" s="8">
         <v>10</v>
@@ -1569,7 +1589,7 @@
         <v>10004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>44</v>
@@ -1605,7 +1625,7 @@
         <v>33</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.55">
@@ -1704,7 +1724,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="6">
         <v>40</v>
@@ -1748,7 +1768,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" s="6">
         <v>70</v>
@@ -1836,7 +1856,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="6">
         <v>150</v>
@@ -1924,7 +1944,7 @@
         <v>43</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="6">
         <v>100</v>
@@ -1965,7 +1985,7 @@
         <v>10013</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>16</v>
@@ -2001,7 +2021,7 @@
         <v>33</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.55">
@@ -2053,7 +2073,7 @@
         <v>10015</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>68</v>
@@ -2089,7 +2109,7 @@
         <v>45</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.55">
@@ -2195,20 +2215,20 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="27.5" style="8" customWidth="1"/>
+    <col min="3" max="3" width="71.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="15.640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
@@ -2217,16 +2237,16 @@
         <v>40</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="I1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
@@ -2234,10 +2254,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>169</v>
+        <v>70</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>192</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -2251,10 +2271,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>169</v>
+        <v>70</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>193</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -2268,10 +2288,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>169</v>
+        <v>70</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>194</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -2285,10 +2305,10 @@
         <v>100002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>169</v>
+        <v>73</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>195</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -2303,10 +2323,10 @@
         <v>100002</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>169</v>
+        <v>73</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>196</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -2320,10 +2340,10 @@
         <v>100002</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>169</v>
+        <v>73</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>197</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -2357,28 +2377,28 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>48</v>
@@ -2389,11 +2409,11 @@
       <c r="A2" s="8">
         <v>110001</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>146</v>
+      <c r="B2" s="28" t="s">
+        <v>182</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2405,10 +2425,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55">
@@ -2416,7 +2436,7 @@
         <v>110002</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>0</v>
@@ -2431,10 +2451,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55">
@@ -2442,10 +2462,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D4" s="8">
         <v>50</v>
@@ -2457,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>22</v>
@@ -2468,7 +2488,7 @@
         <v>110004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>4</v>
@@ -2483,7 +2503,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55">
@@ -2491,7 +2511,7 @@
         <v>110005</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>3</v>
@@ -2506,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2529,22 +2549,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>40</v>
@@ -2558,7 +2578,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2596,40 +2616,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="K1" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -2640,7 +2660,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2649,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H2" s="8">
         <v>5</v>
@@ -2667,7 +2687,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -2687,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H3" s="8">
         <v>5</v>
@@ -2705,7 +2725,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55">
@@ -2723,10 +2743,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" s="8">
         <v>150</v>
@@ -2735,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H7" s="8">
         <v>8</v>
@@ -2750,7 +2770,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55">
@@ -2761,7 +2781,7 @@
         <v>57</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D8" s="8">
         <v>150</v>
@@ -2770,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="H8" s="8">
         <v>13</v>
@@ -2785,7 +2805,7 @@
         <v>0.1</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55">
@@ -2830,43 +2850,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="K1" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -2877,7 +2897,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2886,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="H2" s="8">
         <v>10</v>
@@ -2907,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55">
@@ -2918,7 +2938,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="8">
         <v>100</v>
@@ -2927,10 +2947,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H3" s="8">
         <v>10</v>
@@ -2948,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55">
@@ -2959,7 +2979,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2968,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H4" s="8">
         <v>10</v>
@@ -2989,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55">
@@ -3000,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -3009,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H5" s="8">
         <v>15</v>
@@ -3030,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55">
@@ -3041,7 +3061,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D6" s="8">
         <v>100</v>
@@ -3050,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H6" s="8">
         <v>10</v>
@@ -3071,7 +3091,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55">
@@ -3091,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H7" s="8">
         <v>10</v>
@@ -3112,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55">
@@ -3123,7 +3143,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -3132,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H8" s="8">
         <v>10</v>
@@ -3153,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55">
@@ -3170,10 +3190,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" s="8">
         <v>150</v>
@@ -3182,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H12" s="2">
         <v>10</v>
@@ -3200,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55">
@@ -3211,7 +3231,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" s="8">
         <v>150</v>
@@ -3220,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H13" s="8">
         <v>10</v>
@@ -3238,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55">
@@ -3246,10 +3266,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D14" s="8">
         <v>150</v>
@@ -3258,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H14" s="8">
         <v>10</v>
@@ -3276,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55">
@@ -3284,10 +3304,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D15" s="8">
         <v>150</v>
@@ -3296,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H15" s="8">
         <v>10</v>
@@ -3314,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55">
@@ -3325,7 +3345,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D16" s="8">
         <v>150</v>
@@ -3334,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H16" s="8">
         <v>10</v>
@@ -3352,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55">
@@ -3363,7 +3383,7 @@
         <v>67</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="8">
         <v>150</v>
@@ -3372,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H17" s="8">
         <v>10</v>
@@ -3390,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55">
@@ -3401,7 +3421,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D18" s="8">
         <v>150</v>
@@ -3410,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H18" s="8">
         <v>10</v>
@@ -3428,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55">
@@ -3464,25 +3484,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -3499,7 +3519,7 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>6</v>
@@ -3522,7 +3542,7 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>6</v>
@@ -3545,7 +3565,7 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>60</v>
@@ -3577,10 +3597,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>30</v>
@@ -3589,7 +3609,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -3790,13 +3810,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>30</v>
@@ -4010,13 +4030,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
@@ -4044,7 +4064,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="35.0703125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="88.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="14.140625" style="8" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="8" customWidth="1"/>
@@ -4055,13 +4075,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>42</v>
@@ -4070,16 +4090,16 @@
         <v>40</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="I1" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
@@ -4089,8 +4109,8 @@
       <c r="B2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>164</v>
+      <c r="C2" s="28" t="s">
+        <v>184</v>
       </c>
       <c r="G2" s="8">
         <v>5</v>
@@ -4106,8 +4126,8 @@
       <c r="B3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>164</v>
+      <c r="C3" s="28" t="s">
+        <v>185</v>
       </c>
       <c r="G3" s="8">
         <v>10</v>
@@ -4123,8 +4143,8 @@
       <c r="B4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>164</v>
+      <c r="C4" s="28" t="s">
+        <v>186</v>
       </c>
       <c r="G4" s="8">
         <v>25</v>
@@ -4140,8 +4160,8 @@
       <c r="B5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>69</v>
+      <c r="C5" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G5" s="8">
         <v>2</v>
@@ -4154,8 +4174,8 @@
       <c r="B6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>69</v>
+      <c r="C6" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
@@ -4168,8 +4188,8 @@
       <c r="B7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>69</v>
+      <c r="C7" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G7" s="8">
         <v>10</v>
@@ -4180,10 +4200,10 @@
         <v>90003</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>164</v>
+        <v>69</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>184</v>
       </c>
       <c r="G8" s="8">
         <v>15</v>
@@ -4197,10 +4217,10 @@
         <v>90003</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>164</v>
+        <v>69</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>185</v>
       </c>
       <c r="G9" s="8">
         <v>20</v>
@@ -4214,10 +4234,10 @@
         <v>90003</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>164</v>
+        <v>69</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>186</v>
       </c>
       <c r="G10" s="8">
         <v>40</v>
@@ -4233,8 +4253,8 @@
       <c r="B11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>69</v>
+      <c r="C11" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G11" s="8">
         <v>50</v>
@@ -4247,8 +4267,8 @@
       <c r="B12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>69</v>
+      <c r="C12" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G12" s="8">
         <v>150</v>
@@ -4261,8 +4281,8 @@
       <c r="B13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>69</v>
+      <c r="C13" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G13" s="8">
         <v>250</v>
@@ -4275,8 +4295,8 @@
       <c r="B14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>154</v>
+      <c r="C14" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G14" s="8">
         <v>3</v>
@@ -4292,8 +4312,8 @@
       <c r="B15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>154</v>
+      <c r="C15" s="28" t="s">
+        <v>187</v>
       </c>
       <c r="G15" s="8">
         <v>5</v>
@@ -4309,8 +4329,8 @@
       <c r="B16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>154</v>
+      <c r="C16" s="28" t="s">
+        <v>188</v>
       </c>
       <c r="G16" s="8">
         <v>7</v>
@@ -4324,10 +4344,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>168</v>
+        <v>77</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>189</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
@@ -4341,10 +4361,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>168</v>
+        <v>77</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>190</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -4358,10 +4378,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>168</v>
+        <v>77</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>191</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -4377,8 +4397,8 @@
       <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>69</v>
+      <c r="C20" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G20" s="8">
         <v>50</v>
@@ -4391,8 +4411,8 @@
       <c r="B21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>69</v>
+      <c r="C21" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G21" s="8">
         <v>150</v>
@@ -4405,8 +4425,8 @@
       <c r="B22" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>69</v>
+      <c r="C22" s="28" t="s">
+        <v>183</v>
       </c>
       <c r="G22" s="8">
         <v>350</v>
@@ -4415,6 +4435,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -3,8 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D2C64-4450-4ACE-B87F-43BB8075E71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="4" activeTab="10"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -19,632 +25,648 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="198">
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="203">
+  <si>
+    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>해골 병사다.</t>
+  </si>
+  <si>
+    <t>1;1;1;</t>
+  </si>
+  <si>
+    <t>tier</t>
+  </si>
+  <si>
+    <t>레이저 포탑</t>
+  </si>
+  <si>
+    <t>전기 포탑</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>Dwarf</t>
+  </si>
+  <si>
+    <t>Panda</t>
+  </si>
+  <si>
+    <t>고블린 거인</t>
+  </si>
+  <si>
+    <t>도적이다.</t>
+  </si>
+  <si>
+    <t>메인 기차</t>
+  </si>
+  <si>
+    <t>미노타우로스다</t>
+  </si>
+  <si>
+    <t>거북이다</t>
+  </si>
+  <si>
+    <t>Lizard</t>
+  </si>
+  <si>
+    <t>난쟁이다</t>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+  </si>
+  <si>
+    <t>Skull</t>
+  </si>
+  <si>
+    <t>MaxHp</t>
+  </si>
+  <si>
+    <t>포격 포탑</t>
+  </si>
+  <si>
+    <t>Thief</t>
+  </si>
+  <si>
+    <t>저격 포탑</t>
+  </si>
+  <si>
+    <t>폭발 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">상어다 </t>
   </si>
   <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;5;5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거미다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">판다다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSorcerer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>Gnoll</t>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>놀이다.</t>
+  </si>
+  <si>
+    <t>Turtle</t>
+  </si>
+  <si>
+    <t>도마뱀이다</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+  </si>
+  <si>
+    <t>Bear</t>
+  </si>
+  <si>
+    <t>해골 왕이당.</t>
+  </si>
+  <si>
+    <t>icon_id</t>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>Spider</t>
+  </si>
+  <si>
+    <t>귀상어다.</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>1;5;5;</t>
+  </si>
+  <si>
+    <t>엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t>stat_type</t>
+  </si>
+  <si>
+    <t>엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t>move_speed</t>
+  </si>
+  <si>
+    <t>전기 포탑 강화</t>
+  </si>
+  <si>
+    <t>need_money</t>
+  </si>
+  <si>
+    <t>고블린 창병이다</t>
+  </si>
+  <si>
+    <t>MainTrain</t>
+  </si>
+  <si>
+    <t>화염 포탑 강화</t>
+  </si>
+  <si>
+    <t>attack_type</t>
+  </si>
+  <si>
+    <t>엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t>엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t>레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t>1;1;1;1;</t>
+  </si>
+  <si>
+    <t>GoblinSpear</t>
+  </si>
+  <si>
+    <t>SkullKing</t>
+  </si>
+  <si>
+    <t>기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t>GiantGoblin</t>
+  </si>
+  <si>
+    <t>train_name</t>
+  </si>
+  <si>
+    <t>저격 포탑 강화</t>
+  </si>
+  <si>
+    <t>엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t>고블린 주술사다</t>
+  </si>
+  <si>
+    <t>미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t>폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t>엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t>prefab_id</t>
+  </si>
+  <si>
+    <t>엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t>엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t>포격 포탑 강화</t>
+  </si>
+  <si>
+    <t>Hammershark</t>
+  </si>
+  <si>
+    <t>Minotaur</t>
+  </si>
+  <si>
+    <t>엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>거미다</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>뱀이다</t>
+  </si>
+  <si>
+    <t>곰이다</t>
+  </si>
+  <si>
+    <t>판다다</t>
+  </si>
+  <si>
+    <t>GoblinSorcerer</t>
+  </si>
+  <si>
+    <t>폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>upgrade_type</t>
+  </si>
+  <si>
+    <t>drop_exp_min</t>
+  </si>
+  <si>
+    <t>upgrade_value</t>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t>target_count</t>
+  </si>
+  <si>
+    <t>NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t>upgrade_name</t>
+  </si>
+  <si>
+    <t>체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t>monster_name</t>
+  </si>
+  <si>
+    <t>포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>AttackInterval</t>
+  </si>
+  <si>
+    <t>FireTurretTrain</t>
+  </si>
+  <si>
+    <t>전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>AttackDamage</t>
+  </si>
+  <si>
+    <t>attack_delay</t>
+  </si>
+  <si>
+    <t>stage_end_time</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>train_data_id</t>
+  </si>
+  <si>
+    <t>attack_range</t>
+  </si>
+  <si>
+    <t>attack_count</t>
+  </si>
+  <si>
+    <t>제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t>target_train_id</t>
+  </si>
+  <si>
+    <t>냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>drop_money_min</t>
+  </si>
+  <si>
+    <t>drop_exp_max</t>
+  </si>
+  <si>
+    <t>spawn_monsters</t>
+  </si>
+  <si>
+    <t>LaserProjectile</t>
+  </si>
+  <si>
+    <t>drop_money_max</t>
+  </si>
+  <si>
+    <t>attack_damage</t>
+  </si>
+  <si>
+    <t>spawn_interval</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>TrainUpgrade</t>
+  </si>
+  <si>
+    <t>SniperProjectile</t>
+  </si>
+  <si>
+    <t>10001;10002;10003;</t>
+  </si>
+  <si>
+    <t>ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t>MissileTurretTrain</t>
+  </si>
+  <si>
+    <t>replace_train_id</t>
+  </si>
+  <si>
+    <t>공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t>레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>NormalTurretTrain</t>
+  </si>
+  <si>
+    <t>미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>LaserTurretTrain</t>
+  </si>
+  <si>
+    <t>ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t>max_upgrade_count</t>
+  </si>
+  <si>
+    <t>NormalProjectile</t>
+  </si>
+  <si>
+    <t>10004;10005;10006;</t>
+  </si>
+  <si>
+    <t>ElectrickProjectile</t>
+  </si>
+  <si>
+    <t>CannonTurretTrain</t>
+  </si>
+  <si>
+    <t>SniperTurretTrain</t>
+  </si>
+  <si>
+    <t>ExplosionProjectile</t>
+  </si>
+  <si>
+    <t>기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t>weighted_upgrades</t>
+  </si>
+  <si>
+    <t>CannonProjectile</t>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
+  </si>
+  <si>
+    <t>ColdAirProjectile</t>
+  </si>
+  <si>
+    <t>spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t>EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t>EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t>10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t>EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t>EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t>EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t>spawn_monsters_level</t>
+  </si>
+  <si>
+    <t>레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t>stage_inspection_time</t>
+  </si>
+  <si>
+    <t>획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t>EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t>projectile_prefab_id</t>
+  </si>
+  <si>
+    <t>EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t>획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t>EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t>EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t>FireEffectProjectile</t>
+  </si>
+  <si>
+    <t>ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_KMD_08_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+    <t>Weapon_MEL_05_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+    <t>Weapon_KMD_10_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
+    <t>Weapon_288_19_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+    <t>Weapon_MEL_16_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+    <t>Weapon_MEL_14_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+    <t>Weapon_KMD_12_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
+    <t>절대무적_요새_288버켓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+    <t>절대무적_요새_멜리에스클래식_몸통뉴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+    <t>공격력 {0}/{1} % 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {1} 감소</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {1} 감소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {2} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {3} 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {2} 감소</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {3} 감소</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5853&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;증가&lt;/color&gt;</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5853&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;증가&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5853&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5854&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5855&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5856&gt;증가&lt;/color&gt;</t>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5852&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5853&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5854&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5855&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5856&gt;증가&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t>Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t>Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t>절대무적_요새_288버켓</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -904,27 +926,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <b/>
@@ -1069,29 +1081,27 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="11"/>
-      <tableStyleElement type="headerRow" dxfId="10"/>
-      <tableStyleElement type="totalRow" dxfId="9"/>
-      <tableStyleElement type="firstColumn" dxfId="8"/>
-      <tableStyleElement type="lastColumn" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="8"/>
+      <tableStyleElement type="totalRow" dxfId="7"/>
+      <tableStyleElement type="firstColumn" dxfId="6"/>
+      <tableStyleElement type="lastColumn" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="3"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="5">
-      <tableStyleElement type="wholeTable" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="totalRow" dxfId="2"/>
-      <tableStyleElement type="firstColumn" dxfId="1"/>
-      <tableStyleElement type="lastColumn"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" dxfId="2"/>
+      <tableStyleElement type="headerRow" dxfId="1"/>
+      <tableStyleElement type="totalRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1388,10 +1398,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="8" customWidth="1"/>
@@ -1408,7 +1418,7 @@
     <col min="14" max="14" width="13.35546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -1452,7 +1462,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>10001</v>
       </c>
@@ -1496,7 +1506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>10002</v>
       </c>
@@ -1540,7 +1550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6">
         <v>10003</v>
       </c>
@@ -1584,7 +1594,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6">
         <v>10004</v>
       </c>
@@ -1628,7 +1638,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6">
         <v>10005</v>
       </c>
@@ -1672,7 +1682,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8">
         <v>10006</v>
       </c>
@@ -1716,7 +1726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6">
         <v>10007</v>
       </c>
@@ -1760,7 +1770,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6">
         <v>10008</v>
       </c>
@@ -1804,7 +1814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6">
         <v>10009</v>
       </c>
@@ -1848,7 +1858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6">
         <v>10010</v>
       </c>
@@ -1892,7 +1902,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8">
         <v>10011</v>
       </c>
@@ -1936,7 +1946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6">
         <v>10012</v>
       </c>
@@ -1980,7 +1990,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6">
         <v>10013</v>
       </c>
@@ -2024,7 +2034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6">
         <v>10014</v>
       </c>
@@ -2068,7 +2078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6">
         <v>10015</v>
       </c>
@@ -2112,7 +2122,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8">
         <v>10016</v>
       </c>
@@ -2156,7 +2166,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6">
         <v>10100</v>
       </c>
@@ -2203,16 +2213,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="71.85546875" style="8" bestFit="1" customWidth="1"/>
@@ -2220,7 +2230,7 @@
     <col min="9" max="9" width="19.78515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2249,15 +2259,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>100001</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>192</v>
+      <c r="C2" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>179</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -2266,15 +2279,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8">
         <v>100001</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>193</v>
+      <c r="C3" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -2283,15 +2299,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8">
         <v>100001</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>194</v>
+      <c r="C4" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -2300,15 +2319,18 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8">
         <v>100002</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>195</v>
+      <c r="C5" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>178</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -2318,15 +2340,18 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8">
         <v>100002</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>196</v>
+      <c r="C6" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -2335,15 +2360,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8">
         <v>100002</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>197</v>
+      <c r="C7" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -2354,16 +2382,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="8" customWidth="1"/>
@@ -2375,7 +2403,7 @@
     <col min="10" max="10" width="12.140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2405,15 +2433,15 @@
       </c>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>110001</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>182</v>
+      <c r="B2" s="27" t="s">
+        <v>180</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2431,7 +2459,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8">
         <v>110002</v>
       </c>
@@ -2457,7 +2485,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8">
         <v>110003</v>
       </c>
@@ -2465,7 +2493,7 @@
         <v>97</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D4" s="8">
         <v>50</v>
@@ -2483,12 +2511,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8">
         <v>110004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>4</v>
@@ -2506,12 +2534,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8">
         <v>110005</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>3</v>
@@ -2531,23 +2559,23 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="8" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2570,7 +2598,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>20001</v>
       </c>
@@ -2592,16 +2620,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="8" customWidth="1"/>
@@ -2614,7 +2642,7 @@
     <col min="13" max="13" width="15.640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2649,10 +2677,10 @@
         <v>106</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>40001</v>
       </c>
@@ -2660,7 +2688,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2671,8 +2699,8 @@
       <c r="F2" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>181</v>
+      <c r="G2" s="28" t="s">
+        <v>179</v>
       </c>
       <c r="H2" s="8">
         <v>5</v>
@@ -2690,7 +2718,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16">
         <v>40002</v>
       </c>
@@ -2709,8 +2737,8 @@
       <c r="F3" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>180</v>
+      <c r="G3" s="28" t="s">
+        <v>178</v>
       </c>
       <c r="H3" s="8">
         <v>5</v>
@@ -2725,20 +2753,20 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="16"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="16"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="22">
         <v>41001</v>
       </c>
@@ -2755,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="8">
         <v>8</v>
@@ -2773,7 +2801,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="23">
         <v>41002</v>
       </c>
@@ -2790,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H8" s="8">
         <v>13</v>
@@ -2805,37 +2833,37 @@
         <v>0.1</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="23"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="23"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="24"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="8" customWidth="1"/>
@@ -2848,7 +2876,7 @@
     <col min="12" max="13" width="19.28515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2886,10 +2914,10 @@
         <v>94</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="10">
         <v>30001</v>
       </c>
@@ -2908,8 +2936,8 @@
       <c r="F2" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>173</v>
+      <c r="G2" s="28" t="s">
+        <v>171</v>
       </c>
       <c r="H2" s="8">
         <v>10</v>
@@ -2930,15 +2958,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11">
         <v>30002</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>144</v>
+      <c r="C3" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="D3" s="8">
         <v>100</v>
@@ -2949,8 +2977,8 @@
       <c r="F3" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>174</v>
+      <c r="G3" s="28" t="s">
+        <v>172</v>
       </c>
       <c r="H3" s="8">
         <v>10</v>
@@ -2968,18 +2996,18 @@
         <v>0</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="11">
         <v>30003</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>156</v>
+      <c r="C4" s="27" t="s">
+        <v>198</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2990,8 +3018,8 @@
       <c r="F4" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>175</v>
+      <c r="G4" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="H4" s="8">
         <v>10</v>
@@ -3009,10 +3037,10 @@
         <v>0</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="11">
         <v>30004</v>
       </c>
@@ -3020,7 +3048,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -3031,8 +3059,8 @@
       <c r="F5" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>176</v>
+      <c r="G5" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="H5" s="8">
         <v>15</v>
@@ -3053,7 +3081,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="11">
         <v>30005</v>
       </c>
@@ -3061,7 +3089,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D6" s="8">
         <v>100</v>
@@ -3070,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>177</v>
+        <v>170</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>175</v>
       </c>
       <c r="H6" s="8">
         <v>10</v>
@@ -3094,7 +3122,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11">
         <v>30006</v>
       </c>
@@ -3113,8 +3141,8 @@
       <c r="F7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="27" t="s">
-        <v>178</v>
+      <c r="G7" s="28" t="s">
+        <v>176</v>
       </c>
       <c r="H7" s="8">
         <v>10</v>
@@ -3132,10 +3160,10 @@
         <v>0</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="11">
         <v>30007</v>
       </c>
@@ -3143,7 +3171,7 @@
         <v>25</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -3154,8 +3182,8 @@
       <c r="F8" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="27" t="s">
-        <v>179</v>
+      <c r="G8" s="28" t="s">
+        <v>177</v>
       </c>
       <c r="H8" s="8">
         <v>10</v>
@@ -3176,16 +3204,16 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="12">
         <v>31001</v>
       </c>
@@ -3202,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H12" s="2">
         <v>10</v>
@@ -3223,7 +3251,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13">
         <v>31002</v>
       </c>
@@ -3240,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H13" s="8">
         <v>10</v>
@@ -3258,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="12">
         <v>31003</v>
       </c>
@@ -3278,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H14" s="8">
         <v>10</v>
@@ -3296,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="13">
         <v>31004</v>
       </c>
@@ -3316,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H15" s="8">
         <v>10</v>
@@ -3337,7 +3365,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="12">
         <v>31005</v>
       </c>
@@ -3354,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H16" s="8">
         <v>10</v>
@@ -3375,7 +3403,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="13">
         <v>31006</v>
       </c>
@@ -3392,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H17" s="8">
         <v>10</v>
@@ -3410,10 +3438,10 @@
         <v>0</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="12">
         <v>31007</v>
       </c>
@@ -3430,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H18" s="8">
         <v>10</v>
@@ -3451,27 +3479,27 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="13"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="13"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="8" customWidth="1"/>
@@ -3482,12 +3510,12 @@
     <col min="7" max="7" width="20.2109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>105</v>
@@ -3499,13 +3527,13 @@
         <v>116</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>50001</v>
       </c>
@@ -3528,7 +3556,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3">
         <v>50002</v>
       </c>
@@ -3551,7 +3579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3">
         <v>50003</v>
       </c>
@@ -3565,7 +3593,7 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>60</v>
@@ -3576,16 +3604,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="8" customWidth="1"/>
@@ -3595,7 +3623,7 @@
     <col min="7" max="7" width="13.92578125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -3612,7 +3640,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>60001</v>
       </c>
@@ -3626,7 +3654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16">
         <v>60002</v>
       </c>
@@ -3640,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="16">
         <v>60003</v>
       </c>
@@ -3654,7 +3682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="16">
         <v>60004</v>
       </c>
@@ -3668,7 +3696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16">
         <v>60005</v>
       </c>
@@ -3682,7 +3710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="16">
         <v>60006</v>
       </c>
@@ -3696,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="16">
         <v>60007</v>
       </c>
@@ -3710,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="16">
         <v>60008</v>
       </c>
@@ -3724,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="16">
         <v>60009</v>
       </c>
@@ -3738,43 +3766,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="16"/>
       <c r="D11" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="16"/>
       <c r="D12" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="16"/>
       <c r="D13" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="16"/>
       <c r="D14" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="16"/>
       <c r="D15" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="17"/>
       <c r="D16" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7">
         <v>61001</v>
       </c>
@@ -3790,16 +3818,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="8" customWidth="1"/>
@@ -3808,7 +3836,7 @@
     <col min="5" max="5" width="13.78515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -3825,7 +3853,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15">
         <v>70001</v>
       </c>
@@ -3842,7 +3870,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="16">
         <v>70002</v>
       </c>
@@ -3859,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="16">
         <v>70003</v>
       </c>
@@ -3876,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="16">
         <v>70004</v>
       </c>
@@ -3893,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16">
         <v>70005</v>
       </c>
@@ -3910,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="16">
         <v>70006</v>
       </c>
@@ -3927,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="16">
         <v>70007</v>
       </c>
@@ -3944,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="16">
         <v>70008</v>
       </c>
@@ -3961,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="16">
         <v>70009</v>
       </c>
@@ -3978,57 +4006,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="16"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="16"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="16"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="16"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="17"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="18"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="18"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="18"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="8" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -4045,35 +4073,35 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="8" customWidth="1"/>
     <col min="3" max="3" width="88.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="19.92578125" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="8" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" style="8" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" style="8" customWidth="1"/>
     <col min="9" max="9" width="16" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -4102,15 +4130,18 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>90001</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>184</v>
+      <c r="C2" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="G2" s="8">
         <v>5</v>
@@ -4119,15 +4150,18 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8">
         <v>90001</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>185</v>
+      <c r="C3" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="G3" s="8">
         <v>10</v>
@@ -4136,15 +4170,18 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8">
         <v>90001</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>186</v>
+      <c r="C4" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="G4" s="8">
         <v>25</v>
@@ -4153,57 +4190,69 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8">
         <v>90002</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>183</v>
+      <c r="C5" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>172</v>
       </c>
       <c r="G5" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8">
         <v>90002</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>183</v>
+      <c r="C6" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>172</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8">
         <v>90002</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>183</v>
+      <c r="C7" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>172</v>
       </c>
       <c r="G7" s="8">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="8">
         <v>90003</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>184</v>
+      <c r="C8" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="G8" s="8">
         <v>15</v>
@@ -4212,15 +4261,18 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="8">
         <v>90003</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>185</v>
+      <c r="C9" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="G9" s="8">
         <v>20</v>
@@ -4229,15 +4281,18 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="8">
         <v>90003</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>186</v>
+      <c r="C10" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="G10" s="8">
         <v>40</v>
@@ -4246,57 +4301,69 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7">
         <v>90004</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>183</v>
+      <c r="C11" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>174</v>
       </c>
       <c r="G11" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8">
         <v>90004</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>183</v>
+      <c r="C12" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="G12" s="8">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="8">
         <v>90004</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="28" t="s">
-        <v>183</v>
+      <c r="C13" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="G13" s="8">
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7">
         <v>90005</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>183</v>
+      <c r="C14" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>175</v>
       </c>
       <c r="G14" s="8">
         <v>3</v>
@@ -4305,15 +4372,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8">
         <v>90005</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>187</v>
+      <c r="C15" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="G15" s="8">
         <v>5</v>
@@ -4322,15 +4392,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8">
         <v>90005</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>188</v>
+      <c r="C16" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="G16" s="8">
         <v>7</v>
@@ -4339,15 +4412,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7">
         <v>90006</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>189</v>
+      <c r="C17" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
@@ -4356,15 +4432,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8">
         <v>90006</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>190</v>
+      <c r="C18" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -4373,15 +4452,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="9">
         <v>90006</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>191</v>
+      <c r="C19" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -4390,43 +4472,52 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="9">
         <v>90007</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>183</v>
+      <c r="C20" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="G20" s="8">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9">
         <v>90007</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>183</v>
+      <c r="C21" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="G21" s="8">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="9">
         <v>90007</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>183</v>
+      <c r="C22" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="G22" s="8">
         <v>350</v>
@@ -4434,7 +4525,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4D2C64-4450-4ACE-B87F-43BB8075E71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -25,648 +19,623 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="203">
-  <si>
-    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>해골 병사다.</t>
-  </si>
-  <si>
-    <t>1;1;1;</t>
-  </si>
-  <si>
-    <t>tier</t>
-  </si>
-  <si>
-    <t>레이저 포탑</t>
-  </si>
-  <si>
-    <t>전기 포탑</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>Dwarf</t>
-  </si>
-  <si>
-    <t>Panda</t>
-  </si>
-  <si>
-    <t>고블린 거인</t>
-  </si>
-  <si>
-    <t>도적이다.</t>
-  </si>
-  <si>
-    <t>메인 기차</t>
-  </si>
-  <si>
-    <t>미노타우로스다</t>
-  </si>
-  <si>
-    <t>거북이다</t>
-  </si>
-  <si>
-    <t>Lizard</t>
-  </si>
-  <si>
-    <t>난쟁이다</t>
-  </si>
-  <si>
-    <t>미사일 포탑</t>
-  </si>
-  <si>
-    <t>Skull</t>
-  </si>
-  <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
-    <t>포격 포탑</t>
-  </si>
-  <si>
-    <t>Thief</t>
-  </si>
-  <si>
-    <t>저격 포탑</t>
-  </si>
-  <si>
-    <t>폭발 포탑</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="194">
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">상어다 </t>
   </si>
   <si>
-    <t>Snake</t>
-  </si>
-  <si>
-    <t>Shark</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>Gnoll</t>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-  </si>
-  <si>
-    <t>Melee</t>
-  </si>
-  <si>
-    <t>놀이다.</t>
-  </si>
-  <si>
-    <t>Turtle</t>
-  </si>
-  <si>
-    <t>도마뱀이다</t>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-  </si>
-  <si>
-    <t>Bear</t>
-  </si>
-  <si>
-    <t>해골 왕이당.</t>
-  </si>
-  <si>
-    <t>icon_id</t>
-  </si>
-  <si>
-    <t>화염 포탑</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>Spider</t>
-  </si>
-  <si>
-    <t>귀상어다.</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>1;5;5;</t>
-  </si>
-  <si>
-    <t>엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t>stat_type</t>
-  </si>
-  <si>
-    <t>엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t>move_speed</t>
-  </si>
-  <si>
-    <t>전기 포탑 강화</t>
-  </si>
-  <si>
-    <t>need_money</t>
-  </si>
-  <si>
-    <t>고블린 창병이다</t>
-  </si>
-  <si>
-    <t>MainTrain</t>
-  </si>
-  <si>
-    <t>화염 포탑 강화</t>
-  </si>
-  <si>
-    <t>attack_type</t>
-  </si>
-  <si>
-    <t>엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t>엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t>레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t>1;1;1;1;</t>
-  </si>
-  <si>
-    <t>GoblinSpear</t>
-  </si>
-  <si>
-    <t>SkullKing</t>
-  </si>
-  <si>
-    <t>기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t>GiantGoblin</t>
-  </si>
-  <si>
-    <t>train_name</t>
-  </si>
-  <si>
-    <t>저격 포탑 강화</t>
-  </si>
-  <si>
-    <t>엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t>고블린 주술사다</t>
-  </si>
-  <si>
-    <t>미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t>폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t>엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t>prefab_id</t>
-  </si>
-  <si>
-    <t>엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t>엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t>포격 포탑 강화</t>
-  </si>
-  <si>
-    <t>Hammershark</t>
-  </si>
-  <si>
-    <t>Minotaur</t>
-  </si>
-  <si>
-    <t>엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>거미다</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>뱀이다</t>
-  </si>
-  <si>
-    <t>곰이다</t>
-  </si>
-  <si>
-    <t>판다다</t>
-  </si>
-  <si>
-    <t>GoblinSorcerer</t>
-  </si>
-  <si>
-    <t>폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>upgrade_type</t>
-  </si>
-  <si>
-    <t>drop_exp_min</t>
-  </si>
-  <si>
-    <t>upgrade_value</t>
-  </si>
-  <si>
-    <t>기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t>target_count</t>
-  </si>
-  <si>
-    <t>NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t>upgrade_name</t>
-  </si>
-  <si>
-    <t>체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t>monster_name</t>
-  </si>
-  <si>
-    <t>포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>AttackInterval</t>
-  </si>
-  <si>
-    <t>FireTurretTrain</t>
-  </si>
-  <si>
-    <t>전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>AttackDamage</t>
-  </si>
-  <si>
-    <t>attack_delay</t>
-  </si>
-  <si>
-    <t>stage_end_time</t>
-  </si>
-  <si>
-    <t>attack_interval</t>
-  </si>
-  <si>
-    <t>화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>train_data_id</t>
-  </si>
-  <si>
-    <t>attack_range</t>
-  </si>
-  <si>
-    <t>attack_count</t>
-  </si>
-  <si>
-    <t>제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t>target_train_id</t>
-  </si>
-  <si>
-    <t>냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>drop_money_min</t>
-  </si>
-  <si>
-    <t>drop_exp_max</t>
-  </si>
-  <si>
-    <t>spawn_monsters</t>
-  </si>
-  <si>
-    <t>LaserProjectile</t>
-  </si>
-  <si>
-    <t>drop_money_max</t>
-  </si>
-  <si>
-    <t>attack_damage</t>
-  </si>
-  <si>
-    <t>spawn_interval</t>
-  </si>
-  <si>
-    <t>is_main_train</t>
-  </si>
-  <si>
-    <t>저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>TrainUpgrade</t>
-  </si>
-  <si>
-    <t>SniperProjectile</t>
-  </si>
-  <si>
-    <t>10001;10002;10003;</t>
-  </si>
-  <si>
-    <t>ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t>MissileTurretTrain</t>
-  </si>
-  <si>
-    <t>replace_train_id</t>
-  </si>
-  <si>
-    <t>공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t>레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>NormalTurretTrain</t>
-  </si>
-  <si>
-    <t>미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>LaserTurretTrain</t>
-  </si>
-  <si>
-    <t>ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t>max_upgrade_count</t>
-  </si>
-  <si>
-    <t>NormalProjectile</t>
-  </si>
-  <si>
-    <t>10004;10005;10006;</t>
-  </si>
-  <si>
-    <t>ElectrickProjectile</t>
-  </si>
-  <si>
-    <t>CannonTurretTrain</t>
-  </si>
-  <si>
-    <t>SniperTurretTrain</t>
-  </si>
-  <si>
-    <t>ExplosionProjectile</t>
-  </si>
-  <si>
-    <t>기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t>weighted_upgrades</t>
-  </si>
-  <si>
-    <t>CannonProjectile</t>
-  </si>
-  <si>
-    <t>MissileProjectile</t>
-  </si>
-  <si>
-    <t>ColdAirProjectile</t>
-  </si>
-  <si>
-    <t>spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t>EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t>EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t>저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
-    <t>10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t>EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t>EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t>EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t>spawn_monsters_level</t>
-  </si>
-  <si>
-    <t>레이저로 강하게 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t>stage_inspection_time</t>
-  </si>
-  <si>
-    <t>획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t>EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t>projectile_prefab_id</t>
-  </si>
-  <si>
-    <t>EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t>획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t>EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t>EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t>FireEffectProjectile</t>
-  </si>
-  <si>
-    <t>ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t>Weapon_KMD_08_UI</t>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;5;5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;1;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거미다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">판다다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSorcerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_MEL_05_UI</t>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_KMD_10_UI</t>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_288_19_UI</t>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_MEL_16_UI</t>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_MEL_14_UI</t>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_KMD_12_UI</t>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>절대무적_요새_288버켓</t>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>절대무적_요새_멜리에스클래식_몸통뉴</t>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0}/{1} % 증가</t>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {1} 감소</t>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {2} 감소</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격딜레이 {3} 감소</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;증가&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 {1}&lt;bounce&gt;감소&lt;/bounce&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5853&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;증가&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 {1} &lt;bounce&gt;감소&lt;/bounce&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5852&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5853&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5854&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5855&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>공격력 {0} &lt;color=#FF5851&gt;증가&lt;/color&gt; 범위 {1} &lt;color=FF5856&gt;증가&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t>화염으로 지속적인 피해를 준다.</t>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t>Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t>Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t>절대무적_요새_288버켓</t>
+    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1081,7 +1050,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="9"/>
       <tableStyleElement type="headerRow" dxfId="8"/>
       <tableStyleElement type="totalRow" dxfId="7"/>
@@ -1090,18 +1059,18 @@
       <tableStyleElement type="firstRowStripe" dxfId="4"/>
       <tableStyleElement type="firstColumnStripe" dxfId="3"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="3">
       <tableStyleElement type="wholeTable" dxfId="2"/>
       <tableStyleElement type="headerRow" dxfId="1"/>
-      <tableStyleElement type="totalRow" dxfId="0"/>
+      <tableStyleElement type="totalRow"/>
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1398,10 +1367,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="9" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="8" customWidth="1"/>
@@ -1418,7 +1387,7 @@
     <col min="14" max="14" width="13.35546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -1462,7 +1431,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>10001</v>
       </c>
@@ -1506,7 +1475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A3" s="6">
         <v>10002</v>
       </c>
@@ -1550,7 +1519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A4" s="6">
         <v>10003</v>
       </c>
@@ -1594,7 +1563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A5" s="6">
         <v>10004</v>
       </c>
@@ -1638,7 +1607,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A6" s="6">
         <v>10005</v>
       </c>
@@ -1682,7 +1651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A7" s="8">
         <v>10006</v>
       </c>
@@ -1726,7 +1695,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A8" s="6">
         <v>10007</v>
       </c>
@@ -1770,7 +1739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A9" s="6">
         <v>10008</v>
       </c>
@@ -1814,7 +1783,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A10" s="6">
         <v>10009</v>
       </c>
@@ -1858,7 +1827,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A11" s="6">
         <v>10010</v>
       </c>
@@ -1902,7 +1871,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A12" s="8">
         <v>10011</v>
       </c>
@@ -1946,7 +1915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A13" s="6">
         <v>10012</v>
       </c>
@@ -1990,7 +1959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A14" s="6">
         <v>10013</v>
       </c>
@@ -2034,7 +2003,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A15" s="6">
         <v>10014</v>
       </c>
@@ -2078,7 +2047,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A16" s="6">
         <v>10015</v>
       </c>
@@ -2122,7 +2091,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A17" s="8">
         <v>10016</v>
       </c>
@@ -2166,7 +2135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A22" s="6">
         <v>10100</v>
       </c>
@@ -2213,24 +2182,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="71.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="119.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="15.640625" style="8" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2259,7 +2228,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>100001</v>
       </c>
@@ -2267,7 +2236,7 @@
         <v>70</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>179</v>
@@ -2279,7 +2248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="8">
         <v>100001</v>
       </c>
@@ -2287,10 +2256,10 @@
         <v>70</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -2299,7 +2268,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="8">
         <v>100001</v>
       </c>
@@ -2307,7 +2276,7 @@
         <v>70</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>179</v>
@@ -2319,7 +2288,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="8">
         <v>100002</v>
       </c>
@@ -2340,7 +2309,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="8">
         <v>100002</v>
       </c>
@@ -2348,10 +2317,10 @@
         <v>73</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -2360,7 +2329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="8">
         <v>100002</v>
       </c>
@@ -2368,10 +2337,10 @@
         <v>73</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -2382,16 +2351,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="27.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="8" customWidth="1"/>
@@ -2403,7 +2372,7 @@
     <col min="10" max="10" width="12.140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2433,7 +2402,7 @@
       </c>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>110001</v>
       </c>
@@ -2459,7 +2428,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="8">
         <v>110002</v>
       </c>
@@ -2485,7 +2454,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="8">
         <v>110003</v>
       </c>
@@ -2511,7 +2480,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="8">
         <v>110004</v>
       </c>
@@ -2534,7 +2503,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="8">
         <v>110005</v>
       </c>
@@ -2559,23 +2528,23 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="8" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2598,7 +2567,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>20001</v>
       </c>
@@ -2620,16 +2589,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="8" customWidth="1"/>
@@ -2642,7 +2611,7 @@
     <col min="13" max="13" width="15.640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2680,7 +2649,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="15">
         <v>40001</v>
       </c>
@@ -2718,7 +2687,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A3" s="16">
         <v>40002</v>
       </c>
@@ -2756,17 +2725,17 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A4" s="16"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A5" s="16"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A6" s="16"/>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A7" s="22">
         <v>41001</v>
       </c>
@@ -2801,7 +2770,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A8" s="23">
         <v>41002</v>
       </c>
@@ -2836,34 +2805,34 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A9" s="23"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A10" s="23"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A11" s="24"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="8" customWidth="1"/>
@@ -2876,7 +2845,7 @@
     <col min="12" max="13" width="19.28515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -2917,7 +2886,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="10">
         <v>30001</v>
       </c>
@@ -2958,7 +2927,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A3" s="11">
         <v>30002</v>
       </c>
@@ -2966,7 +2935,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D3" s="8">
         <v>100</v>
@@ -2999,7 +2968,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A4" s="11">
         <v>30003</v>
       </c>
@@ -3007,7 +2976,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -3040,7 +3009,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A5" s="11">
         <v>30004</v>
       </c>
@@ -3081,7 +3050,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A6" s="11">
         <v>30005</v>
       </c>
@@ -3122,7 +3091,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A7" s="11">
         <v>30006</v>
       </c>
@@ -3163,7 +3132,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A8" s="11">
         <v>30007</v>
       </c>
@@ -3204,16 +3173,16 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A12" s="12">
         <v>31001</v>
       </c>
@@ -3251,7 +3220,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A13" s="13">
         <v>31002</v>
       </c>
@@ -3289,7 +3258,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A14" s="12">
         <v>31003</v>
       </c>
@@ -3327,7 +3296,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A15" s="13">
         <v>31004</v>
       </c>
@@ -3365,7 +3334,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A16" s="12">
         <v>31005</v>
       </c>
@@ -3403,7 +3372,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A17" s="13">
         <v>31006</v>
       </c>
@@ -3441,7 +3410,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A18" s="12">
         <v>31007</v>
       </c>
@@ -3479,27 +3448,27 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A19" s="13"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A20" s="13"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A21" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="9" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="8" customWidth="1"/>
@@ -3510,7 +3479,7 @@
     <col min="7" max="7" width="20.2109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -3533,7 +3502,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>50001</v>
       </c>
@@ -3556,7 +3525,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A3" s="3">
         <v>50002</v>
       </c>
@@ -3579,7 +3548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A4" s="3">
         <v>50003</v>
       </c>
@@ -3604,16 +3573,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" style="8" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="8" customWidth="1"/>
@@ -3623,7 +3592,7 @@
     <col min="7" max="7" width="13.92578125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -3640,7 +3609,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="15">
         <v>60001</v>
       </c>
@@ -3654,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="16">
         <v>60002</v>
       </c>
@@ -3668,7 +3637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="16">
         <v>60003</v>
       </c>
@@ -3682,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="16">
         <v>60004</v>
       </c>
@@ -3696,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="16">
         <v>60005</v>
       </c>
@@ -3710,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="16">
         <v>60006</v>
       </c>
@@ -3724,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="16">
         <v>60007</v>
       </c>
@@ -3738,7 +3707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="16">
         <v>60008</v>
       </c>
@@ -3752,7 +3721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="16">
         <v>60009</v>
       </c>
@@ -3766,43 +3735,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="16"/>
       <c r="D11" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="16"/>
       <c r="D12" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="16"/>
       <c r="D13" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="16"/>
       <c r="D14" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="16"/>
       <c r="D15" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="17"/>
       <c r="D16" s="20">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A17" s="7">
         <v>61001</v>
       </c>
@@ -3818,16 +3787,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="10" style="7" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="8" customWidth="1"/>
@@ -3836,7 +3805,7 @@
     <col min="5" max="5" width="13.78515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -3853,7 +3822,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="15">
         <v>70001</v>
       </c>
@@ -3870,7 +3839,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="16">
         <v>70002</v>
       </c>
@@ -3887,7 +3856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="16">
         <v>70003</v>
       </c>
@@ -3904,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="16">
         <v>70004</v>
       </c>
@@ -3921,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="16">
         <v>70005</v>
       </c>
@@ -3938,7 +3907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A7" s="16">
         <v>70006</v>
       </c>
@@ -3955,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A8" s="16">
         <v>70007</v>
       </c>
@@ -3972,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A9" s="16">
         <v>70008</v>
       </c>
@@ -3989,7 +3958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A10" s="16">
         <v>70009</v>
       </c>
@@ -4006,57 +3975,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A11" s="16"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A12" s="16"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A13" s="16"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A14" s="16"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A15" s="16"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A16" s="17"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A17" s="18"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A18" s="18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A19" s="18"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A20" s="18"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55">
       <c r="A21" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="8" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -4073,26 +4042,26 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="17.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="88.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="130.5703125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="19.92578125" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="8" customWidth="1"/>
@@ -4101,7 +4070,7 @@
     <col min="9" max="9" width="16" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
@@ -4130,7 +4099,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>90001</v>
       </c>
@@ -4138,7 +4107,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>171</v>
@@ -4150,7 +4119,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="8">
         <v>90001</v>
       </c>
@@ -4158,7 +4127,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>171</v>
@@ -4170,7 +4139,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="8">
         <v>90001</v>
       </c>
@@ -4178,7 +4147,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>171</v>
@@ -4190,7 +4159,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A5" s="8">
         <v>90002</v>
       </c>
@@ -4198,7 +4167,7 @@
         <v>55</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>172</v>
@@ -4207,7 +4176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A6" s="8">
         <v>90002</v>
       </c>
@@ -4215,7 +4184,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>172</v>
@@ -4224,7 +4193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A7" s="8">
         <v>90002</v>
       </c>
@@ -4232,7 +4201,7 @@
         <v>55</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>172</v>
@@ -4241,7 +4210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A8" s="8">
         <v>90003</v>
       </c>
@@ -4249,10 +4218,10 @@
         <v>69</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="G8" s="8">
         <v>15</v>
@@ -4261,7 +4230,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A9" s="8">
         <v>90003</v>
       </c>
@@ -4269,7 +4238,7 @@
         <v>69</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>173</v>
@@ -4281,7 +4250,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A10" s="8">
         <v>90003</v>
       </c>
@@ -4289,7 +4258,7 @@
         <v>69</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>173</v>
@@ -4301,7 +4270,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A11" s="7">
         <v>90004</v>
       </c>
@@ -4309,7 +4278,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>174</v>
@@ -4318,7 +4287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A12" s="8">
         <v>90004</v>
       </c>
@@ -4326,7 +4295,7 @@
         <v>59</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>174</v>
@@ -4335,7 +4304,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A13" s="8">
         <v>90004</v>
       </c>
@@ -4343,7 +4312,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>174</v>
@@ -4352,7 +4321,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A14" s="7">
         <v>90005</v>
       </c>
@@ -4360,7 +4329,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>175</v>
@@ -4372,7 +4341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A15" s="8">
         <v>90005</v>
       </c>
@@ -4380,7 +4349,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>175</v>
@@ -4392,7 +4361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A16" s="8">
         <v>90005</v>
       </c>
@@ -4400,10 +4369,10 @@
         <v>51</v>
       </c>
       <c r="C16" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>201</v>
       </c>
       <c r="G16" s="8">
         <v>7</v>
@@ -4412,7 +4381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A17" s="7">
         <v>90006</v>
       </c>
@@ -4420,7 +4389,7 @@
         <v>77</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>176</v>
@@ -4432,7 +4401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A18" s="8">
         <v>90006</v>
       </c>
@@ -4440,7 +4409,7 @@
         <v>77</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>176</v>
@@ -4452,7 +4421,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A19" s="9">
         <v>90006</v>
       </c>
@@ -4460,7 +4429,7 @@
         <v>77</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>176</v>
@@ -4472,7 +4441,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A20" s="9">
         <v>90007</v>
       </c>
@@ -4480,7 +4449,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>177</v>
@@ -4489,7 +4458,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A21" s="9">
         <v>90007</v>
       </c>
@@ -4497,16 +4466,16 @@
         <v>66</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G21" s="8">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A22" s="9">
         <v>90007</v>
       </c>
@@ -4514,10 +4483,10 @@
         <v>66</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G22" s="8">
         <v>350</v>
@@ -4525,7 +4494,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69972223043441795" right="0.69972223043441795" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="197">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -607,27 +607,36 @@
     <t xml:space="preserve">절대무적_요새_288버켓</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1}감소&lt;/bounce&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1}감소&lt;/bounce&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 {1}&lt;bounce&gt;감소&lt;/bounce&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 {1} &lt;bounce&gt;감소&lt;/bounce&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1} 감소&lt;/bounce&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 {1} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 {1} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} &lt;color=#FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt; 범위 {1} &lt;color=FF5851&gt;&lt;bounce&gt;증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -905,44 +914,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <border>
-        <left/>
-        <right/>
-        <top style="medium">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FF6182D6"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1051,19 +1023,15 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="totalRow" dxfId="7"/>
-      <tableStyleElement type="firstColumn" dxfId="6"/>
-      <tableStyleElement type="lastColumn" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="3"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="3">
-      <tableStyleElement type="wholeTable" dxfId="2"/>
-      <tableStyleElement type="headerRow" dxfId="1"/>
-      <tableStyleElement type="totalRow"/>
-    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2236,7 +2204,7 @@
         <v>70</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>179</v>
@@ -2256,7 +2224,7 @@
         <v>70</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>181</v>
@@ -2276,7 +2244,7 @@
         <v>70</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>179</v>
@@ -2296,7 +2264,7 @@
         <v>73</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>178</v>
@@ -2317,7 +2285,7 @@
         <v>73</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>187</v>
@@ -2337,7 +2305,7 @@
         <v>73</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>187</v>
@@ -4107,7 +4075,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>171</v>
@@ -4167,7 +4135,7 @@
         <v>55</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>172</v>
@@ -4184,7 +4152,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>172</v>
@@ -4201,7 +4169,7 @@
         <v>55</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>172</v>
@@ -4218,7 +4186,7 @@
         <v>69</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>184</v>
@@ -4238,7 +4206,7 @@
         <v>69</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>173</v>
@@ -4258,7 +4226,7 @@
         <v>69</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>173</v>
@@ -4278,7 +4246,7 @@
         <v>59</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>174</v>
@@ -4295,7 +4263,7 @@
         <v>59</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>174</v>
@@ -4312,7 +4280,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>174</v>
@@ -4329,7 +4297,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>175</v>
@@ -4349,7 +4317,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>175</v>
@@ -4369,7 +4337,7 @@
         <v>51</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>186</v>
@@ -4389,7 +4357,7 @@
         <v>77</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>176</v>
@@ -4409,7 +4377,7 @@
         <v>77</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>176</v>
@@ -4429,7 +4397,7 @@
         <v>77</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>176</v>
@@ -4449,7 +4417,7 @@
         <v>66</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>177</v>
@@ -4466,7 +4434,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>185</v>
@@ -4483,7 +4451,7 @@
         <v>66</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>185</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
   </si>
   <si>
@@ -493,9 +490,6 @@
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">10007;10008;10009;10010;</t>
   </si>
   <si>
@@ -509,9 +503,6 @@
   </si>
   <si>
     <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">stage_inspection_time</t>
@@ -591,10 +582,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Weapon_KMD_10_UI</t>
   </si>
   <si>
@@ -637,6 +624,22 @@
   </si>
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 &lt;shake&gt;강한 피해&lt;/shake&gt;를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 &lt;shake&gt;강하게&lt;/shake&gt; 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;shake&gt;강한 피해&lt;/shake&gt;를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -914,15 +917,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1022,14 +1017,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="6">
+      <tableStyleElement type="wholeTable" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="4"/>
+      <tableStyleElement type="totalRow" dxfId="3"/>
+      <tableStyleElement type="firstColumn" dxfId="2"/>
+      <tableStyleElement type="lastColumn" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
@@ -1357,46 +1351,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.55">
@@ -1404,10 +1398,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="8">
         <v>10</v>
@@ -1419,16 +1413,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I2" s="8">
         <v>10</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K2" s="8">
         <v>10</v>
@@ -1437,10 +1431,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.55">
@@ -1448,10 +1442,10 @@
         <v>10002</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6">
         <v>35</v>
@@ -1481,10 +1475,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.55">
@@ -1492,10 +1486,10 @@
         <v>10003</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6">
         <v>50</v>
@@ -1525,10 +1519,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.55">
@@ -1536,10 +1530,10 @@
         <v>10004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="6">
         <v>60</v>
@@ -1569,10 +1563,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.55">
@@ -1580,10 +1574,10 @@
         <v>10005</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="6">
         <v>40</v>
@@ -1613,10 +1607,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.55">
@@ -1624,10 +1618,10 @@
         <v>10006</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6">
         <v>200</v>
@@ -1657,10 +1651,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.55">
@@ -1668,10 +1662,10 @@
         <v>10007</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="6">
         <v>40</v>
@@ -1701,10 +1695,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.55">
@@ -1712,10 +1706,10 @@
         <v>10008</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" s="6">
         <v>70</v>
@@ -1745,10 +1739,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.55">
@@ -1756,10 +1750,10 @@
         <v>10009</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="6">
         <v>100</v>
@@ -1789,10 +1783,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.55">
@@ -1800,10 +1794,10 @@
         <v>10010</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="6">
         <v>150</v>
@@ -1833,10 +1827,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.55">
@@ -1844,10 +1838,10 @@
         <v>10011</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="6">
         <v>30</v>
@@ -1877,10 +1871,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.55">
@@ -1888,10 +1882,10 @@
         <v>10012</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" s="6">
         <v>100</v>
@@ -1921,10 +1915,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.55">
@@ -1932,10 +1926,10 @@
         <v>10013</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="6">
         <v>250</v>
@@ -1965,10 +1959,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.55">
@@ -1976,10 +1970,10 @@
         <v>10014</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="6">
         <v>60</v>
@@ -2009,10 +2003,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.55">
@@ -2020,10 +2014,10 @@
         <v>10015</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="6">
         <v>60</v>
@@ -2053,10 +2047,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.55">
@@ -2064,10 +2058,10 @@
         <v>10016</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="6">
         <v>300</v>
@@ -2097,10 +2091,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.55">
@@ -2108,10 +2102,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="6">
         <v>500</v>
@@ -2141,10 +2135,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O22" s="3"/>
     </row>
@@ -2169,31 +2163,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="I1" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
@@ -2201,13 +2195,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -2221,13 +2215,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -2241,13 +2235,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -2261,13 +2255,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -2282,13 +2276,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -2302,13 +2296,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -2342,31 +2336,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J1" s="9"/>
     </row>
@@ -2375,10 +2369,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2390,10 +2384,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55">
@@ -2401,7 +2395,7 @@
         <v>110002</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>0</v>
@@ -2416,10 +2410,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55">
@@ -2427,10 +2421,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D4" s="8">
         <v>50</v>
@@ -2442,10 +2436,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55">
@@ -2453,10 +2447,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="8">
         <v>300</v>
@@ -2468,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55">
@@ -2476,10 +2470,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8">
         <v>500</v>
@@ -2491,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2514,25 +2508,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -2540,10 +2534,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2552,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2581,40 +2575,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="K1" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -2622,10 +2616,10 @@
         <v>40001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2634,10 +2628,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H2" s="8">
         <v>5</v>
@@ -2652,7 +2646,7 @@
         <v>4</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -2660,7 +2654,7 @@
         <v>40002</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>1</v>
@@ -2672,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H3" s="8">
         <v>5</v>
@@ -2690,7 +2684,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55">
@@ -2708,10 +2702,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8">
         <v>150</v>
@@ -2720,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="8">
         <v>8</v>
@@ -2735,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.55">
@@ -2743,10 +2737,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8" s="8">
         <v>150</v>
@@ -2755,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H8" s="8">
         <v>13</v>
@@ -2770,7 +2764,7 @@
         <v>0.1</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55">
@@ -2815,43 +2809,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="K1" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -2859,10 +2853,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D2" s="8">
         <v>100</v>
@@ -2871,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H2" s="8">
         <v>10</v>
@@ -2892,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55">
@@ -2900,10 +2894,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D3" s="8">
         <v>100</v>
@@ -2912,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H3" s="8">
         <v>10</v>
@@ -2933,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55">
@@ -2941,10 +2935,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2953,10 +2947,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H4" s="8">
         <v>10</v>
@@ -2974,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55">
@@ -2982,10 +2976,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>160</v>
+        <v>7</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>194</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -2994,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H5" s="8">
         <v>15</v>
@@ -3015,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55">
@@ -3023,10 +3017,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" s="8">
         <v>100</v>
@@ -3035,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H6" s="8">
         <v>10</v>
@@ -3056,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55">
@@ -3064,10 +3058,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>195</v>
       </c>
       <c r="D7" s="8">
         <v>100</v>
@@ -3076,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H7" s="8">
         <v>10</v>
@@ -3097,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55">
@@ -3105,10 +3099,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>154</v>
+        <v>24</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -3117,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H8" s="8">
         <v>10</v>
@@ -3138,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55">
@@ -3155,10 +3149,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="8">
         <v>150</v>
@@ -3167,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H12" s="2">
         <v>10</v>
@@ -3185,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55">
@@ -3193,10 +3187,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="8">
         <v>150</v>
@@ -3205,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H13" s="8">
         <v>10</v>
@@ -3223,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.55">
@@ -3231,10 +3225,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D14" s="8">
         <v>150</v>
@@ -3243,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H14" s="8">
         <v>10</v>
@@ -3261,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55">
@@ -3269,10 +3263,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="8">
         <v>150</v>
@@ -3281,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H15" s="8">
         <v>10</v>
@@ -3299,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55">
@@ -3307,10 +3301,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="8">
         <v>150</v>
@@ -3319,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H16" s="8">
         <v>10</v>
@@ -3337,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55">
@@ -3345,10 +3339,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D17" s="8">
         <v>150</v>
@@ -3357,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H17" s="8">
         <v>10</v>
@@ -3375,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55">
@@ -3383,10 +3377,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D18" s="8">
         <v>150</v>
@@ -3395,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H18" s="8">
         <v>10</v>
@@ -3413,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55">
@@ -3449,25 +3443,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -3484,13 +3478,13 @@
         <v>0.5</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55">
@@ -3507,13 +3501,13 @@
         <v>0.5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55">
@@ -3530,13 +3524,13 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3562,19 +3556,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -3775,19 +3769,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -3995,19 +3989,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -4040,31 +4034,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="I1" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
@@ -4072,13 +4066,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G2" s="8">
         <v>5</v>
@@ -4092,13 +4086,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G3" s="8">
         <v>10</v>
@@ -4112,13 +4106,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G4" s="8">
         <v>25</v>
@@ -4132,13 +4126,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G5" s="8">
         <v>2</v>
@@ -4149,13 +4143,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G6" s="8">
         <v>5</v>
@@ -4166,13 +4160,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G7" s="8">
         <v>10</v>
@@ -4183,13 +4177,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G8" s="8">
         <v>15</v>
@@ -4203,13 +4197,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G9" s="8">
         <v>20</v>
@@ -4223,13 +4217,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G10" s="8">
         <v>40</v>
@@ -4243,13 +4237,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G11" s="8">
         <v>50</v>
@@ -4260,13 +4254,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G12" s="8">
         <v>150</v>
@@ -4277,13 +4271,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G13" s="8">
         <v>250</v>
@@ -4294,13 +4288,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G14" s="8">
         <v>3</v>
@@ -4314,13 +4308,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G15" s="8">
         <v>5</v>
@@ -4334,13 +4328,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G16" s="8">
         <v>7</v>
@@ -4354,13 +4348,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
@@ -4374,13 +4368,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F18" s="8">
         <v>1</v>
@@ -4394,13 +4388,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F19" s="8">
         <v>1</v>
@@ -4414,13 +4408,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G20" s="8">
         <v>50</v>
@@ -4431,13 +4425,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G21" s="8">
         <v>150</v>
@@ -4448,13 +4442,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G22" s="8">
         <v>350</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="196">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -594,13 +594,6 @@
     <t xml:space="preserve">절대무적_요새_288버켓</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1}감소&lt;/bounce&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1}감소&lt;/bounce&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
@@ -608,10 +601,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;bounce&gt;{1} 감소&lt;/bounce&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -640,6 +629,14 @@
   </si>
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;shake&gt;강한 피해&lt;/shake&gt;를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -917,15 +914,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <b/>
@@ -1017,13 +1006,12 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="6">
-      <tableStyleElement type="wholeTable" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="totalRow" dxfId="3"/>
-      <tableStyleElement type="firstColumn" dxfId="2"/>
-      <tableStyleElement type="lastColumn" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="5">
+      <tableStyleElement type="wholeTable" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="totalRow" dxfId="2"/>
+      <tableStyleElement type="firstColumn" dxfId="1"/>
+      <tableStyleElement type="lastColumn"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
@@ -2198,7 +2186,7 @@
         <v>69</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>176</v>
@@ -2218,7 +2206,7 @@
         <v>69</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>178</v>
@@ -2238,7 +2226,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>176</v>
@@ -2258,7 +2246,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>175</v>
@@ -2279,7 +2267,7 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>183</v>
@@ -2299,7 +2287,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>183</v>
@@ -2938,7 +2926,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2979,7 +2967,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -3061,7 +3049,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D7" s="8">
         <v>100</v>
@@ -3102,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -4069,7 +4057,7 @@
         <v>62</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>168</v>
@@ -4089,7 +4077,7 @@
         <v>62</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>168</v>
@@ -4109,7 +4097,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>168</v>
@@ -4129,7 +4117,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>169</v>
@@ -4146,7 +4134,7 @@
         <v>54</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>169</v>
@@ -4163,7 +4151,7 @@
         <v>54</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>169</v>
@@ -4180,7 +4168,7 @@
         <v>68</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>180</v>
@@ -4200,7 +4188,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>170</v>
@@ -4220,7 +4208,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>170</v>
@@ -4240,7 +4228,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>171</v>
@@ -4257,7 +4245,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>171</v>
@@ -4274,7 +4262,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>171</v>
@@ -4291,7 +4279,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>172</v>
@@ -4311,7 +4299,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>172</v>
@@ -4331,7 +4319,7 @@
         <v>50</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>182</v>
@@ -4351,7 +4339,7 @@
         <v>76</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>173</v>
@@ -4371,7 +4359,7 @@
         <v>76</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>173</v>
@@ -4391,7 +4379,7 @@
         <v>76</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>173</v>
@@ -4411,7 +4399,7 @@
         <v>65</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>174</v>
@@ -4428,7 +4416,7 @@
         <v>65</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>181</v>
@@ -4445,7 +4433,7 @@
         <v>65</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>181</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -616,27 +616,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">미사일로 &lt;shake&gt;강한 피해&lt;/shake&gt;를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;shake&gt;강하게&lt;/shake&gt; 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;shake&gt;강한 피해&lt;/shake&gt;를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -914,19 +914,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <b/>
@@ -1006,12 +994,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="5">
-      <tableStyleElement type="wholeTable" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="totalRow" dxfId="2"/>
-      <tableStyleElement type="firstColumn" dxfId="1"/>
-      <tableStyleElement type="lastColumn"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="4">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="totalRow" dxfId="1"/>
+      <tableStyleElement type="firstColumn"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
@@ -2302,7 +2289,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2786,7 +2773,7 @@
   <cols>
     <col min="1" max="1" width="15.640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="17.640625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="47.92578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="85.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15.640625" style="8" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" style="8" customWidth="1"/>
     <col min="7" max="7" width="19.140625" style="8" bestFit="1" customWidth="1"/>
@@ -2926,7 +2913,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2967,7 +2954,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -3049,7 +3036,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7" s="8">
         <v>100</v>
@@ -3090,7 +3077,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -4057,7 +4044,7 @@
         <v>62</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>168</v>
@@ -4077,7 +4064,7 @@
         <v>62</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>168</v>
@@ -4097,7 +4084,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>168</v>
@@ -4168,7 +4155,7 @@
         <v>68</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>180</v>
@@ -4188,7 +4175,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>170</v>
@@ -4208,7 +4195,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>170</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="198">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -609,13 +609,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -638,6 +631,19 @@
   <si>
     <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">has_skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_icon_id</t>
   </si>
 </sst>
 </file>
@@ -914,36 +920,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thick">
-          <color rgb="FFFFFFFF"/>
-        </top>
-      </border>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -994,11 +971,9 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="totalRow" dxfId="1"/>
-      <tableStyleElement type="firstColumn"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
@@ -2173,7 +2148,7 @@
         <v>69</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>176</v>
@@ -2193,7 +2168,7 @@
         <v>69</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>178</v>
@@ -2213,7 +2188,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>176</v>
@@ -2233,7 +2208,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>175</v>
@@ -2254,7 +2229,7 @@
         <v>72</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>183</v>
@@ -2274,7 +2249,7 @@
         <v>72</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>183</v>
@@ -2473,7 +2448,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
@@ -2481,7 +2456,7 @@
     <col min="4" max="13" width="15.640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -2503,8 +2478,17 @@
       <c r="G1" s="8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="H1" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="8">
         <v>20001</v>
       </c>
@@ -2534,7 +2518,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="8" customWidth="1"/>
@@ -2546,9 +2530,11 @@
     <col min="11" max="11" width="18.2109375" style="8" customWidth="1"/>
     <col min="12" max="12" width="21" style="8" customWidth="1"/>
     <col min="13" max="13" width="15.640625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="13.35546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -2571,22 +2557,31 @@
         <v>39</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="M1" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="N1" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="O1" s="0" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A2" s="15">
         <v>40001</v>
       </c>
@@ -2608,23 +2603,23 @@
       <c r="G2" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="H2" s="8">
+      <c r="K2" s="8">
         <v>5</v>
       </c>
-      <c r="I2" s="8">
+      <c r="L2" s="8">
         <v>100</v>
       </c>
-      <c r="J2" s="8">
+      <c r="M2" s="8">
         <v>1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="N2" s="8">
         <v>4</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="O2" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A3" s="16">
         <v>40002</v>
       </c>
@@ -2646,33 +2641,36 @@
       <c r="G3" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H3" s="8">
+      <c r="K3" s="8">
         <v>5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="L3" s="8">
         <v>1</v>
       </c>
-      <c r="J3" s="8">
+      <c r="M3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="N3" s="8">
         <v>0.1</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A4" s="16"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A5" s="16"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A6" s="16"/>
       <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A7" s="22">
         <v>41001</v>
       </c>
@@ -2691,23 +2689,23 @@
       <c r="F7" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="H7" s="8">
+      <c r="K7" s="8">
         <v>8</v>
       </c>
-      <c r="I7" s="8">
+      <c r="L7" s="8">
         <v>500</v>
       </c>
-      <c r="J7" s="8">
+      <c r="M7" s="8">
         <v>1</v>
       </c>
-      <c r="K7" s="8">
+      <c r="N7" s="8">
         <v>4</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="O7" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A8" s="23">
         <v>41002</v>
       </c>
@@ -2726,35 +2724,35 @@
       <c r="F8" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="H8" s="8">
+      <c r="K8" s="8">
         <v>13</v>
       </c>
-      <c r="I8" s="8">
+      <c r="L8" s="8">
         <v>15</v>
       </c>
-      <c r="J8" s="8">
+      <c r="M8" s="8">
         <v>1</v>
       </c>
-      <c r="K8" s="8">
+      <c r="N8" s="8">
         <v>0.1</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="O8" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A9" s="23"/>
       <c r="B9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A10" s="23"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A11" s="24"/>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.55">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
     </row>
@@ -2768,7 +2766,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.640625" style="8" customWidth="1"/>
@@ -2779,10 +2777,14 @@
     <col min="7" max="7" width="19.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="15.640625" style="8" customWidth="1"/>
     <col min="11" max="11" width="20.92578125" style="8" customWidth="1"/>
-    <col min="12" max="13" width="19.28515625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="16.78515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.35546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.92578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
@@ -2805,25 +2807,34 @@
         <v>39</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="N1" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="O1" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="P1" s="0" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A2" s="10">
         <v>30001</v>
       </c>
@@ -2845,26 +2856,26 @@
       <c r="G2" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="8">
+      <c r="K2" s="8">
         <v>10</v>
       </c>
-      <c r="I2" s="8">
+      <c r="L2" s="8">
         <v>10</v>
       </c>
-      <c r="J2" s="8">
+      <c r="M2" s="8">
         <v>1</v>
       </c>
-      <c r="K2" s="8">
+      <c r="N2" s="8">
         <v>0.25</v>
       </c>
-      <c r="L2" s="8">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9" t="s">
+      <c r="O2" s="8">
+        <v>0</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A3" s="11">
         <v>30002</v>
       </c>
@@ -2886,26 +2897,26 @@
       <c r="G3" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="8">
+      <c r="K3" s="8">
         <v>10</v>
       </c>
-      <c r="I3" s="8">
+      <c r="L3" s="8">
         <v>3</v>
       </c>
-      <c r="J3" s="8">
+      <c r="M3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="N3" s="8">
         <v>0.1</v>
       </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A4" s="11">
         <v>30003</v>
       </c>
@@ -2913,7 +2924,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D4" s="8">
         <v>100</v>
@@ -2927,26 +2938,26 @@
       <c r="G4" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="H4" s="8">
+      <c r="K4" s="8">
         <v>10</v>
       </c>
-      <c r="I4" s="8">
+      <c r="L4" s="8">
         <v>25</v>
       </c>
-      <c r="J4" s="8">
+      <c r="M4" s="8">
         <v>1</v>
       </c>
-      <c r="K4" s="8">
+      <c r="N4" s="8">
         <v>1</v>
       </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8" t="s">
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A5" s="11">
         <v>30004</v>
       </c>
@@ -2954,7 +2965,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D5" s="8">
         <v>100</v>
@@ -2968,26 +2979,26 @@
       <c r="G5" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="H5" s="8">
+      <c r="K5" s="8">
         <v>15</v>
       </c>
-      <c r="I5" s="8">
+      <c r="L5" s="8">
         <v>50</v>
       </c>
-      <c r="J5" s="8">
+      <c r="M5" s="8">
         <v>1</v>
       </c>
-      <c r="K5" s="8">
+      <c r="N5" s="8">
         <v>2</v>
       </c>
-      <c r="L5" s="8">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A6" s="11">
         <v>30005</v>
       </c>
@@ -3009,26 +3020,26 @@
       <c r="G6" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="H6" s="8">
+      <c r="K6" s="8">
         <v>10</v>
       </c>
-      <c r="I6" s="8">
+      <c r="L6" s="8">
         <v>10</v>
       </c>
-      <c r="J6" s="8">
+      <c r="M6" s="8">
         <v>5</v>
       </c>
-      <c r="K6" s="8">
+      <c r="N6" s="8">
         <v>2</v>
       </c>
-      <c r="L6" s="8">
+      <c r="O6" s="8">
         <v>5</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="P6" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A7" s="11">
         <v>30006</v>
       </c>
@@ -3036,7 +3047,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D7" s="8">
         <v>100</v>
@@ -3050,26 +3061,26 @@
       <c r="G7" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="8">
+      <c r="K7" s="8">
         <v>10</v>
       </c>
-      <c r="I7" s="8">
+      <c r="L7" s="8">
         <v>50</v>
       </c>
-      <c r="J7" s="8">
+      <c r="M7" s="8">
         <v>1</v>
       </c>
-      <c r="K7" s="8">
+      <c r="N7" s="8">
         <v>3</v>
       </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="s">
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
+      <c r="P7" s="8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A8" s="11">
         <v>30007</v>
       </c>
@@ -3077,7 +3088,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D8" s="8">
         <v>100</v>
@@ -3091,35 +3102,35 @@
       <c r="G8" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="8">
+      <c r="K8" s="8">
         <v>10</v>
       </c>
-      <c r="I8" s="8">
+      <c r="L8" s="8">
         <v>50</v>
       </c>
-      <c r="J8" s="8">
+      <c r="M8" s="8">
         <v>1</v>
       </c>
-      <c r="K8" s="8">
+      <c r="N8" s="8">
         <v>1</v>
       </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8" t="s">
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A12" s="12">
         <v>31001</v>
       </c>
@@ -3138,26 +3149,26 @@
       <c r="F12" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="2">
+      <c r="K12" s="2">
         <v>10</v>
       </c>
-      <c r="I12" s="2">
+      <c r="L12" s="2">
         <v>50</v>
       </c>
-      <c r="J12" s="2">
+      <c r="M12" s="2">
         <v>1</v>
       </c>
-      <c r="K12" s="2">
+      <c r="N12" s="2">
         <v>0.1</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="s">
+      <c r="O12" s="2">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A13" s="13">
         <v>31002</v>
       </c>
@@ -3176,26 +3187,26 @@
       <c r="F13" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="H13" s="8">
+      <c r="K13" s="8">
         <v>10</v>
       </c>
-      <c r="I13" s="8">
+      <c r="L13" s="8">
         <v>25</v>
       </c>
-      <c r="J13" s="8">
+      <c r="M13" s="8">
         <v>1</v>
       </c>
-      <c r="K13" s="8">
+      <c r="N13" s="8">
         <v>0.1</v>
       </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8" t="s">
+      <c r="O13" s="8">
+        <v>0</v>
+      </c>
+      <c r="P13" s="8" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A14" s="12">
         <v>31003</v>
       </c>
@@ -3214,26 +3225,26 @@
       <c r="F14" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="H14" s="8">
+      <c r="K14" s="8">
         <v>10</v>
       </c>
-      <c r="I14" s="8">
+      <c r="L14" s="8">
         <v>100</v>
       </c>
-      <c r="J14" s="8">
+      <c r="M14" s="8">
         <v>1</v>
       </c>
-      <c r="K14" s="8">
+      <c r="N14" s="8">
         <v>0.5</v>
       </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8" t="s">
+      <c r="O14" s="8">
+        <v>0</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A15" s="13">
         <v>31004</v>
       </c>
@@ -3252,26 +3263,26 @@
       <c r="F15" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="H15" s="8">
+      <c r="K15" s="8">
         <v>10</v>
       </c>
-      <c r="I15" s="8">
+      <c r="L15" s="8">
         <v>300</v>
       </c>
-      <c r="J15" s="8">
+      <c r="M15" s="8">
         <v>1</v>
       </c>
-      <c r="K15" s="8">
+      <c r="N15" s="8">
         <v>3</v>
       </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8" t="s">
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A16" s="12">
         <v>31005</v>
       </c>
@@ -3290,26 +3301,26 @@
       <c r="F16" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="H16" s="8">
+      <c r="K16" s="8">
         <v>10</v>
       </c>
-      <c r="I16" s="8">
+      <c r="L16" s="8">
         <v>400</v>
       </c>
-      <c r="J16" s="8">
+      <c r="M16" s="8">
         <v>1</v>
       </c>
-      <c r="K16" s="8">
+      <c r="N16" s="8">
         <v>5</v>
       </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8" t="s">
+      <c r="O16" s="8">
+        <v>0</v>
+      </c>
+      <c r="P16" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A17" s="13">
         <v>31006</v>
       </c>
@@ -3328,26 +3339,26 @@
       <c r="F17" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="H17" s="8">
+      <c r="K17" s="8">
         <v>10</v>
       </c>
-      <c r="I17" s="8">
+      <c r="L17" s="8">
         <v>400</v>
       </c>
-      <c r="J17" s="8">
+      <c r="M17" s="8">
         <v>1</v>
       </c>
-      <c r="K17" s="8">
+      <c r="N17" s="8">
         <v>3</v>
       </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8" t="s">
+      <c r="O17" s="8">
+        <v>0</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A18" s="12">
         <v>31007</v>
       </c>
@@ -3366,32 +3377,32 @@
       <c r="F18" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="H18" s="8">
+      <c r="K18" s="8">
         <v>10</v>
       </c>
-      <c r="I18" s="8">
+      <c r="L18" s="8">
         <v>600</v>
       </c>
-      <c r="J18" s="8">
+      <c r="M18" s="8">
         <v>1</v>
       </c>
-      <c r="K18" s="8">
+      <c r="N18" s="8">
         <v>1.5</v>
       </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8" t="s">
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A19" s="13"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A20" s="13"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.55">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55">
       <c r="A21" s="14"/>
     </row>
   </sheetData>
@@ -4044,7 +4055,7 @@
         <v>62</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>168</v>
@@ -4064,7 +4075,7 @@
         <v>62</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>168</v>
@@ -4084,7 +4095,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>168</v>
@@ -4155,7 +4166,7 @@
         <v>68</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>180</v>
@@ -4175,7 +4186,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>170</v>
@@ -4195,7 +4206,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>170</v>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="3" activeTab="3"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -19,377 +19,535 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
     <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="200">
+  <si>
+    <t xml:space="preserve">1;4;8;</t>
+  </si>
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
     <t xml:space="preserve">drop_money_max</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_range</t>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
   </si>
   <si>
     <t xml:space="preserve">GoblinSorcerer</t>
   </si>
   <si>
-    <t xml:space="preserve">is_main_train</t>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
   </si>
   <si>
     <t xml:space="preserve">skill_cooldown</t>
   </si>
   <si>
-    <t xml:space="preserve">skill_icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;3;5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미노타우로스다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">놀이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6;3;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상어다 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 왕이당.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도마뱀이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turtle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwarf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거북이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 거인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">도적이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">난쟁이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">해골 병사다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀상어다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thief</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5;3;2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gnoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5;4;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 주술사다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고블린 창병이다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoblinSpear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minotaur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammershark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkullKing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;1;5;8;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4;3;2;1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GiantGoblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">곰이다</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
     <t xml:space="preserve">거미다</t>
   </si>
   <si>
     <t xml:space="preserve">판다다</t>
   </si>
   <si>
+    <t xml:space="preserve">뱀이다</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">곰이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 병사다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thief</t>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gnoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">놀이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도적이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">귀상어다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미노타우로스다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">도마뱀이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">해골 왕이당.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turtle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 거인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거북이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상어다 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">난쟁이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwarf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;5;5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammershark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minotaur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 주술사다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GiantGoblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GoblinSpear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkullKing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고블린 창병이다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonTrainUpgrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
+    <t xml:space="preserve">10011;10012;10013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
     <t xml:space="preserve">MissileTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10004;10005;10006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_KMD_10_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">ElectrickProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10014;10015;10016;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replace_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10001;10002;10003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
   </si>
   <si>
     <t xml:space="preserve">LaserTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+    <t xml:space="preserve">SniperProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">MissileProjectile</t>
@@ -398,208 +556,73 @@
     <t xml:space="preserve">Weapon_MEL_16_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">replace_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 {0}/{1} % 감소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10007;10008;10009;10010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;3;6;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteNormalTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
   </si>
   <si>
     <t xml:space="preserve">획득하는 골드 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 {0}/{1} % 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;1;1;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stat_type</t>
   </si>
 </sst>
 </file>
@@ -607,7 +630,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -638,6 +661,11 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -648,7 +676,7 @@
     </fill>
   </fills>
   <borders count="12">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -661,8 +689,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -675,8 +706,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FF5B9BD5"/>
       </left>
@@ -689,8 +723,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -703,8 +740,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -717,8 +757,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFC000"/>
       </left>
@@ -731,8 +774,11 @@
       <bottom style="medium">
         <color rgb="FFFFC000"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -745,8 +791,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -759,8 +808,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -773,8 +825,11 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -787,8 +842,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -801,8 +859,11 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left style="medium">
         <color rgb="FFFFD700"/>
       </left>
@@ -815,10 +876,55 @@
       <bottom style="medium">
         <color rgb="FFFFD700"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -873,64 +979,125 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
         </patternFill>
       </fill>
       <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
         <bottom style="thin">
-          <color rgb="FF6182D6"/>
+          <color rgb="FF8FABDB"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF8FABDB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAE3F3"/>
+          <bgColor rgb="FFDAE3F3"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
-    </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="4">
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
+      <tableStyleElement type="lastColumn" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -979,7 +1146,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri Light" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1031,7 +1198,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="21474836470000000000"/>
+        <a:latin typeface="Calibri" panose="2147483647"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1228,7 +1395,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="13" customWidth="1"/>
@@ -1247,46 +1414,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>2</v>
-      </c>
       <c r="L1" s="13" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1294,31 +1461,31 @@
         <v>10001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D2" s="13">
         <v>10</v>
       </c>
       <c r="E2" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" s="13">
         <v>5</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="I2" s="13">
         <v>10</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="K2" s="13">
         <v>10</v>
@@ -1327,10 +1494,10 @@
         <v>2</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1338,16 +1505,16 @@
         <v>10002</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="D3" s="13">
         <v>35</v>
       </c>
       <c r="E3" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="13">
         <v>8</v>
@@ -1371,10 +1538,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1382,16 +1549,16 @@
         <v>10003</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D4" s="13">
         <v>50</v>
       </c>
       <c r="E4" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="13">
         <v>3</v>
@@ -1415,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1426,16 +1593,16 @@
         <v>10004</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D5" s="13">
         <v>60</v>
       </c>
       <c r="E5" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5" s="13">
         <v>4</v>
@@ -1459,10 +1626,10 @@
         <v>2</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1470,16 +1637,16 @@
         <v>10005</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D6" s="13">
         <v>40</v>
       </c>
       <c r="E6" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F6" s="13">
         <v>3</v>
@@ -1503,10 +1670,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1514,16 +1681,16 @@
         <v>10006</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D7" s="13">
         <v>200</v>
       </c>
       <c r="E7" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F7" s="13">
         <v>2.2000000000000002</v>
@@ -1547,10 +1714,10 @@
         <v>2</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1558,16 +1725,16 @@
         <v>10007</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="D8" s="13">
         <v>40</v>
       </c>
       <c r="E8" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" s="13">
         <v>5</v>
@@ -1591,10 +1758,10 @@
         <v>3</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1602,16 +1769,16 @@
         <v>10008</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D9" s="13">
         <v>70</v>
       </c>
       <c r="E9" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" s="13">
         <v>6.4000000000000004</v>
@@ -1635,10 +1802,10 @@
         <v>1.5</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1646,16 +1813,16 @@
         <v>10009</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D10" s="13">
         <v>100</v>
       </c>
       <c r="E10" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F10" s="13">
         <v>4.2999999999999998</v>
@@ -1679,10 +1846,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1690,16 +1857,16 @@
         <v>10010</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="D11" s="13">
         <v>150</v>
       </c>
       <c r="E11" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F11" s="13">
         <v>7</v>
@@ -1723,10 +1890,10 @@
         <v>2</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1734,16 +1901,16 @@
         <v>10011</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="D12" s="13">
         <v>30</v>
       </c>
       <c r="E12" s="13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" s="13">
         <v>7</v>
@@ -1767,10 +1934,10 @@
         <v>2</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1778,16 +1945,16 @@
         <v>10012</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="D13" s="13">
         <v>100</v>
       </c>
       <c r="E13" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F13" s="13">
         <v>5</v>
@@ -1811,10 +1978,10 @@
         <v>3</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1822,16 +1989,16 @@
         <v>10013</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D14" s="13">
         <v>250</v>
       </c>
       <c r="E14" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F14" s="13">
         <v>5</v>
@@ -1855,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1866,16 +2033,16 @@
         <v>10014</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D15" s="13">
         <v>60</v>
       </c>
       <c r="E15" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F15" s="13">
         <v>5</v>
@@ -1899,10 +2066,10 @@
         <v>2</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1910,16 +2077,16 @@
         <v>10015</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D16" s="13">
         <v>60</v>
       </c>
       <c r="E16" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F16" s="13">
         <v>4</v>
@@ -1943,10 +2110,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1954,16 +2121,16 @@
         <v>10016</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="D17" s="13">
         <v>300</v>
       </c>
       <c r="E17" s="13">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F17" s="13">
         <v>2.5</v>
@@ -1987,10 +2154,10 @@
         <v>2</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -1998,10 +2165,10 @@
         <v>10100</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D22" s="13">
         <v>500</v>
@@ -2031,10 +2198,10 @@
         <v>3</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="O22" s="13"/>
     </row>
@@ -2048,7 +2215,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="13" customWidth="1"/>
     <col min="3" max="3" width="119.5703125" style="13" bestFit="1" customWidth="1"/>
@@ -2060,31 +2227,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2092,16 +2259,16 @@
         <v>100001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F2" s="13">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G2" s="13">
         <v>1</v>
@@ -2112,19 +2279,19 @@
         <v>100001</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F3" s="13">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="G3" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2132,19 +2299,19 @@
         <v>100001</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F4" s="13">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="G4" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2152,13 +2319,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="F5" s="13">
         <v>2</v>
@@ -2172,19 +2339,19 @@
         <v>100002</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="F6" s="13">
         <v>3</v>
       </c>
       <c r="G6" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2192,19 +2359,19 @@
         <v>100002</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>190</v>
+        <v>133</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="F7" s="13">
         <v>4</v>
       </c>
       <c r="G7" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2231,31 +2398,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2263,10 +2430,10 @@
         <v>110001</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D2" s="13">
         <v>100</v>
@@ -2278,10 +2445,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2289,10 +2456,10 @@
         <v>110002</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D3" s="13">
         <v>200</v>
@@ -2304,10 +2471,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>102</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2315,10 +2482,10 @@
         <v>110003</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D4" s="13">
         <v>50</v>
@@ -2330,10 +2497,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2341,10 +2508,10 @@
         <v>110004</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="D5" s="13">
         <v>300</v>
@@ -2356,7 +2523,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2364,10 +2531,10 @@
         <v>110005</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="D6" s="13">
         <v>500</v>
@@ -2379,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2392,7 +2559,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="13" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="13" customWidth="1"/>
@@ -2401,34 +2568,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2436,10 +2603,10 @@
         <v>20001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D2" s="13">
         <v>100</v>
@@ -2448,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2461,7 +2628,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="13" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" style="13" customWidth="1"/>
@@ -2478,60 +2645,60 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16.75">
       <c r="A2" s="7">
         <v>40001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D2" s="13">
         <v>100</v>
@@ -2540,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="K2" s="13">
         <v>5</v>
@@ -2558,7 +2725,7 @@
         <v>4</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -2566,10 +2733,10 @@
         <v>40002</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D3" s="13">
         <v>100</v>
@@ -2578,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="K3" s="13">
         <v>5</v>
@@ -2611,15 +2778,15 @@
       <c r="A6" s="8"/>
       <c r="O6" s="13"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="16.75">
       <c r="A7" s="10">
         <v>41001</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D7" s="13">
         <v>150</v>
@@ -2628,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="K7" s="13">
         <v>8</v>
@@ -2643,7 +2810,7 @@
         <v>4</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2651,10 +2818,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D8" s="13">
         <v>150</v>
@@ -2663,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="K8" s="13">
         <v>13</v>
@@ -2687,7 +2854,7 @@
     <row r="10" spans="1:1">
       <c r="A10" s="11"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" ht="16.75">
       <c r="A11" s="12"/>
     </row>
   </sheetData>
@@ -2719,52 +2886,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16.75">
@@ -2772,10 +2939,10 @@
         <v>30001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="D2" s="13">
         <v>100</v>
@@ -2784,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>145</v>
@@ -2799,13 +2966,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="13">
-        <v>0.25</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="O2" s="13">
         <v>0</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2813,10 +2980,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="D3" s="13">
         <v>100</v>
@@ -2825,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="K3" s="13">
         <v>10</v>
@@ -2846,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2854,10 +3021,10 @@
         <v>30003</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>170</v>
+        <v>61</v>
       </c>
       <c r="D4" s="13">
         <v>100</v>
@@ -2866,10 +3033,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="K4" s="13">
         <v>10</v>
@@ -2887,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2895,10 +3062,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D5" s="13">
         <v>100</v>
@@ -2907,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="K5" s="13">
         <v>15</v>
@@ -2928,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2936,10 +3103,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D6" s="13">
         <v>100</v>
@@ -2948,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="K6" s="13">
         <v>10</v>
@@ -2960,7 +3127,7 @@
         <v>10</v>
       </c>
       <c r="M6" s="13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" s="13">
         <v>2</v>
@@ -2969,7 +3136,7 @@
         <v>5</v>
       </c>
       <c r="P6" s="13" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2977,10 +3144,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D7" s="13">
         <v>100</v>
@@ -2989,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="K7" s="13">
         <v>10</v>
@@ -3010,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3018,10 +3185,10 @@
         <v>30007</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D8" s="13">
         <v>100</v>
@@ -3030,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="K8" s="13">
         <v>10</v>
@@ -3051,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3068,10 +3235,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D12" s="13">
         <v>150</v>
@@ -3080,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="H12" s="13" t="b">
         <v>1</v>
@@ -3101,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="13" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3109,10 +3276,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="D13" s="13">
         <v>150</v>
@@ -3121,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="H13" s="13" t="b">
         <v>1</v>
@@ -3142,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="13" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.75">
@@ -3150,10 +3317,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D14" s="13">
         <v>150</v>
@@ -3162,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="H14" s="13" t="b">
         <v>1</v>
@@ -3183,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3191,10 +3358,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D15" s="13">
         <v>150</v>
@@ -3203,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="H15" s="13" t="b">
         <v>1</v>
@@ -3224,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="13" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.75">
@@ -3232,10 +3399,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="D16" s="13">
         <v>150</v>
@@ -3244,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="H16" s="13" t="b">
         <v>1</v>
@@ -3265,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3273,10 +3440,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D17" s="13">
         <v>150</v>
@@ -3285,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="H17" s="13" t="b">
         <v>1</v>
@@ -3306,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="16.75">
@@ -3314,10 +3481,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="D18" s="13">
         <v>150</v>
@@ -3326,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="H18" s="13" t="b">
         <v>1</v>
@@ -3347,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="13" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -3368,8 +3535,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" style="13" customWidth="1"/>
@@ -3382,25 +3549,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3408,22 +3575,22 @@
         <v>50001</v>
       </c>
       <c r="B2" s="13">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="C2" s="13">
         <v>180</v>
       </c>
       <c r="D2" s="13">
-        <v>0.5</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3431,22 +3598,22 @@
         <v>50002</v>
       </c>
       <c r="B3" s="13">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="C3" s="13">
         <v>180</v>
       </c>
       <c r="D3" s="13">
-        <v>0.5</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3454,7 +3621,7 @@
         <v>50003</v>
       </c>
       <c r="B4" s="13">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="C4" s="13">
         <v>180</v>
@@ -3463,13 +3630,59 @@
         <v>0.5</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>185</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="13">
+        <v>50004</v>
+      </c>
+      <c r="B5" s="13">
+        <v>60</v>
+      </c>
+      <c r="C5" s="13">
+        <v>180</v>
+      </c>
+      <c r="D5" s="13">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="13">
+        <v>50005</v>
+      </c>
+      <c r="B6" s="13">
+        <v>60</v>
+      </c>
+      <c r="C6" s="13">
+        <v>180</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3482,7 +3695,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="12" style="13" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="13" customWidth="1"/>
@@ -3494,22 +3707,22 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.75">
       <c r="A2" s="7">
         <v>60001</v>
       </c>
@@ -3665,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="16.75">
       <c r="A16" s="9"/>
       <c r="D16" s="13">
         <v>0</v>
@@ -3695,7 +3908,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="10" style="13" customWidth="1"/>
     <col min="2" max="2" width="13.92578125" style="13" customWidth="1"/>
@@ -3706,22 +3919,22 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.75">
       <c r="A2" s="7">
         <v>70001</v>
       </c>
@@ -3889,7 +4102,7 @@
     <row r="15" spans="1:1">
       <c r="A15" s="8"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" ht="16.75">
       <c r="A16" s="9"/>
     </row>
   </sheetData>
@@ -3902,7 +4115,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="13" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="13" customWidth="1"/>
@@ -3910,19 +4123,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3954,31 +4167,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="13" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3986,10 +4199,10 @@
         <v>90001</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>145</v>
@@ -4006,10 +4219,10 @@
         <v>90001</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>145</v>
@@ -4026,10 +4239,10 @@
         <v>90001</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>145</v>
@@ -4046,13 +4259,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -4063,13 +4276,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
@@ -4080,13 +4293,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F7" s="1">
         <v>10</v>
@@ -4097,13 +4310,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="F8" s="1">
         <v>15</v>
@@ -4117,13 +4330,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -4137,13 +4350,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="F10" s="1">
         <v>40</v>
@@ -4157,13 +4370,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
@@ -4174,16 +4387,16 @@
         <v>90004</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F12" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4191,16 +4404,16 @@
         <v>90004</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F13" s="1">
-        <v>250</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4208,19 +4421,19 @@
         <v>90005</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
       </c>
       <c r="H14" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4228,19 +4441,19 @@
         <v>90005</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
       </c>
       <c r="H15" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4248,19 +4461,19 @@
         <v>90005</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="F16" s="1">
         <v>7</v>
       </c>
       <c r="H16" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4268,19 +4481,19 @@
         <v>90006</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="F17" s="13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G17" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4288,19 +4501,19 @@
         <v>90006</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="F18" s="13">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="G18" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4308,70 +4521,79 @@
         <v>90006</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="F19" s="13">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="G19" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="13">
         <v>90007</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F20" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="I20" s="13">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="13">
         <v>90007</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F21" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>50</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0.14999999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="13">
         <v>90007</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F22" s="1">
-        <v>350</v>
+        <v>100</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0.20000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainDefenseData.xlsx
+++ b/Assets/02_Resources/Data/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="3" activeTab="5"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="3"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
@@ -28,604 +28,604 @@
     <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
   </x:si>
   <x:si>
+    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
+  </x:si>
+  <x:si>
     <x:t>공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</x:t>
   </x:si>
   <x:si>
-    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
-  </x:si>
-  <x:si>
     <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</x:t>
   </x:si>
   <x:si>
-    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
+    <x:t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판다다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뱀이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거미다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MissileTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10011;10012;10013;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CannonTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExplosionRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_KMD_12_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SniperProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_MEL_05_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ColdAirRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염으로 지속적인 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10004;10005;10006;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격 딜레이 {0}/{1} % 감소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CannonProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_288_19_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_MEL_16_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MissileProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weighted_upgrades</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SniperTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_MEL_14_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>replace_train_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>max_upgrade_count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ColdAirProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LaserTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_KMD_10_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10014;10015;10016;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectrickProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10001;10002;10003;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>절대무적_요새_멜리에스클래식_몸통뉴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ExplosionProjectile</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_KMD_08_UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해골 왕이당.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">상어다 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미노타우로스다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5;3;2;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>놀이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Snake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>icon_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thief</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skull</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ranged</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해골 병사다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 거인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Turtle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>귀상어다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;3;5;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>max_hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;3;6;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거북이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도적이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spider</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Panda</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Melee</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lizard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gnoll</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인 기차</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_monsters</x:t>
   </x:si>
   <x:si>
     <x:t>target_train_id</x:t>
   </x:si>
   <x:si>
+    <x:t>FireTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제일 기본이 되는 기차이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력 {0}/{1} % 증가</x:t>
+  </x:si>
+  <x:si>
     <x:t>monster_name</x:t>
   </x:si>
   <x:si>
-    <x:t>제일 기본이 되는 기차이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>spawn_monsters</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FireTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>AttackInterval</x:t>
   </x:si>
   <x:si>
-    <x:t>폭발 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>NonTrainUpgrade</x:t>
   </x:si>
   <x:si>
+    <x:t>절대무적_요새_288버켓</x:t>
+  </x:si>
+  <x:si>
     <x:t>skill_icon_id</x:t>
   </x:si>
   <x:si>
-    <x:t>체력 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>절대무적_요새_288버켓</x:t>
-  </x:si>
-  <x:si>
     <x:t>upgrade_type</x:t>
   </x:si>
   <x:si>
+    <x:t>attack_count</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4;3.5;2;0.5;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_interval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_data_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>is_main_train</x:t>
+  </x:si>
+  <x:si>
+    <x:t>upgrade_value</x:t>
+  </x:si>
+  <x:si>
     <x:t>stage_end_time</x:t>
   </x:si>
   <x:si>
     <x:t>기관총으로 피해를 준다.</x:t>
   </x:si>
   <x:si>
-    <x:t>4;3.5;2;0.5;</x:t>
+    <x:t>화염 포탑에 강화 버전이다.</x:t>
   </x:si>
   <x:si>
     <x:t>저격 포탑에 강화 버전이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>skill_cooldown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>upgrade_name</x:t>
+  </x:si>
+  <x:si>
     <x:t>LaserProjectile</x:t>
   </x:si>
   <x:si>
-    <x:t>spawn_interval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>is_main_train</x:t>
-  </x:si>
-  <x:si>
-    <x:t>skill_cooldown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_data_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>upgrade_value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>upgrade_name</x:t>
-  </x:si>
-  <x:si>
     <x:t>AttackDamage</x:t>
   </x:si>
   <x:si>
     <x:t>attack_range</x:t>
   </x:si>
   <x:si>
+    <x:t>냉기 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑에 강화 버전이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_money_min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoblinSorcerer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_interval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target_count</x:t>
+  </x:si>
+  <x:si>
     <x:t>TrainUpgrade</x:t>
   </x:si>
   <x:si>
+    <x:t>attack_damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_exp_min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>drop_money_max</x:t>
+  </x:si>
+  <x:si>
     <x:t>drop_exp_max</x:t>
   </x:si>
   <x:si>
-    <x:t>target_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_exp_min</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_damage</x:t>
-  </x:si>
-  <x:si>
     <x:t>attack_delay</x:t>
   </x:si>
   <x:si>
-    <x:t>GoblinSorcerer</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_money_max</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포격 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>drop_money_min</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_interval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뱀이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거미다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판다다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>id</x:t>
+    <x:t>저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>stat_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 폭발 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포격 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>냉기 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 포격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 레이저 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;3;5;9;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>move_speed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 저격 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 미사일 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkullKing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoblinSpear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>attack_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>need_money</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 기관총 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hammershark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저격 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 화염 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>has_skill</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 창병이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Minotaur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MainTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prefab_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기관총 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GiantGoblin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.5;4;1.5;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린 주술사다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>train_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 전기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폭발 포탑 강화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>엘리트 냉기 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.5;3.5;1;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dwarf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도마뱀이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5;4;1;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>레이저 포탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난쟁이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1;4;6;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>범위 내에 있는 적들을 밀치고 피해를 준다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteElectrickTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteExplosionRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10007;10008;10009;10010;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_monsters_probability</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면에 있는 다수의 적들을 전기로 공격한다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포탑들의 체력이 {0}({1})만큼 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteFireTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spawn_monsters_level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteColdAirRangeTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectrickTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>projectile_prefab_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteSniperTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>획득하는 골드 {0}/{1} % 증가</x:t>
   </x:si>
   <x:si>
     <x:t>EliteMissileTurretTrain</x:t>
   </x:si>
   <x:si>
+    <x:t>FireEffectProjectile</x:t>
+  </x:si>
+  <x:si>
     <x:t>획득하는 경험치 {0}/{1} % 증가</x:t>
   </x:si>
   <x:si>
+    <x:t>EliteLaserTurretTrain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EliteCannonTurretTrain</x:t>
+  </x:si>
+  <x:si>
     <x:t>stage_inspection_time</x:t>
   </x:si>
   <x:si>
-    <x:t>EliteLaserTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>spawn_monsters_level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EliteCannonTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EliteSniperTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EliteColdAirRangeTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectrickTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>projectile_prefab_id</x:t>
-  </x:si>
-  <x:si>
     <x:t>EliteNormalTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FireEffectProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EliteFireTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>획득하는 골드 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MissileTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10011;10012;10013;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CannonTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExplosionRangeTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ColdAirRangeTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격 딜레이 {0}/{1} % 감소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_MEL_16_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>절대무적_요새_멜리에스클래식_몸통뉴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>max_upgrade_count</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10001;10002;10003;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MissileProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ExplosionProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_KMD_10_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>replace_train_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염으로 지속적인 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weighted_upgrades</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_KMD_08_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_KMD_12_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ColdAirProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_MEL_14_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SniperProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10014;10015;10016;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑에 강화 버전이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SniperTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_MEL_05_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LaserTurretTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectrickProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10004;10005;10006;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CannonProjectile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 {0}/{1} % 증가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_288_19_UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>prefab_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>폭발 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.5;4;1.5;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GiantGoblin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 주술사다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.5;3.5;1;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 전기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 냉기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>train_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 저격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>need_money</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포격 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 폭발 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 미사일 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkullKing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>move_speed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 포격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 레이저 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1;3;5;9;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stat_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GoblinSpear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 기관총 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Minotaur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MainTrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리트 화염 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>has_skill</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 창병이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hammershark</x:t>
-  </x:si>
-  <x:si>
-    <x:t>레이저 포탑 강화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해골 왕이당.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>icon_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린 거인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미노타우로스다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skull</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thief</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ranged</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저격 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해골 병사다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5;3;2;</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">상어다 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>기관총 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Turtle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미사일 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>놀이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Snake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>귀상어다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화염 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1;3;5;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>냉기 포탑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거북이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>max_hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1;3;6;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도적이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Spider</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포